--- a/MBA BA 2026-28 Term I Schedule .xlsx
+++ b/MBA BA 2026-28 Term I Schedule .xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="290" uniqueCount="210">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="290" uniqueCount="215">
   <si>
     <t>INDIAN INSTITUTE OF MANAGEMENT SAMBALPUR</t>
   </si>
@@ -221,25 +221,25 @@
     <t>DS-I - 9 (Guest Session)</t>
   </si>
   <si>
-    <t>DS-I - 10 (Guest Session)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MM - 9 (Prof. Atul Prashar) </t>
-  </si>
-  <si>
-    <t xml:space="preserve">FRA-8 (Prof. Seema Gupta) </t>
-  </si>
-  <si>
-    <t>MC -9 (Prof Kakoli Sen)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MM - 10 (Prof. Atul Prashar) </t>
-  </si>
-  <si>
     <t>Prof. Kaushik Bhattacharya
 BE_07</t>
   </si>
   <si>
+    <t>DS-I - 10 (Guest Session)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MM - 9 (Prof. Atul Prashar) </t>
+  </si>
+  <si>
+    <t xml:space="preserve">FRA-8 (Prof. Seema Gupta) </t>
+  </si>
+  <si>
+    <t>MC -9 (Prof Kakoli Sen)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MM - 10 (Prof. Atul Prashar) </t>
+  </si>
+  <si>
     <t xml:space="preserve">FRA-9 (Prof. Seema Gupta) </t>
   </si>
   <si>
@@ -271,21 +271,51 @@
     <t xml:space="preserve">OBD- 9 ( Prof. Atri Sengupta) </t>
   </si>
   <si>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color theme="1"/>
+      </rPr>
+      <t xml:space="preserve">OBD- 10 ( Prof. Atri Sengupta) 
+</t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <b/>
+        <color theme="1"/>
+      </rPr>
+      <t>09:00 - 10:30 AM</t>
+    </r>
+  </si>
+  <si>
+    <t>Prof. Kaushik Bhattacharya
+BE_10</t>
+  </si>
+  <si>
     <t>Prof. Kaushik Bhattacharya
 BE_09</t>
   </si>
   <si>
-    <t>Prof. Kaushik Bhattacharya
-BE_10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OBD- 10 ( Prof. Atri Sengupta) </t>
-  </si>
-  <si>
     <t>MComp - 10 (Prof. Manish Kumar)</t>
   </si>
   <si>
-    <t>MID TERM</t>
+    <t>MID TERM (FRA)</t>
+  </si>
+  <si>
+    <t>MID TERM (OBD)</t>
+  </si>
+  <si>
+    <t>MID TERM (BE)</t>
+  </si>
+  <si>
+    <t>MID TERM (MC)</t>
+  </si>
+  <si>
+    <t>MID TERM (MM)</t>
+  </si>
+  <si>
+    <t>MID TERM (DS I)</t>
   </si>
   <si>
     <t>END TERM (Mcomp)</t>
@@ -411,13 +441,13 @@
     <t>OBD - 14 (Prof. Shubhi Gupta)</t>
   </si>
   <si>
+    <t>OBD - 15 Guest Session</t>
+  </si>
+  <si>
+    <t>OBD - 16 Guest session</t>
+  </si>
+  <si>
     <t>DS-I - 16 (Prof. Kaustov Chakraborty)</t>
-  </si>
-  <si>
-    <t>OBD - 15 (Prof. Shubhi Gupta)</t>
-  </si>
-  <si>
-    <t>OBD - 16 (Prof. Shubhi Gupta)</t>
   </si>
   <si>
     <t>DS-I - 17 (Prof. Kaustov Chakraborty)</t>
@@ -565,7 +595,7 @@
     <t>MBA-BA102</t>
   </si>
   <si>
-    <t>Prof Kaustov Chakraborty</t>
+    <t>Prof. Kaustov Chakraborty</t>
   </si>
   <si>
     <t>kchakraborty@iimsambalpur.ac.in</t>
@@ -861,7 +891,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="79">
+  <cellXfs count="84">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -945,6 +975,9 @@
     <xf borderId="5" fillId="11" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" vertical="center"/>
     </xf>
+    <xf borderId="5" fillId="10" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
     <xf borderId="5" fillId="12" fontId="3" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" readingOrder="0" vertical="center"/>
     </xf>
@@ -981,6 +1014,7 @@
     <xf borderId="1" fillId="15" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" vertical="center"/>
     </xf>
+    <xf borderId="5" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="5" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
@@ -1002,12 +1036,15 @@
     <xf borderId="5" fillId="11" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
+    <xf borderId="5" fillId="11" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="5" fillId="11" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
+    </xf>
     <xf borderId="5" fillId="11" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="5" fillId="11" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
     <xf borderId="5" fillId="8" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" wrapText="0"/>
     </xf>
@@ -1020,16 +1057,18 @@
     <xf borderId="5" fillId="8" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" wrapText="1"/>
     </xf>
-    <xf borderId="5" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="5" fillId="3" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
+    <xf borderId="5" fillId="3" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="5" fillId="3" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
+    </xf>
     <xf borderId="5" fillId="3" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="5" fillId="3" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
     <xf borderId="5" fillId="14" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
@@ -1045,12 +1084,15 @@
     <xf borderId="5" fillId="7" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" wrapText="0"/>
     </xf>
+    <xf borderId="5" fillId="7" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="1"/>
+    </xf>
+    <xf borderId="5" fillId="7" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    </xf>
     <xf borderId="5" fillId="7" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="1"/>
     </xf>
-    <xf borderId="5" fillId="7" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
     <xf borderId="5" fillId="7" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" wrapText="1"/>
     </xf>
@@ -1069,11 +1111,14 @@
     <xf borderId="5" fillId="6" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" wrapText="0"/>
     </xf>
+    <xf borderId="5" fillId="6" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="1"/>
+    </xf>
+    <xf borderId="5" fillId="6" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    </xf>
     <xf borderId="5" fillId="6" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="1"/>
-    </xf>
-    <xf borderId="5" fillId="6" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
     <xf borderId="5" fillId="6" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" wrapText="1"/>
@@ -1311,14 +1356,15 @@
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
   <cols>
     <col customWidth="1" min="1" max="1" width="19.13"/>
-    <col customWidth="1" min="2" max="2" width="15.25"/>
+    <col customWidth="1" min="2" max="2" width="19.5"/>
     <col customWidth="1" min="3" max="3" width="25.0"/>
     <col customWidth="1" min="4" max="4" width="24.38"/>
     <col customWidth="1" min="5" max="5" width="17.13"/>
     <col customWidth="1" min="6" max="6" width="28.5"/>
     <col customWidth="1" min="7" max="7" width="26.0"/>
-    <col customWidth="1" min="9" max="9" width="25.63"/>
-    <col customWidth="1" min="11" max="11" width="29.0"/>
+    <col customWidth="1" min="9" max="9" width="14.25"/>
+    <col customWidth="1" min="10" max="10" width="7.38"/>
+    <col customWidth="1" min="11" max="11" width="23.5"/>
     <col customWidth="1" min="12" max="12" width="30.25"/>
   </cols>
   <sheetData>
@@ -1548,7 +1594,7 @@
       <c r="F12" s="16" t="s">
         <v>36</v>
       </c>
-      <c r="G12" s="9"/>
+      <c r="G12" s="17"/>
       <c r="J12" s="4"/>
     </row>
     <row r="13">
@@ -1582,7 +1628,7 @@
       <c r="F14" s="26" t="s">
         <v>39</v>
       </c>
-      <c r="G14" s="9"/>
+      <c r="G14" s="17"/>
       <c r="J14" s="4"/>
     </row>
     <row r="15">
@@ -1624,7 +1670,7 @@
       <c r="F16" s="26" t="s">
         <v>46</v>
       </c>
-      <c r="G16" s="9"/>
+      <c r="G16" s="17"/>
       <c r="J16" s="4"/>
     </row>
     <row r="17">
@@ -1658,10 +1704,10 @@
       <c r="F18" s="19" t="s">
         <v>49</v>
       </c>
-      <c r="G18" s="9"/>
+      <c r="G18" s="17"/>
       <c r="J18" s="4"/>
     </row>
-    <row r="19">
+    <row r="19" ht="28.5" customHeight="1">
       <c r="A19" s="11">
         <v>46231.0</v>
       </c>
@@ -1698,7 +1744,7 @@
       <c r="F20" s="16" t="s">
         <v>55</v>
       </c>
-      <c r="G20" s="9"/>
+      <c r="G20" s="17"/>
       <c r="J20" s="4"/>
     </row>
     <row r="21" ht="39.75" customHeight="1">
@@ -1738,7 +1784,7 @@
       <c r="F22" s="16" t="s">
         <v>61</v>
       </c>
-      <c r="G22" s="9"/>
+      <c r="G22" s="17"/>
       <c r="J22" s="4"/>
     </row>
     <row r="23">
@@ -1800,18 +1846,20 @@
       <c r="B26" s="12" t="s">
         <v>13</v>
       </c>
-      <c r="C26" s="9"/>
+      <c r="C26" s="28" t="s">
+        <v>67</v>
+      </c>
       <c r="D26" s="19" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E26" s="15"/>
       <c r="F26" s="16" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G26" s="17"/>
       <c r="J26" s="4"/>
     </row>
-    <row r="27">
+    <row r="27" ht="17.25" customHeight="1">
       <c r="A27" s="11">
         <v>46239.0</v>
       </c>
@@ -1819,16 +1867,16 @@
         <v>17</v>
       </c>
       <c r="C27" s="13" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D27" s="18" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E27" s="15"/>
       <c r="F27" s="16" t="s">
-        <v>71</v>
-      </c>
-      <c r="G27" s="9"/>
+        <v>72</v>
+      </c>
+      <c r="G27" s="17"/>
       <c r="J27" s="4"/>
     </row>
     <row r="28">
@@ -1838,9 +1886,6 @@
       <c r="B28" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="C28" s="28" t="s">
-        <v>72</v>
-      </c>
       <c r="D28" s="13" t="s">
         <v>73</v>
       </c>
@@ -1848,7 +1893,7 @@
       <c r="F28" s="14" t="s">
         <v>74</v>
       </c>
-      <c r="G28" s="9"/>
+      <c r="G28" s="17"/>
       <c r="J28" s="4"/>
     </row>
     <row r="29">
@@ -1902,14 +1947,14 @@
       <c r="B31" s="12" t="s">
         <v>31</v>
       </c>
-      <c r="C31" s="28" t="s">
+      <c r="C31" s="29" t="s">
         <v>83</v>
       </c>
       <c r="D31" s="28" t="s">
         <v>84</v>
       </c>
       <c r="E31" s="15"/>
-      <c r="F31" s="26" t="s">
+      <c r="F31" s="28" t="s">
         <v>85</v>
       </c>
       <c r="G31" s="14" t="s">
@@ -1932,84 +1977,82 @@
       <c r="J32" s="4"/>
     </row>
     <row r="33">
-      <c r="A33" s="29">
+      <c r="A33" s="30">
         <v>46245.0</v>
       </c>
-      <c r="B33" s="30" t="s">
+      <c r="B33" s="31" t="s">
         <v>13</v>
       </c>
-      <c r="C33" s="9"/>
-      <c r="D33" s="9"/>
-      <c r="E33" s="9"/>
-      <c r="F33" s="31" t="s">
+      <c r="C33" s="32" t="s">
         <v>87</v>
+      </c>
+      <c r="D33" s="3"/>
+      <c r="E33" s="33"/>
+      <c r="F33" s="32" t="s">
+        <v>88</v>
       </c>
       <c r="G33" s="3"/>
       <c r="J33" s="4"/>
     </row>
     <row r="34">
-      <c r="A34" s="29">
+      <c r="A34" s="30">
         <v>46246.0</v>
       </c>
-      <c r="B34" s="30" t="s">
+      <c r="B34" s="31" t="s">
         <v>17</v>
       </c>
-      <c r="C34" s="31" t="s">
-        <v>87</v>
+      <c r="C34" s="32" t="s">
+        <v>89</v>
       </c>
       <c r="D34" s="3"/>
-      <c r="E34" s="32"/>
-      <c r="F34" s="31" t="s">
-        <v>87</v>
+      <c r="E34" s="33"/>
+      <c r="F34" s="32" t="s">
+        <v>90</v>
       </c>
       <c r="G34" s="3"/>
       <c r="J34" s="4"/>
     </row>
     <row r="35">
-      <c r="A35" s="29">
+      <c r="A35" s="30">
         <v>46247.0</v>
       </c>
-      <c r="B35" s="30" t="s">
+      <c r="B35" s="31" t="s">
         <v>21</v>
       </c>
-      <c r="C35" s="31" t="s">
-        <v>87</v>
+      <c r="C35" s="32" t="s">
+        <v>91</v>
       </c>
       <c r="D35" s="3"/>
-      <c r="E35" s="32"/>
-      <c r="F35" s="31" t="s">
-        <v>87</v>
+      <c r="E35" s="33"/>
+      <c r="F35" s="32" t="s">
+        <v>92</v>
       </c>
       <c r="G35" s="3"/>
       <c r="J35" s="4"/>
     </row>
     <row r="36">
-      <c r="A36" s="29">
+      <c r="A36" s="30">
         <v>46248.0</v>
       </c>
-      <c r="B36" s="30" t="s">
+      <c r="B36" s="31" t="s">
         <v>25</v>
       </c>
-      <c r="C36" s="31" t="s">
-        <v>87</v>
+      <c r="C36" s="32" t="s">
+        <v>93</v>
       </c>
       <c r="D36" s="3"/>
-      <c r="E36" s="32"/>
-      <c r="F36" s="31" t="s">
-        <v>88</v>
-      </c>
-      <c r="G36" s="3"/>
+      <c r="E36" s="33"/>
       <c r="J36" s="4"/>
     </row>
     <row r="37" ht="21.0" customHeight="1">
-      <c r="A37" s="33">
+      <c r="A37" s="34">
         <v>46249.0</v>
       </c>
-      <c r="B37" s="34" t="s">
+      <c r="B37" s="35" t="s">
         <v>28</v>
       </c>
-      <c r="C37" s="35" t="s">
-        <v>89</v>
+      <c r="C37" s="36" t="s">
+        <v>94</v>
       </c>
       <c r="D37" s="2"/>
       <c r="E37" s="2"/>
@@ -2038,15 +2081,15 @@
       <c r="B39" s="12" t="s">
         <v>32</v>
       </c>
-      <c r="C39" s="36" t="s">
-        <v>90</v>
+      <c r="C39" s="37" t="s">
+        <v>95</v>
       </c>
       <c r="D39" s="18" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="E39" s="15"/>
       <c r="F39" s="13" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="G39" s="17"/>
       <c r="J39" s="4"/>
@@ -2058,15 +2101,15 @@
       <c r="B40" s="12" t="s">
         <v>13</v>
       </c>
-      <c r="C40" s="36" t="s">
-        <v>93</v>
+      <c r="C40" s="37" t="s">
+        <v>98</v>
       </c>
       <c r="D40" s="16" t="s">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="E40" s="15"/>
       <c r="F40" s="13" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="G40" s="17"/>
       <c r="J40" s="4"/>
@@ -2078,15 +2121,15 @@
       <c r="B41" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="C41" s="36" t="s">
-        <v>96</v>
+      <c r="C41" s="37" t="s">
+        <v>101</v>
       </c>
       <c r="D41" s="18" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="E41" s="15"/>
       <c r="F41" s="16" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="G41" s="17"/>
       <c r="J41" s="4"/>
@@ -2098,15 +2141,15 @@
       <c r="B42" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="C42" s="36" t="s">
-        <v>99</v>
+      <c r="C42" s="37" t="s">
+        <v>104</v>
       </c>
       <c r="D42" s="26" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="E42" s="15"/>
       <c r="F42" s="19" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="G42" s="17"/>
       <c r="J42" s="4"/>
@@ -2119,14 +2162,14 @@
         <v>25</v>
       </c>
       <c r="C43" s="19" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="D43" s="13" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="E43" s="15"/>
       <c r="F43" s="26" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="G43" s="17"/>
       <c r="J43" s="4"/>
@@ -2139,14 +2182,14 @@
         <v>28</v>
       </c>
       <c r="C44" s="19" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="D44" s="19" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="E44" s="15"/>
       <c r="F44" s="26" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="G44" s="17"/>
       <c r="J44" s="4"/>
@@ -2172,15 +2215,15 @@
       <c r="B46" s="12" t="s">
         <v>32</v>
       </c>
-      <c r="C46" s="37" t="s">
-        <v>108</v>
+      <c r="C46" s="38" t="s">
+        <v>113</v>
       </c>
       <c r="D46" s="16" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="E46" s="15"/>
       <c r="F46" s="13" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="G46" s="17"/>
       <c r="J46" s="4"/>
@@ -2194,24 +2237,24 @@
       </c>
       <c r="C47" s="17"/>
       <c r="D47" s="18" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="E47" s="15"/>
       <c r="F47" s="13" t="s">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="G47" s="17"/>
       <c r="J47" s="4"/>
     </row>
     <row r="48" ht="27.75" customHeight="1">
-      <c r="A48" s="38">
+      <c r="A48" s="39">
         <v>46260.0</v>
       </c>
-      <c r="B48" s="39" t="s">
+      <c r="B48" s="40" t="s">
         <v>17</v>
       </c>
-      <c r="C48" s="40" t="s">
-        <v>113</v>
+      <c r="C48" s="41" t="s">
+        <v>118</v>
       </c>
       <c r="D48" s="2"/>
       <c r="E48" s="2"/>
@@ -2226,15 +2269,15 @@
       <c r="B49" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="C49" s="37" t="s">
-        <v>114</v>
+      <c r="C49" s="38" t="s">
+        <v>119</v>
       </c>
       <c r="D49" s="16" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="E49" s="15"/>
       <c r="F49" s="13" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="G49" s="17"/>
       <c r="J49" s="4"/>
@@ -2248,7 +2291,7 @@
       </c>
       <c r="C50" s="17"/>
       <c r="D50" s="18" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="E50" s="15"/>
       <c r="F50" s="9"/>
@@ -2290,15 +2333,15 @@
       <c r="B53" s="12" t="s">
         <v>32</v>
       </c>
-      <c r="C53" s="36" t="s">
-        <v>118</v>
+      <c r="C53" s="37" t="s">
+        <v>123</v>
       </c>
       <c r="D53" s="16" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="E53" s="15"/>
       <c r="F53" s="13" t="s">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="G53" s="17"/>
       <c r="J53" s="4"/>
@@ -2310,15 +2353,15 @@
       <c r="B54" s="12" t="s">
         <v>13</v>
       </c>
-      <c r="C54" s="36" t="s">
-        <v>121</v>
-      </c>
-      <c r="D54" s="37" t="s">
-        <v>122</v>
+      <c r="C54" s="37" t="s">
+        <v>126</v>
+      </c>
+      <c r="D54" s="38" t="s">
+        <v>127</v>
       </c>
       <c r="E54" s="15"/>
       <c r="F54" s="18" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="G54" s="17"/>
       <c r="J54" s="4"/>
@@ -2330,15 +2373,15 @@
       <c r="B55" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="C55" s="36" t="s">
-        <v>124</v>
+      <c r="C55" s="37" t="s">
+        <v>129</v>
       </c>
       <c r="D55" s="13" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="E55" s="15"/>
       <c r="F55" s="16" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="G55" s="17"/>
       <c r="J55" s="4"/>
@@ -2351,10 +2394,10 @@
         <v>21</v>
       </c>
       <c r="C56" s="19" t="s">
-        <v>127</v>
+        <v>132</v>
       </c>
       <c r="D56" s="26" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="E56" s="15"/>
       <c r="F56" s="9"/>
@@ -2368,17 +2411,17 @@
       <c r="B57" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="C57" s="19" t="s">
-        <v>129</v>
+      <c r="C57" s="26" t="s">
+        <v>134</v>
       </c>
       <c r="D57" s="26" t="s">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="E57" s="15"/>
-      <c r="F57" s="26" t="s">
-        <v>131</v>
-      </c>
-      <c r="G57" s="17"/>
+      <c r="F57" s="19" t="s">
+        <v>136</v>
+      </c>
+      <c r="G57" s="42"/>
       <c r="J57" s="4"/>
     </row>
     <row r="58">
@@ -2389,14 +2432,14 @@
         <v>28</v>
       </c>
       <c r="C58" s="19" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="D58" s="26" t="s">
-        <v>133</v>
+        <v>138</v>
       </c>
       <c r="E58" s="15"/>
       <c r="F58" s="16" t="s">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="G58" s="17"/>
       <c r="J58" s="4"/>
@@ -2422,15 +2465,15 @@
       <c r="B60" s="12" t="s">
         <v>32</v>
       </c>
-      <c r="C60" s="37" t="s">
-        <v>135</v>
+      <c r="C60" s="38" t="s">
+        <v>140</v>
       </c>
       <c r="D60" s="16" t="s">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="E60" s="15"/>
       <c r="F60" s="13" t="s">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="G60" s="17"/>
       <c r="J60" s="4"/>
@@ -2443,8 +2486,8 @@
         <v>13</v>
       </c>
       <c r="C61" s="9"/>
-      <c r="D61" s="37" t="s">
-        <v>138</v>
+      <c r="D61" s="38" t="s">
+        <v>143</v>
       </c>
       <c r="E61" s="15"/>
       <c r="F61" s="17"/>
@@ -2458,15 +2501,15 @@
       <c r="B62" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="C62" s="36" t="s">
-        <v>139</v>
+      <c r="C62" s="37" t="s">
+        <v>144</v>
       </c>
       <c r="D62" s="16" t="s">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="E62" s="15"/>
       <c r="F62" s="16" t="s">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="G62" s="17"/>
       <c r="J62" s="4"/>
@@ -2478,15 +2521,15 @@
       <c r="B63" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="C63" s="37" t="s">
-        <v>142</v>
+      <c r="C63" s="38" t="s">
+        <v>147</v>
       </c>
       <c r="D63" s="13" t="s">
-        <v>143</v>
+        <v>148</v>
       </c>
       <c r="E63" s="15"/>
-      <c r="F63" s="36" t="s">
-        <v>144</v>
+      <c r="F63" s="37" t="s">
+        <v>149</v>
       </c>
       <c r="G63" s="17"/>
       <c r="J63" s="4"/>
@@ -2498,14 +2541,14 @@
       <c r="B64" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="C64" s="36" t="s">
-        <v>145</v>
+      <c r="C64" s="37" t="s">
+        <v>150</v>
       </c>
       <c r="D64" s="18" t="s">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="E64" s="15"/>
-      <c r="F64" s="9"/>
+      <c r="F64" s="17"/>
       <c r="G64" s="17"/>
       <c r="J64" s="4"/>
     </row>
@@ -2519,7 +2562,7 @@
       <c r="C65" s="9"/>
       <c r="D65" s="9"/>
       <c r="E65" s="15"/>
-      <c r="F65" s="9"/>
+      <c r="F65" s="17"/>
       <c r="G65" s="17"/>
       <c r="J65" s="4"/>
     </row>
@@ -2544,11 +2587,11 @@
       <c r="B67" s="12" t="s">
         <v>32</v>
       </c>
-      <c r="C67" s="37" t="s">
-        <v>147</v>
+      <c r="C67" s="38" t="s">
+        <v>152</v>
       </c>
       <c r="D67" s="18" t="s">
-        <v>148</v>
+        <v>153</v>
       </c>
       <c r="E67" s="15"/>
       <c r="F67" s="9"/>
@@ -2562,11 +2605,11 @@
       <c r="B68" s="12" t="s">
         <v>13</v>
       </c>
-      <c r="C68" s="37" t="s">
-        <v>149</v>
+      <c r="C68" s="38" t="s">
+        <v>154</v>
       </c>
       <c r="D68" s="18" t="s">
-        <v>150</v>
+        <v>155</v>
       </c>
       <c r="E68" s="15"/>
       <c r="F68" s="17"/>
@@ -2581,10 +2624,10 @@
         <v>17</v>
       </c>
       <c r="C69" s="19" t="s">
-        <v>151</v>
+        <v>156</v>
       </c>
       <c r="D69" s="26" t="s">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="E69" s="15"/>
       <c r="F69" s="9"/>
@@ -2599,14 +2642,14 @@
         <v>21</v>
       </c>
       <c r="C70" s="19" t="s">
-        <v>153</v>
+        <v>158</v>
       </c>
       <c r="D70" s="26" t="s">
-        <v>154</v>
+        <v>159</v>
       </c>
       <c r="E70" s="15"/>
       <c r="F70" s="18" t="s">
-        <v>155</v>
+        <v>160</v>
       </c>
       <c r="G70" s="17"/>
       <c r="J70" s="4"/>
@@ -2619,14 +2662,14 @@
         <v>25</v>
       </c>
       <c r="C71" s="19" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="D71" s="26" t="s">
-        <v>157</v>
+        <v>162</v>
       </c>
       <c r="E71" s="15"/>
-      <c r="F71" s="37" t="s">
-        <v>158</v>
+      <c r="F71" s="38" t="s">
+        <v>163</v>
       </c>
       <c r="G71" s="17"/>
       <c r="J71" s="4"/>
@@ -2638,11 +2681,11 @@
       <c r="B72" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="C72" s="37" t="s">
-        <v>159</v>
+      <c r="C72" s="38" t="s">
+        <v>164</v>
       </c>
       <c r="D72" s="18" t="s">
-        <v>160</v>
+        <v>165</v>
       </c>
       <c r="E72" s="15"/>
       <c r="F72" s="17"/>
@@ -2673,7 +2716,7 @@
       <c r="C74" s="17"/>
       <c r="D74" s="17"/>
       <c r="E74" s="15"/>
-      <c r="F74" s="41"/>
+      <c r="F74" s="43"/>
       <c r="G74" s="17"/>
       <c r="J74" s="4"/>
     </row>
@@ -2687,143 +2730,143 @@
       <c r="C75" s="17"/>
       <c r="D75" s="17"/>
       <c r="E75" s="15"/>
-      <c r="F75" s="41"/>
+      <c r="F75" s="43"/>
       <c r="G75" s="17"/>
       <c r="J75" s="4"/>
     </row>
     <row r="76">
-      <c r="A76" s="29">
+      <c r="A76" s="30">
         <v>46288.0</v>
       </c>
-      <c r="B76" s="30" t="s">
+      <c r="B76" s="31" t="s">
         <v>17</v>
       </c>
-      <c r="C76" s="31" t="s">
-        <v>161</v>
+      <c r="C76" s="32" t="s">
+        <v>166</v>
       </c>
       <c r="D76" s="3"/>
-      <c r="E76" s="32"/>
-      <c r="F76" s="31" t="s">
-        <v>161</v>
+      <c r="E76" s="33"/>
+      <c r="F76" s="32" t="s">
+        <v>166</v>
       </c>
       <c r="G76" s="3"/>
       <c r="J76" s="4"/>
     </row>
     <row r="77">
-      <c r="A77" s="29">
+      <c r="A77" s="30">
         <v>46289.0</v>
       </c>
-      <c r="B77" s="30" t="s">
+      <c r="B77" s="31" t="s">
         <v>21</v>
       </c>
-      <c r="C77" s="31" t="s">
-        <v>161</v>
+      <c r="C77" s="32" t="s">
+        <v>166</v>
       </c>
       <c r="D77" s="3"/>
-      <c r="E77" s="32"/>
-      <c r="F77" s="31" t="s">
-        <v>161</v>
+      <c r="E77" s="33"/>
+      <c r="F77" s="32" t="s">
+        <v>166</v>
       </c>
       <c r="G77" s="3"/>
       <c r="J77" s="4"/>
     </row>
     <row r="78">
-      <c r="A78" s="29">
+      <c r="A78" s="30">
         <v>46290.0</v>
       </c>
-      <c r="B78" s="30" t="s">
+      <c r="B78" s="31" t="s">
         <v>25</v>
       </c>
-      <c r="C78" s="31" t="s">
-        <v>161</v>
+      <c r="C78" s="32" t="s">
+        <v>166</v>
       </c>
       <c r="D78" s="3"/>
-      <c r="E78" s="32"/>
-      <c r="F78" s="31" t="s">
-        <v>161</v>
+      <c r="E78" s="33"/>
+      <c r="F78" s="32" t="s">
+        <v>166</v>
       </c>
       <c r="G78" s="3"/>
       <c r="J78" s="4"/>
     </row>
     <row r="79">
-      <c r="A79" s="29">
+      <c r="A79" s="30">
         <v>46291.0</v>
       </c>
-      <c r="B79" s="30" t="s">
+      <c r="B79" s="31" t="s">
         <v>28</v>
       </c>
-      <c r="C79" s="31" t="s">
-        <v>162</v>
+      <c r="C79" s="32" t="s">
+        <v>167</v>
       </c>
       <c r="D79" s="3"/>
-      <c r="E79" s="32"/>
-      <c r="F79" s="31"/>
+      <c r="E79" s="33"/>
+      <c r="F79" s="32"/>
       <c r="G79" s="3"/>
       <c r="J79" s="4"/>
     </row>
     <row r="80">
-      <c r="A80" s="42"/>
-      <c r="F80" s="43"/>
+      <c r="A80" s="44"/>
+      <c r="F80" s="45"/>
       <c r="J80" s="4"/>
     </row>
     <row r="81">
-      <c r="A81" s="42"/>
-      <c r="F81" s="43"/>
+      <c r="A81" s="44"/>
+      <c r="F81" s="45"/>
       <c r="J81" s="4"/>
     </row>
     <row r="82">
-      <c r="A82" s="44" t="s">
-        <v>163</v>
-      </c>
-      <c r="B82" s="45" t="s">
-        <v>164</v>
-      </c>
-      <c r="C82" s="44" t="s">
-        <v>165</v>
-      </c>
-      <c r="D82" s="44" t="s">
-        <v>166</v>
-      </c>
-      <c r="E82" s="44" t="s">
-        <v>167</v>
-      </c>
-      <c r="F82" s="45" t="s">
+      <c r="A82" s="46" t="s">
         <v>168</v>
       </c>
-      <c r="G82" s="46" t="s">
+      <c r="B82" s="47" t="s">
         <v>169</v>
       </c>
-      <c r="H82" s="46" t="s">
+      <c r="C82" s="46" t="s">
         <v>170</v>
       </c>
-      <c r="I82" s="46" t="s">
+      <c r="D82" s="46" t="s">
         <v>171</v>
       </c>
+      <c r="E82" s="46" t="s">
+        <v>172</v>
+      </c>
+      <c r="F82" s="47" t="s">
+        <v>173</v>
+      </c>
+      <c r="G82" s="48" t="s">
+        <v>174</v>
+      </c>
+      <c r="H82" s="48" t="s">
+        <v>175</v>
+      </c>
+      <c r="I82" s="48" t="s">
+        <v>176</v>
+      </c>
       <c r="J82" s="4"/>
     </row>
     <row r="83">
-      <c r="A83" s="47">
+      <c r="A83" s="49">
         <v>1.0</v>
       </c>
-      <c r="B83" s="48" t="s">
-        <v>172</v>
-      </c>
-      <c r="C83" s="47">
+      <c r="B83" s="50" t="s">
+        <v>177</v>
+      </c>
+      <c r="C83" s="49">
         <v>3.0</v>
       </c>
-      <c r="D83" s="49" t="s">
-        <v>173</v>
-      </c>
-      <c r="E83" s="49" t="s">
-        <v>174</v>
-      </c>
-      <c r="F83" s="48" t="s">
-        <v>175</v>
-      </c>
-      <c r="G83" s="36"/>
+      <c r="D83" s="51" t="s">
+        <v>178</v>
+      </c>
+      <c r="E83" s="51" t="s">
+        <v>179</v>
+      </c>
+      <c r="F83" s="52" t="s">
+        <v>180</v>
+      </c>
+      <c r="G83" s="37"/>
       <c r="H83" s="17"/>
       <c r="I83" s="12" t="s">
-        <v>176</v>
+        <v>181</v>
       </c>
       <c r="J83" s="10"/>
       <c r="K83" s="9"/>
@@ -2841,54 +2884,54 @@
       <c r="W83" s="9"/>
     </row>
     <row r="84">
-      <c r="A84" s="50">
+      <c r="A84" s="53">
         <v>2.0</v>
       </c>
-      <c r="B84" s="51" t="s">
-        <v>177</v>
-      </c>
-      <c r="C84" s="50">
+      <c r="B84" s="54" t="s">
+        <v>182</v>
+      </c>
+      <c r="C84" s="53">
         <v>3.0</v>
       </c>
-      <c r="D84" s="52" t="s">
-        <v>178</v>
-      </c>
-      <c r="E84" s="52" t="s">
-        <v>179</v>
-      </c>
-      <c r="F84" s="51" t="s">
-        <v>180</v>
-      </c>
-      <c r="G84" s="53"/>
-      <c r="H84" s="54"/>
-      <c r="I84" s="46" t="s">
-        <v>181</v>
+      <c r="D84" s="55" t="s">
+        <v>183</v>
+      </c>
+      <c r="E84" s="55" t="s">
+        <v>184</v>
+      </c>
+      <c r="F84" s="54" t="s">
+        <v>185</v>
+      </c>
+      <c r="G84" s="56"/>
+      <c r="H84" s="42"/>
+      <c r="I84" s="48" t="s">
+        <v>186</v>
       </c>
       <c r="J84" s="4"/>
     </row>
     <row r="85">
-      <c r="A85" s="55">
+      <c r="A85" s="57">
         <v>3.0</v>
       </c>
-      <c r="B85" s="56" t="s">
-        <v>182</v>
-      </c>
-      <c r="C85" s="55">
+      <c r="B85" s="58" t="s">
+        <v>187</v>
+      </c>
+      <c r="C85" s="57">
         <v>3.0</v>
       </c>
-      <c r="D85" s="57" t="s">
-        <v>183</v>
-      </c>
-      <c r="E85" s="57" t="s">
-        <v>184</v>
-      </c>
-      <c r="F85" s="56" t="s">
-        <v>185</v>
+      <c r="D85" s="59" t="s">
+        <v>188</v>
+      </c>
+      <c r="E85" s="59" t="s">
+        <v>189</v>
+      </c>
+      <c r="F85" s="60" t="s">
+        <v>190</v>
       </c>
       <c r="G85" s="13"/>
       <c r="H85" s="17"/>
       <c r="I85" s="12" t="s">
-        <v>186</v>
+        <v>191</v>
       </c>
       <c r="J85" s="10"/>
       <c r="K85" s="9"/>
@@ -2906,4701 +2949,4701 @@
       <c r="W85" s="9"/>
     </row>
     <row r="86">
-      <c r="A86" s="58">
+      <c r="A86" s="61">
         <v>4.0</v>
       </c>
-      <c r="B86" s="59" t="s">
-        <v>187</v>
-      </c>
-      <c r="C86" s="58">
+      <c r="B86" s="62" t="s">
+        <v>192</v>
+      </c>
+      <c r="C86" s="61">
         <v>1.5</v>
       </c>
-      <c r="D86" s="60" t="s">
-        <v>188</v>
-      </c>
-      <c r="E86" s="60" t="s">
-        <v>189</v>
-      </c>
-      <c r="F86" s="59" t="s">
-        <v>190</v>
-      </c>
-      <c r="G86" s="61"/>
-      <c r="H86" s="54"/>
-      <c r="I86" s="46" t="s">
-        <v>191</v>
+      <c r="D86" s="63" t="s">
+        <v>193</v>
+      </c>
+      <c r="E86" s="63" t="s">
+        <v>194</v>
+      </c>
+      <c r="F86" s="62" t="s">
+        <v>195</v>
+      </c>
+      <c r="G86" s="64"/>
+      <c r="H86" s="42"/>
+      <c r="I86" s="48" t="s">
+        <v>196</v>
       </c>
       <c r="J86" s="4"/>
     </row>
     <row r="87">
-      <c r="A87" s="62">
+      <c r="A87" s="65">
         <v>5.0</v>
       </c>
-      <c r="B87" s="63" t="s">
-        <v>192</v>
-      </c>
-      <c r="C87" s="62">
+      <c r="B87" s="66" t="s">
+        <v>197</v>
+      </c>
+      <c r="C87" s="65">
         <v>3.0</v>
       </c>
-      <c r="D87" s="64" t="s">
-        <v>173</v>
-      </c>
-      <c r="E87" s="64" t="s">
+      <c r="D87" s="67" t="s">
+        <v>178</v>
+      </c>
+      <c r="E87" s="67" t="s">
+        <v>198</v>
+      </c>
+      <c r="F87" s="68" t="s">
+        <v>199</v>
+      </c>
+      <c r="G87" s="69"/>
+      <c r="H87" s="42"/>
+      <c r="I87" s="48" t="s">
+        <v>200</v>
+      </c>
+      <c r="J87" s="4"/>
+    </row>
+    <row r="88">
+      <c r="A88" s="70">
+        <v>6.0</v>
+      </c>
+      <c r="B88" s="71" t="s">
+        <v>201</v>
+      </c>
+      <c r="C88" s="70">
+        <v>1.5</v>
+      </c>
+      <c r="D88" s="72" t="s">
         <v>193</v>
       </c>
-      <c r="F87" s="63" t="s">
-        <v>194</v>
-      </c>
-      <c r="G87" s="65"/>
-      <c r="H87" s="54"/>
-      <c r="I87" s="46" t="s">
-        <v>195</v>
-      </c>
-      <c r="J87" s="4"/>
-    </row>
-    <row r="88">
-      <c r="A88" s="66">
-        <v>6.0</v>
-      </c>
-      <c r="B88" s="67" t="s">
-        <v>196</v>
-      </c>
-      <c r="C88" s="66">
-        <v>1.5</v>
-      </c>
-      <c r="D88" s="68" t="s">
-        <v>188</v>
-      </c>
-      <c r="E88" s="68" t="s">
-        <v>197</v>
-      </c>
-      <c r="F88" s="67" t="s">
-        <v>198</v>
-      </c>
-      <c r="G88" s="69"/>
-      <c r="H88" s="54"/>
-      <c r="I88" s="46" t="s">
-        <v>199</v>
+      <c r="E88" s="72" t="s">
+        <v>202</v>
+      </c>
+      <c r="F88" s="71" t="s">
+        <v>203</v>
+      </c>
+      <c r="G88" s="73"/>
+      <c r="H88" s="42"/>
+      <c r="I88" s="48" t="s">
+        <v>204</v>
       </c>
       <c r="J88" s="4"/>
     </row>
     <row r="89">
-      <c r="A89" s="70">
+      <c r="A89" s="74">
         <v>7.0</v>
       </c>
-      <c r="B89" s="71" t="s">
-        <v>200</v>
-      </c>
-      <c r="C89" s="70">
+      <c r="B89" s="75" t="s">
+        <v>205</v>
+      </c>
+      <c r="C89" s="74">
         <v>3.0</v>
       </c>
-      <c r="D89" s="72" t="s">
-        <v>201</v>
-      </c>
-      <c r="E89" s="72" t="s">
-        <v>202</v>
-      </c>
-      <c r="F89" s="71" t="s">
-        <v>203</v>
-      </c>
-      <c r="G89" s="73"/>
-      <c r="H89" s="54"/>
-      <c r="I89" s="46" t="s">
-        <v>204</v>
+      <c r="D89" s="76" t="s">
+        <v>206</v>
+      </c>
+      <c r="E89" s="76" t="s">
+        <v>207</v>
+      </c>
+      <c r="F89" s="77" t="s">
+        <v>208</v>
+      </c>
+      <c r="G89" s="78"/>
+      <c r="H89" s="42"/>
+      <c r="I89" s="48" t="s">
+        <v>209</v>
       </c>
       <c r="J89" s="4"/>
     </row>
     <row r="90">
-      <c r="A90" s="74">
+      <c r="A90" s="79">
         <v>8.0</v>
       </c>
-      <c r="B90" s="75" t="s">
-        <v>205</v>
-      </c>
-      <c r="C90" s="74">
+      <c r="B90" s="80" t="s">
+        <v>210</v>
+      </c>
+      <c r="C90" s="79">
         <v>3.0</v>
       </c>
-      <c r="D90" s="76" t="s">
-        <v>206</v>
-      </c>
-      <c r="E90" s="76" t="s">
-        <v>207</v>
-      </c>
-      <c r="F90" s="77" t="s">
-        <v>208</v>
-      </c>
-      <c r="G90" s="78"/>
-      <c r="H90" s="54"/>
-      <c r="I90" s="46" t="s">
-        <v>209</v>
+      <c r="D90" s="81" t="s">
+        <v>211</v>
+      </c>
+      <c r="E90" s="81" t="s">
+        <v>212</v>
+      </c>
+      <c r="F90" s="82" t="s">
+        <v>213</v>
+      </c>
+      <c r="G90" s="83"/>
+      <c r="H90" s="42"/>
+      <c r="I90" s="48" t="s">
+        <v>214</v>
       </c>
       <c r="J90" s="4"/>
     </row>
     <row r="91">
-      <c r="A91" s="42"/>
-      <c r="F91" s="43"/>
+      <c r="A91" s="44"/>
+      <c r="F91" s="45"/>
       <c r="J91" s="4"/>
     </row>
     <row r="92">
-      <c r="A92" s="42"/>
-      <c r="F92" s="43"/>
+      <c r="A92" s="44"/>
+      <c r="F92" s="45"/>
       <c r="J92" s="4"/>
     </row>
     <row r="93">
-      <c r="A93" s="42"/>
-      <c r="F93" s="43"/>
+      <c r="A93" s="44"/>
+      <c r="F93" s="45"/>
       <c r="J93" s="4"/>
     </row>
     <row r="94">
-      <c r="A94" s="42"/>
-      <c r="F94" s="43"/>
+      <c r="A94" s="44"/>
+      <c r="F94" s="45"/>
       <c r="J94" s="4"/>
     </row>
     <row r="95">
-      <c r="A95" s="42"/>
-      <c r="F95" s="43"/>
+      <c r="A95" s="44"/>
+      <c r="F95" s="45"/>
       <c r="J95" s="4"/>
     </row>
     <row r="96">
-      <c r="A96" s="42"/>
-      <c r="F96" s="43"/>
+      <c r="A96" s="44"/>
+      <c r="F96" s="45"/>
       <c r="J96" s="4"/>
     </row>
     <row r="97">
-      <c r="A97" s="42"/>
-      <c r="F97" s="43"/>
+      <c r="A97" s="44"/>
+      <c r="F97" s="45"/>
       <c r="J97" s="4"/>
     </row>
     <row r="98">
-      <c r="A98" s="42"/>
-      <c r="F98" s="43"/>
+      <c r="A98" s="44"/>
+      <c r="F98" s="45"/>
       <c r="J98" s="4"/>
     </row>
     <row r="99">
-      <c r="A99" s="42"/>
-      <c r="F99" s="43"/>
+      <c r="A99" s="44"/>
+      <c r="F99" s="45"/>
       <c r="J99" s="4"/>
     </row>
     <row r="100">
-      <c r="A100" s="42"/>
-      <c r="F100" s="43"/>
+      <c r="A100" s="44"/>
+      <c r="F100" s="45"/>
       <c r="J100" s="4"/>
     </row>
     <row r="101">
-      <c r="A101" s="42"/>
-      <c r="F101" s="43"/>
+      <c r="A101" s="44"/>
+      <c r="F101" s="45"/>
       <c r="J101" s="4"/>
     </row>
     <row r="102">
-      <c r="A102" s="42"/>
-      <c r="F102" s="43"/>
+      <c r="A102" s="44"/>
+      <c r="F102" s="45"/>
       <c r="J102" s="4"/>
     </row>
     <row r="103">
-      <c r="A103" s="42"/>
-      <c r="F103" s="43"/>
+      <c r="A103" s="44"/>
+      <c r="F103" s="45"/>
       <c r="J103" s="4"/>
     </row>
     <row r="104">
-      <c r="A104" s="42"/>
-      <c r="F104" s="43"/>
+      <c r="A104" s="44"/>
+      <c r="F104" s="45"/>
       <c r="J104" s="4"/>
     </row>
     <row r="105">
-      <c r="A105" s="42"/>
-      <c r="F105" s="43"/>
+      <c r="A105" s="44"/>
+      <c r="F105" s="45"/>
       <c r="J105" s="4"/>
     </row>
     <row r="106">
-      <c r="A106" s="42"/>
-      <c r="F106" s="43"/>
+      <c r="A106" s="44"/>
+      <c r="F106" s="45"/>
       <c r="J106" s="4"/>
     </row>
     <row r="107">
-      <c r="A107" s="42"/>
-      <c r="F107" s="43"/>
+      <c r="A107" s="44"/>
+      <c r="F107" s="45"/>
       <c r="J107" s="4"/>
     </row>
     <row r="108">
-      <c r="A108" s="42"/>
-      <c r="F108" s="43"/>
+      <c r="A108" s="44"/>
+      <c r="F108" s="45"/>
       <c r="J108" s="4"/>
     </row>
     <row r="109">
-      <c r="A109" s="42"/>
-      <c r="F109" s="43"/>
+      <c r="A109" s="44"/>
+      <c r="F109" s="45"/>
       <c r="J109" s="4"/>
     </row>
     <row r="110">
-      <c r="A110" s="42"/>
-      <c r="F110" s="43"/>
+      <c r="A110" s="44"/>
+      <c r="F110" s="45"/>
       <c r="J110" s="4"/>
     </row>
     <row r="111">
-      <c r="A111" s="42"/>
-      <c r="F111" s="43"/>
+      <c r="A111" s="44"/>
+      <c r="F111" s="45"/>
       <c r="J111" s="4"/>
     </row>
     <row r="112">
-      <c r="A112" s="42"/>
-      <c r="F112" s="43"/>
+      <c r="A112" s="44"/>
+      <c r="F112" s="45"/>
       <c r="J112" s="4"/>
     </row>
     <row r="113">
-      <c r="A113" s="42"/>
-      <c r="F113" s="43"/>
+      <c r="A113" s="44"/>
+      <c r="F113" s="45"/>
       <c r="J113" s="4"/>
     </row>
     <row r="114">
-      <c r="A114" s="42"/>
-      <c r="F114" s="43"/>
+      <c r="A114" s="44"/>
+      <c r="F114" s="45"/>
       <c r="J114" s="4"/>
     </row>
     <row r="115">
-      <c r="A115" s="42"/>
-      <c r="F115" s="43"/>
+      <c r="A115" s="44"/>
+      <c r="F115" s="45"/>
       <c r="J115" s="4"/>
     </row>
     <row r="116">
-      <c r="A116" s="42"/>
-      <c r="F116" s="43"/>
+      <c r="A116" s="44"/>
+      <c r="F116" s="45"/>
       <c r="J116" s="4"/>
     </row>
     <row r="117">
-      <c r="A117" s="42"/>
-      <c r="F117" s="43"/>
+      <c r="A117" s="44"/>
+      <c r="F117" s="45"/>
       <c r="J117" s="4"/>
     </row>
     <row r="118">
       <c r="A118" s="4"/>
-      <c r="F118" s="43"/>
+      <c r="F118" s="45"/>
       <c r="J118" s="4"/>
     </row>
     <row r="119">
       <c r="A119" s="4"/>
-      <c r="F119" s="43"/>
+      <c r="F119" s="45"/>
       <c r="J119" s="4"/>
     </row>
     <row r="120">
       <c r="A120" s="4"/>
-      <c r="F120" s="43"/>
+      <c r="F120" s="45"/>
       <c r="J120" s="4"/>
     </row>
     <row r="121">
       <c r="A121" s="4"/>
-      <c r="F121" s="43"/>
+      <c r="F121" s="45"/>
       <c r="J121" s="4"/>
     </row>
     <row r="122">
       <c r="A122" s="4"/>
-      <c r="F122" s="43"/>
+      <c r="F122" s="45"/>
       <c r="J122" s="4"/>
     </row>
     <row r="123">
       <c r="A123" s="4"/>
-      <c r="F123" s="43"/>
+      <c r="F123" s="45"/>
       <c r="J123" s="4"/>
     </row>
     <row r="124">
       <c r="A124" s="4"/>
-      <c r="F124" s="43"/>
+      <c r="F124" s="45"/>
       <c r="J124" s="4"/>
     </row>
     <row r="125">
       <c r="A125" s="4"/>
-      <c r="F125" s="43"/>
+      <c r="F125" s="45"/>
       <c r="J125" s="4"/>
     </row>
     <row r="126">
       <c r="A126" s="4"/>
-      <c r="F126" s="43"/>
+      <c r="F126" s="45"/>
       <c r="J126" s="4"/>
     </row>
     <row r="127">
       <c r="A127" s="4"/>
-      <c r="F127" s="43"/>
+      <c r="F127" s="45"/>
       <c r="J127" s="4"/>
     </row>
     <row r="128">
       <c r="A128" s="4"/>
-      <c r="F128" s="43"/>
+      <c r="F128" s="45"/>
       <c r="J128" s="4"/>
     </row>
     <row r="129">
       <c r="A129" s="4"/>
-      <c r="F129" s="43"/>
+      <c r="F129" s="45"/>
       <c r="J129" s="4"/>
     </row>
     <row r="130">
       <c r="A130" s="4"/>
-      <c r="F130" s="43"/>
+      <c r="F130" s="45"/>
       <c r="J130" s="4"/>
     </row>
     <row r="131">
       <c r="A131" s="4"/>
-      <c r="F131" s="43"/>
+      <c r="F131" s="45"/>
       <c r="J131" s="4"/>
     </row>
     <row r="132">
       <c r="A132" s="4"/>
-      <c r="F132" s="43"/>
+      <c r="F132" s="45"/>
       <c r="J132" s="4"/>
     </row>
     <row r="133">
       <c r="A133" s="4"/>
-      <c r="F133" s="43"/>
+      <c r="F133" s="45"/>
       <c r="J133" s="4"/>
     </row>
     <row r="134">
       <c r="A134" s="4"/>
-      <c r="F134" s="43"/>
+      <c r="F134" s="45"/>
       <c r="J134" s="4"/>
     </row>
     <row r="135">
       <c r="A135" s="4"/>
-      <c r="F135" s="43"/>
+      <c r="F135" s="45"/>
       <c r="J135" s="4"/>
     </row>
     <row r="136">
       <c r="A136" s="4"/>
-      <c r="F136" s="43"/>
+      <c r="F136" s="45"/>
       <c r="J136" s="4"/>
     </row>
     <row r="137">
       <c r="A137" s="4"/>
-      <c r="F137" s="43"/>
+      <c r="F137" s="45"/>
       <c r="J137" s="4"/>
     </row>
     <row r="138">
       <c r="A138" s="4"/>
-      <c r="F138" s="43"/>
+      <c r="F138" s="45"/>
       <c r="J138" s="4"/>
     </row>
     <row r="139">
       <c r="A139" s="4"/>
-      <c r="F139" s="43"/>
+      <c r="F139" s="45"/>
       <c r="J139" s="4"/>
     </row>
     <row r="140">
       <c r="A140" s="4"/>
-      <c r="F140" s="43"/>
+      <c r="F140" s="45"/>
       <c r="J140" s="4"/>
     </row>
     <row r="141">
       <c r="A141" s="4"/>
-      <c r="F141" s="43"/>
+      <c r="F141" s="45"/>
       <c r="J141" s="4"/>
     </row>
     <row r="142">
       <c r="A142" s="4"/>
-      <c r="F142" s="43"/>
+      <c r="F142" s="45"/>
       <c r="J142" s="4"/>
     </row>
     <row r="143">
       <c r="A143" s="4"/>
-      <c r="F143" s="43"/>
+      <c r="F143" s="45"/>
       <c r="J143" s="4"/>
     </row>
     <row r="144">
       <c r="A144" s="4"/>
-      <c r="F144" s="43"/>
+      <c r="F144" s="45"/>
       <c r="J144" s="4"/>
     </row>
     <row r="145">
       <c r="A145" s="4"/>
-      <c r="F145" s="43"/>
+      <c r="F145" s="45"/>
       <c r="J145" s="4"/>
     </row>
     <row r="146">
       <c r="A146" s="4"/>
-      <c r="F146" s="43"/>
+      <c r="F146" s="45"/>
       <c r="J146" s="4"/>
     </row>
     <row r="147">
       <c r="A147" s="4"/>
-      <c r="F147" s="43"/>
+      <c r="F147" s="45"/>
       <c r="J147" s="4"/>
     </row>
     <row r="148">
       <c r="A148" s="4"/>
-      <c r="F148" s="43"/>
+      <c r="F148" s="45"/>
       <c r="J148" s="4"/>
     </row>
     <row r="149">
       <c r="A149" s="4"/>
-      <c r="F149" s="43"/>
+      <c r="F149" s="45"/>
       <c r="J149" s="4"/>
     </row>
     <row r="150">
       <c r="A150" s="4"/>
-      <c r="F150" s="43"/>
+      <c r="F150" s="45"/>
       <c r="J150" s="4"/>
     </row>
     <row r="151">
       <c r="A151" s="4"/>
-      <c r="F151" s="43"/>
+      <c r="F151" s="45"/>
       <c r="J151" s="4"/>
     </row>
     <row r="152">
       <c r="A152" s="4"/>
-      <c r="F152" s="43"/>
+      <c r="F152" s="45"/>
       <c r="J152" s="4"/>
     </row>
     <row r="153">
       <c r="A153" s="4"/>
-      <c r="F153" s="43"/>
+      <c r="F153" s="45"/>
       <c r="J153" s="4"/>
     </row>
     <row r="154">
       <c r="A154" s="4"/>
-      <c r="F154" s="43"/>
+      <c r="F154" s="45"/>
       <c r="J154" s="4"/>
     </row>
     <row r="155">
       <c r="A155" s="4"/>
-      <c r="F155" s="43"/>
+      <c r="F155" s="45"/>
       <c r="J155" s="4"/>
     </row>
     <row r="156">
       <c r="A156" s="4"/>
-      <c r="F156" s="43"/>
+      <c r="F156" s="45"/>
       <c r="J156" s="4"/>
     </row>
     <row r="157">
       <c r="A157" s="4"/>
-      <c r="F157" s="43"/>
+      <c r="F157" s="45"/>
       <c r="J157" s="4"/>
     </row>
     <row r="158">
       <c r="A158" s="4"/>
-      <c r="F158" s="43"/>
+      <c r="F158" s="45"/>
       <c r="J158" s="4"/>
     </row>
     <row r="159">
       <c r="A159" s="4"/>
-      <c r="F159" s="43"/>
+      <c r="F159" s="45"/>
       <c r="J159" s="4"/>
     </row>
     <row r="160">
       <c r="A160" s="4"/>
-      <c r="F160" s="43"/>
+      <c r="F160" s="45"/>
       <c r="J160" s="4"/>
     </row>
     <row r="161">
       <c r="A161" s="4"/>
-      <c r="F161" s="43"/>
+      <c r="F161" s="45"/>
       <c r="J161" s="4"/>
     </row>
     <row r="162">
       <c r="A162" s="4"/>
-      <c r="F162" s="43"/>
+      <c r="F162" s="45"/>
       <c r="J162" s="4"/>
     </row>
     <row r="163">
       <c r="A163" s="4"/>
-      <c r="F163" s="43"/>
+      <c r="F163" s="45"/>
       <c r="J163" s="4"/>
     </row>
     <row r="164">
       <c r="A164" s="4"/>
-      <c r="F164" s="43"/>
+      <c r="F164" s="45"/>
       <c r="J164" s="4"/>
     </row>
     <row r="165">
       <c r="A165" s="4"/>
-      <c r="F165" s="43"/>
+      <c r="F165" s="45"/>
       <c r="J165" s="4"/>
     </row>
     <row r="166">
       <c r="A166" s="4"/>
-      <c r="F166" s="43"/>
+      <c r="F166" s="45"/>
       <c r="J166" s="4"/>
     </row>
     <row r="167">
       <c r="A167" s="4"/>
-      <c r="F167" s="43"/>
+      <c r="F167" s="45"/>
       <c r="J167" s="4"/>
     </row>
     <row r="168">
       <c r="A168" s="4"/>
-      <c r="F168" s="43"/>
+      <c r="F168" s="45"/>
       <c r="J168" s="4"/>
     </row>
     <row r="169">
       <c r="A169" s="4"/>
-      <c r="F169" s="43"/>
+      <c r="F169" s="45"/>
       <c r="J169" s="4"/>
     </row>
     <row r="170">
       <c r="A170" s="4"/>
-      <c r="F170" s="43"/>
+      <c r="F170" s="45"/>
       <c r="J170" s="4"/>
     </row>
     <row r="171">
       <c r="A171" s="4"/>
-      <c r="F171" s="43"/>
+      <c r="F171" s="45"/>
       <c r="J171" s="4"/>
     </row>
     <row r="172">
       <c r="A172" s="4"/>
-      <c r="F172" s="43"/>
+      <c r="F172" s="45"/>
       <c r="J172" s="4"/>
     </row>
     <row r="173">
       <c r="A173" s="4"/>
-      <c r="F173" s="43"/>
+      <c r="F173" s="45"/>
       <c r="J173" s="4"/>
     </row>
     <row r="174">
       <c r="A174" s="4"/>
-      <c r="F174" s="43"/>
+      <c r="F174" s="45"/>
       <c r="J174" s="4"/>
     </row>
     <row r="175">
       <c r="A175" s="4"/>
-      <c r="F175" s="43"/>
+      <c r="F175" s="45"/>
       <c r="J175" s="4"/>
     </row>
     <row r="176">
       <c r="A176" s="4"/>
-      <c r="F176" s="43"/>
+      <c r="F176" s="45"/>
       <c r="J176" s="4"/>
     </row>
     <row r="177">
       <c r="A177" s="4"/>
-      <c r="F177" s="43"/>
+      <c r="F177" s="45"/>
       <c r="J177" s="4"/>
     </row>
     <row r="178">
       <c r="A178" s="4"/>
-      <c r="F178" s="43"/>
+      <c r="F178" s="45"/>
       <c r="J178" s="4"/>
     </row>
     <row r="179">
       <c r="A179" s="4"/>
-      <c r="F179" s="43"/>
+      <c r="F179" s="45"/>
       <c r="J179" s="4"/>
     </row>
     <row r="180">
       <c r="A180" s="4"/>
-      <c r="F180" s="43"/>
+      <c r="F180" s="45"/>
       <c r="J180" s="4"/>
     </row>
     <row r="181">
       <c r="A181" s="4"/>
-      <c r="F181" s="43"/>
+      <c r="F181" s="45"/>
       <c r="J181" s="4"/>
     </row>
     <row r="182">
       <c r="A182" s="4"/>
-      <c r="F182" s="43"/>
+      <c r="F182" s="45"/>
       <c r="J182" s="4"/>
     </row>
     <row r="183">
       <c r="A183" s="4"/>
-      <c r="F183" s="43"/>
+      <c r="F183" s="45"/>
       <c r="J183" s="4"/>
     </row>
     <row r="184">
       <c r="A184" s="4"/>
-      <c r="F184" s="43"/>
+      <c r="F184" s="45"/>
       <c r="J184" s="4"/>
     </row>
     <row r="185">
       <c r="A185" s="4"/>
-      <c r="F185" s="43"/>
+      <c r="F185" s="45"/>
       <c r="J185" s="4"/>
     </row>
     <row r="186">
       <c r="A186" s="4"/>
-      <c r="F186" s="43"/>
+      <c r="F186" s="45"/>
       <c r="J186" s="4"/>
     </row>
     <row r="187">
       <c r="A187" s="4"/>
-      <c r="F187" s="43"/>
+      <c r="F187" s="45"/>
       <c r="J187" s="4"/>
     </row>
     <row r="188">
       <c r="A188" s="4"/>
-      <c r="F188" s="43"/>
+      <c r="F188" s="45"/>
       <c r="J188" s="4"/>
     </row>
     <row r="189">
       <c r="A189" s="4"/>
-      <c r="F189" s="43"/>
+      <c r="F189" s="45"/>
       <c r="J189" s="4"/>
     </row>
     <row r="190">
       <c r="A190" s="4"/>
-      <c r="F190" s="43"/>
+      <c r="F190" s="45"/>
       <c r="J190" s="4"/>
     </row>
     <row r="191">
       <c r="A191" s="4"/>
-      <c r="F191" s="43"/>
+      <c r="F191" s="45"/>
       <c r="J191" s="4"/>
     </row>
     <row r="192">
       <c r="A192" s="4"/>
-      <c r="F192" s="43"/>
+      <c r="F192" s="45"/>
       <c r="J192" s="4"/>
     </row>
     <row r="193">
       <c r="A193" s="4"/>
-      <c r="F193" s="43"/>
+      <c r="F193" s="45"/>
       <c r="J193" s="4"/>
     </row>
     <row r="194">
       <c r="A194" s="4"/>
-      <c r="F194" s="43"/>
+      <c r="F194" s="45"/>
       <c r="J194" s="4"/>
     </row>
     <row r="195">
       <c r="A195" s="4"/>
-      <c r="F195" s="43"/>
+      <c r="F195" s="45"/>
       <c r="J195" s="4"/>
     </row>
     <row r="196">
       <c r="A196" s="4"/>
-      <c r="F196" s="43"/>
+      <c r="F196" s="45"/>
       <c r="J196" s="4"/>
     </row>
     <row r="197">
       <c r="A197" s="4"/>
-      <c r="F197" s="43"/>
+      <c r="F197" s="45"/>
       <c r="J197" s="4"/>
     </row>
     <row r="198">
       <c r="A198" s="4"/>
-      <c r="F198" s="43"/>
+      <c r="F198" s="45"/>
       <c r="J198" s="4"/>
     </row>
     <row r="199">
       <c r="A199" s="4"/>
-      <c r="F199" s="43"/>
+      <c r="F199" s="45"/>
       <c r="J199" s="4"/>
     </row>
     <row r="200">
       <c r="A200" s="4"/>
-      <c r="F200" s="43"/>
+      <c r="F200" s="45"/>
       <c r="J200" s="4"/>
     </row>
     <row r="201">
       <c r="A201" s="4"/>
-      <c r="F201" s="43"/>
+      <c r="F201" s="45"/>
       <c r="J201" s="4"/>
     </row>
     <row r="202">
       <c r="A202" s="4"/>
-      <c r="F202" s="43"/>
+      <c r="F202" s="45"/>
       <c r="J202" s="4"/>
     </row>
     <row r="203">
       <c r="A203" s="4"/>
-      <c r="F203" s="43"/>
+      <c r="F203" s="45"/>
       <c r="J203" s="4"/>
     </row>
     <row r="204">
       <c r="A204" s="4"/>
-      <c r="F204" s="43"/>
+      <c r="F204" s="45"/>
       <c r="J204" s="4"/>
     </row>
     <row r="205">
       <c r="A205" s="4"/>
-      <c r="F205" s="43"/>
+      <c r="F205" s="45"/>
       <c r="J205" s="4"/>
     </row>
     <row r="206">
       <c r="A206" s="4"/>
-      <c r="F206" s="43"/>
+      <c r="F206" s="45"/>
       <c r="J206" s="4"/>
     </row>
     <row r="207">
       <c r="A207" s="4"/>
-      <c r="F207" s="43"/>
+      <c r="F207" s="45"/>
       <c r="J207" s="4"/>
     </row>
     <row r="208">
       <c r="A208" s="4"/>
-      <c r="F208" s="43"/>
+      <c r="F208" s="45"/>
       <c r="J208" s="4"/>
     </row>
     <row r="209">
       <c r="A209" s="4"/>
-      <c r="F209" s="43"/>
+      <c r="F209" s="45"/>
       <c r="J209" s="4"/>
     </row>
     <row r="210">
       <c r="A210" s="4"/>
-      <c r="F210" s="43"/>
+      <c r="F210" s="45"/>
       <c r="J210" s="4"/>
     </row>
     <row r="211">
       <c r="A211" s="4"/>
-      <c r="F211" s="43"/>
+      <c r="F211" s="45"/>
       <c r="J211" s="4"/>
     </row>
     <row r="212">
       <c r="A212" s="4"/>
-      <c r="F212" s="43"/>
+      <c r="F212" s="45"/>
       <c r="J212" s="4"/>
     </row>
     <row r="213">
       <c r="A213" s="4"/>
-      <c r="F213" s="43"/>
+      <c r="F213" s="45"/>
       <c r="J213" s="4"/>
     </row>
     <row r="214">
       <c r="A214" s="4"/>
-      <c r="F214" s="43"/>
+      <c r="F214" s="45"/>
       <c r="J214" s="4"/>
     </row>
     <row r="215">
       <c r="A215" s="4"/>
-      <c r="F215" s="43"/>
+      <c r="F215" s="45"/>
       <c r="J215" s="4"/>
     </row>
     <row r="216">
       <c r="A216" s="4"/>
-      <c r="F216" s="43"/>
+      <c r="F216" s="45"/>
       <c r="J216" s="4"/>
     </row>
     <row r="217">
       <c r="A217" s="4"/>
-      <c r="F217" s="43"/>
+      <c r="F217" s="45"/>
       <c r="J217" s="4"/>
     </row>
     <row r="218">
       <c r="A218" s="4"/>
-      <c r="F218" s="43"/>
+      <c r="F218" s="45"/>
       <c r="J218" s="4"/>
     </row>
     <row r="219">
       <c r="A219" s="4"/>
-      <c r="F219" s="43"/>
+      <c r="F219" s="45"/>
       <c r="J219" s="4"/>
     </row>
     <row r="220">
       <c r="A220" s="4"/>
-      <c r="F220" s="43"/>
+      <c r="F220" s="45"/>
       <c r="J220" s="4"/>
     </row>
     <row r="221">
       <c r="A221" s="4"/>
-      <c r="F221" s="43"/>
+      <c r="F221" s="45"/>
       <c r="J221" s="4"/>
     </row>
     <row r="222">
       <c r="A222" s="4"/>
-      <c r="F222" s="43"/>
+      <c r="F222" s="45"/>
       <c r="J222" s="4"/>
     </row>
     <row r="223">
       <c r="A223" s="4"/>
-      <c r="F223" s="43"/>
+      <c r="F223" s="45"/>
       <c r="J223" s="4"/>
     </row>
     <row r="224">
       <c r="A224" s="4"/>
-      <c r="F224" s="43"/>
+      <c r="F224" s="45"/>
       <c r="J224" s="4"/>
     </row>
     <row r="225">
       <c r="A225" s="4"/>
-      <c r="F225" s="43"/>
+      <c r="F225" s="45"/>
       <c r="J225" s="4"/>
     </row>
     <row r="226">
       <c r="A226" s="4"/>
-      <c r="F226" s="43"/>
+      <c r="F226" s="45"/>
       <c r="J226" s="4"/>
     </row>
     <row r="227">
       <c r="A227" s="4"/>
-      <c r="F227" s="43"/>
+      <c r="F227" s="45"/>
       <c r="J227" s="4"/>
     </row>
     <row r="228">
       <c r="A228" s="4"/>
-      <c r="F228" s="43"/>
+      <c r="F228" s="45"/>
       <c r="J228" s="4"/>
     </row>
     <row r="229">
       <c r="A229" s="4"/>
-      <c r="F229" s="43"/>
+      <c r="F229" s="45"/>
       <c r="J229" s="4"/>
     </row>
     <row r="230">
       <c r="A230" s="4"/>
-      <c r="F230" s="43"/>
+      <c r="F230" s="45"/>
       <c r="J230" s="4"/>
     </row>
     <row r="231">
       <c r="A231" s="4"/>
-      <c r="F231" s="43"/>
+      <c r="F231" s="45"/>
       <c r="J231" s="4"/>
     </row>
     <row r="232">
       <c r="A232" s="4"/>
-      <c r="F232" s="43"/>
+      <c r="F232" s="45"/>
       <c r="J232" s="4"/>
     </row>
     <row r="233">
       <c r="A233" s="4"/>
-      <c r="F233" s="43"/>
+      <c r="F233" s="45"/>
       <c r="J233" s="4"/>
     </row>
     <row r="234">
       <c r="A234" s="4"/>
-      <c r="F234" s="43"/>
+      <c r="F234" s="45"/>
       <c r="J234" s="4"/>
     </row>
     <row r="235">
       <c r="A235" s="4"/>
-      <c r="F235" s="43"/>
+      <c r="F235" s="45"/>
       <c r="J235" s="4"/>
     </row>
     <row r="236">
       <c r="A236" s="4"/>
-      <c r="F236" s="43"/>
+      <c r="F236" s="45"/>
       <c r="J236" s="4"/>
     </row>
     <row r="237">
       <c r="A237" s="4"/>
-      <c r="F237" s="43"/>
+      <c r="F237" s="45"/>
       <c r="J237" s="4"/>
     </row>
     <row r="238">
       <c r="A238" s="4"/>
-      <c r="F238" s="43"/>
+      <c r="F238" s="45"/>
       <c r="J238" s="4"/>
     </row>
     <row r="239">
       <c r="A239" s="4"/>
-      <c r="F239" s="43"/>
+      <c r="F239" s="45"/>
       <c r="J239" s="4"/>
     </row>
     <row r="240">
       <c r="A240" s="4"/>
-      <c r="F240" s="43"/>
+      <c r="F240" s="45"/>
       <c r="J240" s="4"/>
     </row>
     <row r="241">
       <c r="A241" s="4"/>
-      <c r="F241" s="43"/>
+      <c r="F241" s="45"/>
       <c r="J241" s="4"/>
     </row>
     <row r="242">
       <c r="A242" s="4"/>
-      <c r="F242" s="43"/>
+      <c r="F242" s="45"/>
       <c r="J242" s="4"/>
     </row>
     <row r="243">
       <c r="A243" s="4"/>
-      <c r="F243" s="43"/>
+      <c r="F243" s="45"/>
       <c r="J243" s="4"/>
     </row>
     <row r="244">
       <c r="A244" s="4"/>
-      <c r="F244" s="43"/>
+      <c r="F244" s="45"/>
       <c r="J244" s="4"/>
     </row>
     <row r="245">
       <c r="A245" s="4"/>
-      <c r="F245" s="43"/>
+      <c r="F245" s="45"/>
       <c r="J245" s="4"/>
     </row>
     <row r="246">
       <c r="A246" s="4"/>
-      <c r="F246" s="43"/>
+      <c r="F246" s="45"/>
       <c r="J246" s="4"/>
     </row>
     <row r="247">
       <c r="A247" s="4"/>
-      <c r="F247" s="43"/>
+      <c r="F247" s="45"/>
       <c r="J247" s="4"/>
     </row>
     <row r="248">
       <c r="A248" s="4"/>
-      <c r="F248" s="43"/>
+      <c r="F248" s="45"/>
       <c r="J248" s="4"/>
     </row>
     <row r="249">
       <c r="A249" s="4"/>
-      <c r="F249" s="43"/>
+      <c r="F249" s="45"/>
       <c r="J249" s="4"/>
     </row>
     <row r="250">
       <c r="A250" s="4"/>
-      <c r="F250" s="43"/>
+      <c r="F250" s="45"/>
       <c r="J250" s="4"/>
     </row>
     <row r="251">
       <c r="A251" s="4"/>
-      <c r="F251" s="43"/>
+      <c r="F251" s="45"/>
       <c r="J251" s="4"/>
     </row>
     <row r="252">
       <c r="A252" s="4"/>
-      <c r="F252" s="43"/>
+      <c r="F252" s="45"/>
       <c r="J252" s="4"/>
     </row>
     <row r="253">
       <c r="A253" s="4"/>
-      <c r="F253" s="43"/>
+      <c r="F253" s="45"/>
       <c r="J253" s="4"/>
     </row>
     <row r="254">
       <c r="A254" s="4"/>
-      <c r="F254" s="43"/>
+      <c r="F254" s="45"/>
       <c r="J254" s="4"/>
     </row>
     <row r="255">
       <c r="A255" s="4"/>
-      <c r="F255" s="43"/>
+      <c r="F255" s="45"/>
       <c r="J255" s="4"/>
     </row>
     <row r="256">
       <c r="A256" s="4"/>
-      <c r="F256" s="43"/>
+      <c r="F256" s="45"/>
       <c r="J256" s="4"/>
     </row>
     <row r="257">
       <c r="A257" s="4"/>
-      <c r="F257" s="43"/>
+      <c r="F257" s="45"/>
       <c r="J257" s="4"/>
     </row>
     <row r="258">
       <c r="A258" s="4"/>
-      <c r="F258" s="43"/>
+      <c r="F258" s="45"/>
       <c r="J258" s="4"/>
     </row>
     <row r="259">
       <c r="A259" s="4"/>
-      <c r="F259" s="43"/>
+      <c r="F259" s="45"/>
       <c r="J259" s="4"/>
     </row>
     <row r="260">
       <c r="A260" s="4"/>
-      <c r="F260" s="43"/>
+      <c r="F260" s="45"/>
       <c r="J260" s="4"/>
     </row>
     <row r="261">
       <c r="A261" s="4"/>
-      <c r="F261" s="43"/>
+      <c r="F261" s="45"/>
       <c r="J261" s="4"/>
     </row>
     <row r="262">
       <c r="A262" s="4"/>
-      <c r="F262" s="43"/>
+      <c r="F262" s="45"/>
       <c r="J262" s="4"/>
     </row>
     <row r="263">
       <c r="A263" s="4"/>
-      <c r="F263" s="43"/>
+      <c r="F263" s="45"/>
       <c r="J263" s="4"/>
     </row>
     <row r="264">
       <c r="A264" s="4"/>
-      <c r="F264" s="43"/>
+      <c r="F264" s="45"/>
       <c r="J264" s="4"/>
     </row>
     <row r="265">
       <c r="A265" s="4"/>
-      <c r="F265" s="43"/>
+      <c r="F265" s="45"/>
       <c r="J265" s="4"/>
     </row>
     <row r="266">
       <c r="A266" s="4"/>
-      <c r="F266" s="43"/>
+      <c r="F266" s="45"/>
       <c r="J266" s="4"/>
     </row>
     <row r="267">
       <c r="A267" s="4"/>
-      <c r="F267" s="43"/>
+      <c r="F267" s="45"/>
       <c r="J267" s="4"/>
     </row>
     <row r="268">
       <c r="A268" s="4"/>
-      <c r="F268" s="43"/>
+      <c r="F268" s="45"/>
       <c r="J268" s="4"/>
     </row>
     <row r="269">
       <c r="A269" s="4"/>
-      <c r="F269" s="43"/>
+      <c r="F269" s="45"/>
       <c r="J269" s="4"/>
     </row>
     <row r="270">
       <c r="A270" s="4"/>
-      <c r="F270" s="43"/>
+      <c r="F270" s="45"/>
       <c r="J270" s="4"/>
     </row>
     <row r="271">
       <c r="A271" s="4"/>
-      <c r="F271" s="43"/>
+      <c r="F271" s="45"/>
       <c r="J271" s="4"/>
     </row>
     <row r="272">
       <c r="A272" s="4"/>
-      <c r="F272" s="43"/>
+      <c r="F272" s="45"/>
       <c r="J272" s="4"/>
     </row>
     <row r="273">
       <c r="A273" s="4"/>
-      <c r="F273" s="43"/>
+      <c r="F273" s="45"/>
       <c r="J273" s="4"/>
     </row>
     <row r="274">
       <c r="A274" s="4"/>
-      <c r="F274" s="43"/>
+      <c r="F274" s="45"/>
       <c r="J274" s="4"/>
     </row>
     <row r="275">
       <c r="A275" s="4"/>
-      <c r="F275" s="43"/>
+      <c r="F275" s="45"/>
       <c r="J275" s="4"/>
     </row>
     <row r="276">
       <c r="A276" s="4"/>
-      <c r="F276" s="43"/>
+      <c r="F276" s="45"/>
       <c r="J276" s="4"/>
     </row>
     <row r="277">
       <c r="A277" s="4"/>
-      <c r="F277" s="43"/>
+      <c r="F277" s="45"/>
       <c r="J277" s="4"/>
     </row>
     <row r="278">
       <c r="A278" s="4"/>
-      <c r="F278" s="43"/>
+      <c r="F278" s="45"/>
       <c r="J278" s="4"/>
     </row>
     <row r="279">
       <c r="A279" s="4"/>
-      <c r="F279" s="43"/>
+      <c r="F279" s="45"/>
       <c r="J279" s="4"/>
     </row>
     <row r="280">
       <c r="A280" s="4"/>
-      <c r="F280" s="43"/>
+      <c r="F280" s="45"/>
       <c r="J280" s="4"/>
     </row>
     <row r="281">
       <c r="A281" s="4"/>
-      <c r="F281" s="43"/>
+      <c r="F281" s="45"/>
       <c r="J281" s="4"/>
     </row>
     <row r="282">
       <c r="A282" s="4"/>
-      <c r="F282" s="43"/>
+      <c r="F282" s="45"/>
       <c r="J282" s="4"/>
     </row>
     <row r="283">
       <c r="A283" s="4"/>
-      <c r="F283" s="43"/>
+      <c r="F283" s="45"/>
       <c r="J283" s="4"/>
     </row>
     <row r="284">
       <c r="A284" s="4"/>
-      <c r="F284" s="43"/>
+      <c r="F284" s="45"/>
       <c r="J284" s="4"/>
     </row>
     <row r="285">
       <c r="A285" s="4"/>
-      <c r="F285" s="43"/>
+      <c r="F285" s="45"/>
       <c r="J285" s="4"/>
     </row>
     <row r="286">
       <c r="A286" s="4"/>
-      <c r="F286" s="43"/>
+      <c r="F286" s="45"/>
       <c r="J286" s="4"/>
     </row>
     <row r="287">
       <c r="A287" s="4"/>
-      <c r="F287" s="43"/>
+      <c r="F287" s="45"/>
       <c r="J287" s="4"/>
     </row>
     <row r="288">
       <c r="A288" s="4"/>
-      <c r="F288" s="43"/>
+      <c r="F288" s="45"/>
       <c r="J288" s="4"/>
     </row>
     <row r="289">
       <c r="A289" s="4"/>
-      <c r="F289" s="43"/>
+      <c r="F289" s="45"/>
       <c r="J289" s="4"/>
     </row>
     <row r="290">
       <c r="A290" s="4"/>
-      <c r="F290" s="43"/>
+      <c r="F290" s="45"/>
       <c r="J290" s="4"/>
     </row>
     <row r="291">
       <c r="A291" s="4"/>
-      <c r="F291" s="43"/>
+      <c r="F291" s="45"/>
       <c r="J291" s="4"/>
     </row>
     <row r="292">
       <c r="A292" s="4"/>
-      <c r="F292" s="43"/>
+      <c r="F292" s="45"/>
       <c r="J292" s="4"/>
     </row>
     <row r="293">
       <c r="A293" s="4"/>
-      <c r="F293" s="43"/>
+      <c r="F293" s="45"/>
       <c r="J293" s="4"/>
     </row>
     <row r="294">
       <c r="A294" s="4"/>
-      <c r="F294" s="43"/>
+      <c r="F294" s="45"/>
       <c r="J294" s="4"/>
     </row>
     <row r="295">
       <c r="A295" s="4"/>
-      <c r="F295" s="43"/>
+      <c r="F295" s="45"/>
       <c r="J295" s="4"/>
     </row>
     <row r="296">
       <c r="A296" s="4"/>
-      <c r="F296" s="43"/>
+      <c r="F296" s="45"/>
       <c r="J296" s="4"/>
     </row>
     <row r="297">
       <c r="A297" s="4"/>
-      <c r="F297" s="43"/>
+      <c r="F297" s="45"/>
       <c r="J297" s="4"/>
     </row>
     <row r="298">
       <c r="A298" s="4"/>
-      <c r="F298" s="43"/>
+      <c r="F298" s="45"/>
       <c r="J298" s="4"/>
     </row>
     <row r="299">
       <c r="A299" s="4"/>
-      <c r="F299" s="43"/>
+      <c r="F299" s="45"/>
       <c r="J299" s="4"/>
     </row>
     <row r="300">
       <c r="A300" s="4"/>
-      <c r="F300" s="43"/>
+      <c r="F300" s="45"/>
       <c r="J300" s="4"/>
     </row>
     <row r="301">
       <c r="A301" s="4"/>
-      <c r="F301" s="43"/>
+      <c r="F301" s="45"/>
       <c r="J301" s="4"/>
     </row>
     <row r="302">
       <c r="A302" s="4"/>
-      <c r="F302" s="43"/>
+      <c r="F302" s="45"/>
       <c r="J302" s="4"/>
     </row>
     <row r="303">
       <c r="A303" s="4"/>
-      <c r="F303" s="43"/>
+      <c r="F303" s="45"/>
       <c r="J303" s="4"/>
     </row>
     <row r="304">
       <c r="A304" s="4"/>
-      <c r="F304" s="43"/>
+      <c r="F304" s="45"/>
       <c r="J304" s="4"/>
     </row>
     <row r="305">
       <c r="A305" s="4"/>
-      <c r="F305" s="43"/>
+      <c r="F305" s="45"/>
       <c r="J305" s="4"/>
     </row>
     <row r="306">
       <c r="A306" s="4"/>
-      <c r="F306" s="43"/>
+      <c r="F306" s="45"/>
       <c r="J306" s="4"/>
     </row>
     <row r="307">
       <c r="A307" s="4"/>
-      <c r="F307" s="43"/>
+      <c r="F307" s="45"/>
       <c r="J307" s="4"/>
     </row>
     <row r="308">
       <c r="A308" s="4"/>
-      <c r="F308" s="43"/>
+      <c r="F308" s="45"/>
       <c r="J308" s="4"/>
     </row>
     <row r="309">
       <c r="A309" s="4"/>
-      <c r="F309" s="43"/>
+      <c r="F309" s="45"/>
       <c r="J309" s="4"/>
     </row>
     <row r="310">
       <c r="A310" s="4"/>
-      <c r="F310" s="43"/>
+      <c r="F310" s="45"/>
       <c r="J310" s="4"/>
     </row>
     <row r="311">
       <c r="A311" s="4"/>
-      <c r="F311" s="43"/>
+      <c r="F311" s="45"/>
       <c r="J311" s="4"/>
     </row>
     <row r="312">
       <c r="A312" s="4"/>
-      <c r="F312" s="43"/>
+      <c r="F312" s="45"/>
       <c r="J312" s="4"/>
     </row>
     <row r="313">
       <c r="A313" s="4"/>
-      <c r="F313" s="43"/>
+      <c r="F313" s="45"/>
       <c r="J313" s="4"/>
     </row>
     <row r="314">
       <c r="A314" s="4"/>
-      <c r="F314" s="43"/>
+      <c r="F314" s="45"/>
       <c r="J314" s="4"/>
     </row>
     <row r="315">
       <c r="A315" s="4"/>
-      <c r="F315" s="43"/>
+      <c r="F315" s="45"/>
       <c r="J315" s="4"/>
     </row>
     <row r="316">
       <c r="A316" s="4"/>
-      <c r="F316" s="43"/>
+      <c r="F316" s="45"/>
       <c r="J316" s="4"/>
     </row>
     <row r="317">
       <c r="A317" s="4"/>
-      <c r="F317" s="43"/>
+      <c r="F317" s="45"/>
       <c r="J317" s="4"/>
     </row>
     <row r="318">
       <c r="A318" s="4"/>
-      <c r="F318" s="43"/>
+      <c r="F318" s="45"/>
       <c r="J318" s="4"/>
     </row>
     <row r="319">
       <c r="A319" s="4"/>
-      <c r="F319" s="43"/>
+      <c r="F319" s="45"/>
       <c r="J319" s="4"/>
     </row>
     <row r="320">
       <c r="A320" s="4"/>
-      <c r="F320" s="43"/>
+      <c r="F320" s="45"/>
       <c r="J320" s="4"/>
     </row>
     <row r="321">
       <c r="A321" s="4"/>
-      <c r="F321" s="43"/>
+      <c r="F321" s="45"/>
       <c r="J321" s="4"/>
     </row>
     <row r="322">
       <c r="A322" s="4"/>
-      <c r="F322" s="43"/>
+      <c r="F322" s="45"/>
       <c r="J322" s="4"/>
     </row>
     <row r="323">
       <c r="A323" s="4"/>
-      <c r="F323" s="43"/>
+      <c r="F323" s="45"/>
       <c r="J323" s="4"/>
     </row>
     <row r="324">
       <c r="A324" s="4"/>
-      <c r="F324" s="43"/>
+      <c r="F324" s="45"/>
       <c r="J324" s="4"/>
     </row>
     <row r="325">
       <c r="A325" s="4"/>
-      <c r="F325" s="43"/>
+      <c r="F325" s="45"/>
       <c r="J325" s="4"/>
     </row>
     <row r="326">
       <c r="A326" s="4"/>
-      <c r="F326" s="43"/>
+      <c r="F326" s="45"/>
       <c r="J326" s="4"/>
     </row>
     <row r="327">
       <c r="A327" s="4"/>
-      <c r="F327" s="43"/>
+      <c r="F327" s="45"/>
       <c r="J327" s="4"/>
     </row>
     <row r="328">
       <c r="A328" s="4"/>
-      <c r="F328" s="43"/>
+      <c r="F328" s="45"/>
       <c r="J328" s="4"/>
     </row>
     <row r="329">
       <c r="A329" s="4"/>
-      <c r="F329" s="43"/>
+      <c r="F329" s="45"/>
       <c r="J329" s="4"/>
     </row>
     <row r="330">
       <c r="A330" s="4"/>
-      <c r="F330" s="43"/>
+      <c r="F330" s="45"/>
       <c r="J330" s="4"/>
     </row>
     <row r="331">
       <c r="A331" s="4"/>
-      <c r="F331" s="43"/>
+      <c r="F331" s="45"/>
       <c r="J331" s="4"/>
     </row>
     <row r="332">
       <c r="A332" s="4"/>
-      <c r="F332" s="43"/>
+      <c r="F332" s="45"/>
       <c r="J332" s="4"/>
     </row>
     <row r="333">
       <c r="A333" s="4"/>
-      <c r="F333" s="43"/>
+      <c r="F333" s="45"/>
       <c r="J333" s="4"/>
     </row>
     <row r="334">
       <c r="A334" s="4"/>
-      <c r="F334" s="43"/>
+      <c r="F334" s="45"/>
       <c r="J334" s="4"/>
     </row>
     <row r="335">
       <c r="A335" s="4"/>
-      <c r="F335" s="43"/>
+      <c r="F335" s="45"/>
       <c r="J335" s="4"/>
     </row>
     <row r="336">
       <c r="A336" s="4"/>
-      <c r="F336" s="43"/>
+      <c r="F336" s="45"/>
       <c r="J336" s="4"/>
     </row>
     <row r="337">
       <c r="A337" s="4"/>
-      <c r="F337" s="43"/>
+      <c r="F337" s="45"/>
       <c r="J337" s="4"/>
     </row>
     <row r="338">
       <c r="A338" s="4"/>
-      <c r="F338" s="43"/>
+      <c r="F338" s="45"/>
       <c r="J338" s="4"/>
     </row>
     <row r="339">
       <c r="A339" s="4"/>
-      <c r="F339" s="43"/>
+      <c r="F339" s="45"/>
       <c r="J339" s="4"/>
     </row>
     <row r="340">
       <c r="A340" s="4"/>
-      <c r="F340" s="43"/>
+      <c r="F340" s="45"/>
       <c r="J340" s="4"/>
     </row>
     <row r="341">
       <c r="A341" s="4"/>
-      <c r="F341" s="43"/>
+      <c r="F341" s="45"/>
       <c r="J341" s="4"/>
     </row>
     <row r="342">
       <c r="A342" s="4"/>
-      <c r="F342" s="43"/>
+      <c r="F342" s="45"/>
       <c r="J342" s="4"/>
     </row>
     <row r="343">
       <c r="A343" s="4"/>
-      <c r="F343" s="43"/>
+      <c r="F343" s="45"/>
       <c r="J343" s="4"/>
     </row>
     <row r="344">
       <c r="A344" s="4"/>
-      <c r="F344" s="43"/>
+      <c r="F344" s="45"/>
       <c r="J344" s="4"/>
     </row>
     <row r="345">
       <c r="A345" s="4"/>
-      <c r="F345" s="43"/>
+      <c r="F345" s="45"/>
       <c r="J345" s="4"/>
     </row>
     <row r="346">
       <c r="A346" s="4"/>
-      <c r="F346" s="43"/>
+      <c r="F346" s="45"/>
       <c r="J346" s="4"/>
     </row>
     <row r="347">
       <c r="A347" s="4"/>
-      <c r="F347" s="43"/>
+      <c r="F347" s="45"/>
       <c r="J347" s="4"/>
     </row>
     <row r="348">
       <c r="A348" s="4"/>
-      <c r="F348" s="43"/>
+      <c r="F348" s="45"/>
       <c r="J348" s="4"/>
     </row>
     <row r="349">
       <c r="A349" s="4"/>
-      <c r="F349" s="43"/>
+      <c r="F349" s="45"/>
       <c r="J349" s="4"/>
     </row>
     <row r="350">
       <c r="A350" s="4"/>
-      <c r="F350" s="43"/>
+      <c r="F350" s="45"/>
       <c r="J350" s="4"/>
     </row>
     <row r="351">
       <c r="A351" s="4"/>
-      <c r="F351" s="43"/>
+      <c r="F351" s="45"/>
       <c r="J351" s="4"/>
     </row>
     <row r="352">
       <c r="A352" s="4"/>
-      <c r="F352" s="43"/>
+      <c r="F352" s="45"/>
       <c r="J352" s="4"/>
     </row>
     <row r="353">
       <c r="A353" s="4"/>
-      <c r="F353" s="43"/>
+      <c r="F353" s="45"/>
       <c r="J353" s="4"/>
     </row>
     <row r="354">
       <c r="A354" s="4"/>
-      <c r="F354" s="43"/>
+      <c r="F354" s="45"/>
       <c r="J354" s="4"/>
     </row>
     <row r="355">
       <c r="A355" s="4"/>
-      <c r="F355" s="43"/>
+      <c r="F355" s="45"/>
       <c r="J355" s="4"/>
     </row>
     <row r="356">
       <c r="A356" s="4"/>
-      <c r="F356" s="43"/>
+      <c r="F356" s="45"/>
       <c r="J356" s="4"/>
     </row>
     <row r="357">
       <c r="A357" s="4"/>
-      <c r="F357" s="43"/>
+      <c r="F357" s="45"/>
       <c r="J357" s="4"/>
     </row>
     <row r="358">
       <c r="A358" s="4"/>
-      <c r="F358" s="43"/>
+      <c r="F358" s="45"/>
       <c r="J358" s="4"/>
     </row>
     <row r="359">
       <c r="A359" s="4"/>
-      <c r="F359" s="43"/>
+      <c r="F359" s="45"/>
       <c r="J359" s="4"/>
     </row>
     <row r="360">
       <c r="A360" s="4"/>
-      <c r="F360" s="43"/>
+      <c r="F360" s="45"/>
       <c r="J360" s="4"/>
     </row>
     <row r="361">
       <c r="A361" s="4"/>
-      <c r="F361" s="43"/>
+      <c r="F361" s="45"/>
       <c r="J361" s="4"/>
     </row>
     <row r="362">
       <c r="A362" s="4"/>
-      <c r="F362" s="43"/>
+      <c r="F362" s="45"/>
       <c r="J362" s="4"/>
     </row>
     <row r="363">
       <c r="A363" s="4"/>
-      <c r="F363" s="43"/>
+      <c r="F363" s="45"/>
       <c r="J363" s="4"/>
     </row>
     <row r="364">
       <c r="A364" s="4"/>
-      <c r="F364" s="43"/>
+      <c r="F364" s="45"/>
       <c r="J364" s="4"/>
     </row>
     <row r="365">
       <c r="A365" s="4"/>
-      <c r="F365" s="43"/>
+      <c r="F365" s="45"/>
       <c r="J365" s="4"/>
     </row>
     <row r="366">
       <c r="A366" s="4"/>
-      <c r="F366" s="43"/>
+      <c r="F366" s="45"/>
       <c r="J366" s="4"/>
     </row>
     <row r="367">
       <c r="A367" s="4"/>
-      <c r="F367" s="43"/>
+      <c r="F367" s="45"/>
       <c r="J367" s="4"/>
     </row>
     <row r="368">
       <c r="A368" s="4"/>
-      <c r="F368" s="43"/>
+      <c r="F368" s="45"/>
       <c r="J368" s="4"/>
     </row>
     <row r="369">
       <c r="A369" s="4"/>
-      <c r="F369" s="43"/>
+      <c r="F369" s="45"/>
       <c r="J369" s="4"/>
     </row>
     <row r="370">
       <c r="A370" s="4"/>
-      <c r="F370" s="43"/>
+      <c r="F370" s="45"/>
       <c r="J370" s="4"/>
     </row>
     <row r="371">
       <c r="A371" s="4"/>
-      <c r="F371" s="43"/>
+      <c r="F371" s="45"/>
       <c r="J371" s="4"/>
     </row>
     <row r="372">
       <c r="A372" s="4"/>
-      <c r="F372" s="43"/>
+      <c r="F372" s="45"/>
       <c r="J372" s="4"/>
     </row>
     <row r="373">
       <c r="A373" s="4"/>
-      <c r="F373" s="43"/>
+      <c r="F373" s="45"/>
       <c r="J373" s="4"/>
     </row>
     <row r="374">
       <c r="A374" s="4"/>
-      <c r="F374" s="43"/>
+      <c r="F374" s="45"/>
       <c r="J374" s="4"/>
     </row>
     <row r="375">
       <c r="A375" s="4"/>
-      <c r="F375" s="43"/>
+      <c r="F375" s="45"/>
       <c r="J375" s="4"/>
     </row>
     <row r="376">
       <c r="A376" s="4"/>
-      <c r="F376" s="43"/>
+      <c r="F376" s="45"/>
       <c r="J376" s="4"/>
     </row>
     <row r="377">
       <c r="A377" s="4"/>
-      <c r="F377" s="43"/>
+      <c r="F377" s="45"/>
       <c r="J377" s="4"/>
     </row>
     <row r="378">
       <c r="A378" s="4"/>
-      <c r="F378" s="43"/>
+      <c r="F378" s="45"/>
       <c r="J378" s="4"/>
     </row>
     <row r="379">
       <c r="A379" s="4"/>
-      <c r="F379" s="43"/>
+      <c r="F379" s="45"/>
       <c r="J379" s="4"/>
     </row>
     <row r="380">
       <c r="A380" s="4"/>
-      <c r="F380" s="43"/>
+      <c r="F380" s="45"/>
       <c r="J380" s="4"/>
     </row>
     <row r="381">
       <c r="A381" s="4"/>
-      <c r="F381" s="43"/>
+      <c r="F381" s="45"/>
       <c r="J381" s="4"/>
     </row>
     <row r="382">
       <c r="A382" s="4"/>
-      <c r="F382" s="43"/>
+      <c r="F382" s="45"/>
       <c r="J382" s="4"/>
     </row>
     <row r="383">
       <c r="A383" s="4"/>
-      <c r="F383" s="43"/>
+      <c r="F383" s="45"/>
       <c r="J383" s="4"/>
     </row>
     <row r="384">
       <c r="A384" s="4"/>
-      <c r="F384" s="43"/>
+      <c r="F384" s="45"/>
       <c r="J384" s="4"/>
     </row>
     <row r="385">
       <c r="A385" s="4"/>
-      <c r="F385" s="43"/>
+      <c r="F385" s="45"/>
       <c r="J385" s="4"/>
     </row>
     <row r="386">
       <c r="A386" s="4"/>
-      <c r="F386" s="43"/>
+      <c r="F386" s="45"/>
       <c r="J386" s="4"/>
     </row>
     <row r="387">
       <c r="A387" s="4"/>
-      <c r="F387" s="43"/>
+      <c r="F387" s="45"/>
       <c r="J387" s="4"/>
     </row>
     <row r="388">
       <c r="A388" s="4"/>
-      <c r="F388" s="43"/>
+      <c r="F388" s="45"/>
       <c r="J388" s="4"/>
     </row>
     <row r="389">
       <c r="A389" s="4"/>
-      <c r="F389" s="43"/>
+      <c r="F389" s="45"/>
       <c r="J389" s="4"/>
     </row>
     <row r="390">
       <c r="A390" s="4"/>
-      <c r="F390" s="43"/>
+      <c r="F390" s="45"/>
       <c r="J390" s="4"/>
     </row>
     <row r="391">
       <c r="A391" s="4"/>
-      <c r="F391" s="43"/>
+      <c r="F391" s="45"/>
       <c r="J391" s="4"/>
     </row>
     <row r="392">
       <c r="A392" s="4"/>
-      <c r="F392" s="43"/>
+      <c r="F392" s="45"/>
       <c r="J392" s="4"/>
     </row>
     <row r="393">
       <c r="A393" s="4"/>
-      <c r="F393" s="43"/>
+      <c r="F393" s="45"/>
       <c r="J393" s="4"/>
     </row>
     <row r="394">
       <c r="A394" s="4"/>
-      <c r="F394" s="43"/>
+      <c r="F394" s="45"/>
       <c r="J394" s="4"/>
     </row>
     <row r="395">
       <c r="A395" s="4"/>
-      <c r="F395" s="43"/>
+      <c r="F395" s="45"/>
       <c r="J395" s="4"/>
     </row>
     <row r="396">
       <c r="A396" s="4"/>
-      <c r="F396" s="43"/>
+      <c r="F396" s="45"/>
       <c r="J396" s="4"/>
     </row>
     <row r="397">
       <c r="A397" s="4"/>
-      <c r="F397" s="43"/>
+      <c r="F397" s="45"/>
       <c r="J397" s="4"/>
     </row>
     <row r="398">
       <c r="A398" s="4"/>
-      <c r="F398" s="43"/>
+      <c r="F398" s="45"/>
       <c r="J398" s="4"/>
     </row>
     <row r="399">
       <c r="A399" s="4"/>
-      <c r="F399" s="43"/>
+      <c r="F399" s="45"/>
       <c r="J399" s="4"/>
     </row>
     <row r="400">
       <c r="A400" s="4"/>
-      <c r="F400" s="43"/>
+      <c r="F400" s="45"/>
       <c r="J400" s="4"/>
     </row>
     <row r="401">
       <c r="A401" s="4"/>
-      <c r="F401" s="43"/>
+      <c r="F401" s="45"/>
       <c r="J401" s="4"/>
     </row>
     <row r="402">
       <c r="A402" s="4"/>
-      <c r="F402" s="43"/>
+      <c r="F402" s="45"/>
       <c r="J402" s="4"/>
     </row>
     <row r="403">
       <c r="A403" s="4"/>
-      <c r="F403" s="43"/>
+      <c r="F403" s="45"/>
       <c r="J403" s="4"/>
     </row>
     <row r="404">
       <c r="A404" s="4"/>
-      <c r="F404" s="43"/>
+      <c r="F404" s="45"/>
       <c r="J404" s="4"/>
     </row>
     <row r="405">
       <c r="A405" s="4"/>
-      <c r="F405" s="43"/>
+      <c r="F405" s="45"/>
       <c r="J405" s="4"/>
     </row>
     <row r="406">
       <c r="A406" s="4"/>
-      <c r="F406" s="43"/>
+      <c r="F406" s="45"/>
       <c r="J406" s="4"/>
     </row>
     <row r="407">
       <c r="A407" s="4"/>
-      <c r="F407" s="43"/>
+      <c r="F407" s="45"/>
       <c r="J407" s="4"/>
     </row>
     <row r="408">
       <c r="A408" s="4"/>
-      <c r="F408" s="43"/>
+      <c r="F408" s="45"/>
       <c r="J408" s="4"/>
     </row>
     <row r="409">
       <c r="A409" s="4"/>
-      <c r="F409" s="43"/>
+      <c r="F409" s="45"/>
       <c r="J409" s="4"/>
     </row>
     <row r="410">
       <c r="A410" s="4"/>
-      <c r="F410" s="43"/>
+      <c r="F410" s="45"/>
       <c r="J410" s="4"/>
     </row>
     <row r="411">
       <c r="A411" s="4"/>
-      <c r="F411" s="43"/>
+      <c r="F411" s="45"/>
       <c r="J411" s="4"/>
     </row>
     <row r="412">
       <c r="A412" s="4"/>
-      <c r="F412" s="43"/>
+      <c r="F412" s="45"/>
       <c r="J412" s="4"/>
     </row>
     <row r="413">
       <c r="A413" s="4"/>
-      <c r="F413" s="43"/>
+      <c r="F413" s="45"/>
       <c r="J413" s="4"/>
     </row>
     <row r="414">
       <c r="A414" s="4"/>
-      <c r="F414" s="43"/>
+      <c r="F414" s="45"/>
       <c r="J414" s="4"/>
     </row>
     <row r="415">
       <c r="A415" s="4"/>
-      <c r="F415" s="43"/>
+      <c r="F415" s="45"/>
       <c r="J415" s="4"/>
     </row>
     <row r="416">
       <c r="A416" s="4"/>
-      <c r="F416" s="43"/>
+      <c r="F416" s="45"/>
       <c r="J416" s="4"/>
     </row>
     <row r="417">
       <c r="A417" s="4"/>
-      <c r="F417" s="43"/>
+      <c r="F417" s="45"/>
       <c r="J417" s="4"/>
     </row>
     <row r="418">
       <c r="A418" s="4"/>
-      <c r="F418" s="43"/>
+      <c r="F418" s="45"/>
       <c r="J418" s="4"/>
     </row>
     <row r="419">
       <c r="A419" s="4"/>
-      <c r="F419" s="43"/>
+      <c r="F419" s="45"/>
       <c r="J419" s="4"/>
     </row>
     <row r="420">
       <c r="A420" s="4"/>
-      <c r="F420" s="43"/>
+      <c r="F420" s="45"/>
       <c r="J420" s="4"/>
     </row>
     <row r="421">
       <c r="A421" s="4"/>
-      <c r="F421" s="43"/>
+      <c r="F421" s="45"/>
       <c r="J421" s="4"/>
     </row>
     <row r="422">
       <c r="A422" s="4"/>
-      <c r="F422" s="43"/>
+      <c r="F422" s="45"/>
       <c r="J422" s="4"/>
     </row>
     <row r="423">
       <c r="A423" s="4"/>
-      <c r="F423" s="43"/>
+      <c r="F423" s="45"/>
       <c r="J423" s="4"/>
     </row>
     <row r="424">
       <c r="A424" s="4"/>
-      <c r="F424" s="43"/>
+      <c r="F424" s="45"/>
       <c r="J424" s="4"/>
     </row>
     <row r="425">
       <c r="A425" s="4"/>
-      <c r="F425" s="43"/>
+      <c r="F425" s="45"/>
       <c r="J425" s="4"/>
     </row>
     <row r="426">
       <c r="A426" s="4"/>
-      <c r="F426" s="43"/>
+      <c r="F426" s="45"/>
       <c r="J426" s="4"/>
     </row>
     <row r="427">
       <c r="A427" s="4"/>
-      <c r="F427" s="43"/>
+      <c r="F427" s="45"/>
       <c r="J427" s="4"/>
     </row>
     <row r="428">
       <c r="A428" s="4"/>
-      <c r="F428" s="43"/>
+      <c r="F428" s="45"/>
       <c r="J428" s="4"/>
     </row>
     <row r="429">
       <c r="A429" s="4"/>
-      <c r="F429" s="43"/>
+      <c r="F429" s="45"/>
       <c r="J429" s="4"/>
     </row>
     <row r="430">
       <c r="A430" s="4"/>
-      <c r="F430" s="43"/>
+      <c r="F430" s="45"/>
       <c r="J430" s="4"/>
     </row>
     <row r="431">
       <c r="A431" s="4"/>
-      <c r="F431" s="43"/>
+      <c r="F431" s="45"/>
       <c r="J431" s="4"/>
     </row>
     <row r="432">
       <c r="A432" s="4"/>
-      <c r="F432" s="43"/>
+      <c r="F432" s="45"/>
       <c r="J432" s="4"/>
     </row>
     <row r="433">
       <c r="A433" s="4"/>
-      <c r="F433" s="43"/>
+      <c r="F433" s="45"/>
       <c r="J433" s="4"/>
     </row>
     <row r="434">
       <c r="A434" s="4"/>
-      <c r="F434" s="43"/>
+      <c r="F434" s="45"/>
       <c r="J434" s="4"/>
     </row>
     <row r="435">
       <c r="A435" s="4"/>
-      <c r="F435" s="43"/>
+      <c r="F435" s="45"/>
       <c r="J435" s="4"/>
     </row>
     <row r="436">
       <c r="A436" s="4"/>
-      <c r="F436" s="43"/>
+      <c r="F436" s="45"/>
       <c r="J436" s="4"/>
     </row>
     <row r="437">
       <c r="A437" s="4"/>
-      <c r="F437" s="43"/>
+      <c r="F437" s="45"/>
       <c r="J437" s="4"/>
     </row>
     <row r="438">
       <c r="A438" s="4"/>
-      <c r="F438" s="43"/>
+      <c r="F438" s="45"/>
       <c r="J438" s="4"/>
     </row>
     <row r="439">
       <c r="A439" s="4"/>
-      <c r="F439" s="43"/>
+      <c r="F439" s="45"/>
       <c r="J439" s="4"/>
     </row>
     <row r="440">
       <c r="A440" s="4"/>
-      <c r="F440" s="43"/>
+      <c r="F440" s="45"/>
       <c r="J440" s="4"/>
     </row>
     <row r="441">
       <c r="A441" s="4"/>
-      <c r="F441" s="43"/>
+      <c r="F441" s="45"/>
       <c r="J441" s="4"/>
     </row>
     <row r="442">
       <c r="A442" s="4"/>
-      <c r="F442" s="43"/>
+      <c r="F442" s="45"/>
       <c r="J442" s="4"/>
     </row>
     <row r="443">
       <c r="A443" s="4"/>
-      <c r="F443" s="43"/>
+      <c r="F443" s="45"/>
       <c r="J443" s="4"/>
     </row>
     <row r="444">
       <c r="A444" s="4"/>
-      <c r="F444" s="43"/>
+      <c r="F444" s="45"/>
       <c r="J444" s="4"/>
     </row>
     <row r="445">
       <c r="A445" s="4"/>
-      <c r="F445" s="43"/>
+      <c r="F445" s="45"/>
       <c r="J445" s="4"/>
     </row>
     <row r="446">
       <c r="A446" s="4"/>
-      <c r="F446" s="43"/>
+      <c r="F446" s="45"/>
       <c r="J446" s="4"/>
     </row>
     <row r="447">
       <c r="A447" s="4"/>
-      <c r="F447" s="43"/>
+      <c r="F447" s="45"/>
       <c r="J447" s="4"/>
     </row>
     <row r="448">
       <c r="A448" s="4"/>
-      <c r="F448" s="43"/>
+      <c r="F448" s="45"/>
       <c r="J448" s="4"/>
     </row>
     <row r="449">
       <c r="A449" s="4"/>
-      <c r="F449" s="43"/>
+      <c r="F449" s="45"/>
       <c r="J449" s="4"/>
     </row>
     <row r="450">
       <c r="A450" s="4"/>
-      <c r="F450" s="43"/>
+      <c r="F450" s="45"/>
       <c r="J450" s="4"/>
     </row>
     <row r="451">
       <c r="A451" s="4"/>
-      <c r="F451" s="43"/>
+      <c r="F451" s="45"/>
       <c r="J451" s="4"/>
     </row>
     <row r="452">
       <c r="A452" s="4"/>
-      <c r="F452" s="43"/>
+      <c r="F452" s="45"/>
       <c r="J452" s="4"/>
     </row>
     <row r="453">
       <c r="A453" s="4"/>
-      <c r="F453" s="43"/>
+      <c r="F453" s="45"/>
       <c r="J453" s="4"/>
     </row>
     <row r="454">
       <c r="A454" s="4"/>
-      <c r="F454" s="43"/>
+      <c r="F454" s="45"/>
       <c r="J454" s="4"/>
     </row>
     <row r="455">
       <c r="A455" s="4"/>
-      <c r="F455" s="43"/>
+      <c r="F455" s="45"/>
       <c r="J455" s="4"/>
     </row>
     <row r="456">
       <c r="A456" s="4"/>
-      <c r="F456" s="43"/>
+      <c r="F456" s="45"/>
       <c r="J456" s="4"/>
     </row>
     <row r="457">
       <c r="A457" s="4"/>
-      <c r="F457" s="43"/>
+      <c r="F457" s="45"/>
       <c r="J457" s="4"/>
     </row>
     <row r="458">
       <c r="A458" s="4"/>
-      <c r="F458" s="43"/>
+      <c r="F458" s="45"/>
       <c r="J458" s="4"/>
     </row>
     <row r="459">
       <c r="A459" s="4"/>
-      <c r="F459" s="43"/>
+      <c r="F459" s="45"/>
       <c r="J459" s="4"/>
     </row>
     <row r="460">
       <c r="A460" s="4"/>
-      <c r="F460" s="43"/>
+      <c r="F460" s="45"/>
       <c r="J460" s="4"/>
     </row>
     <row r="461">
       <c r="A461" s="4"/>
-      <c r="F461" s="43"/>
+      <c r="F461" s="45"/>
       <c r="J461" s="4"/>
     </row>
     <row r="462">
       <c r="A462" s="4"/>
-      <c r="F462" s="43"/>
+      <c r="F462" s="45"/>
       <c r="J462" s="4"/>
     </row>
     <row r="463">
       <c r="A463" s="4"/>
-      <c r="F463" s="43"/>
+      <c r="F463" s="45"/>
       <c r="J463" s="4"/>
     </row>
     <row r="464">
       <c r="A464" s="4"/>
-      <c r="F464" s="43"/>
+      <c r="F464" s="45"/>
       <c r="J464" s="4"/>
     </row>
     <row r="465">
       <c r="A465" s="4"/>
-      <c r="F465" s="43"/>
+      <c r="F465" s="45"/>
       <c r="J465" s="4"/>
     </row>
     <row r="466">
       <c r="A466" s="4"/>
-      <c r="F466" s="43"/>
+      <c r="F466" s="45"/>
       <c r="J466" s="4"/>
     </row>
     <row r="467">
       <c r="A467" s="4"/>
-      <c r="F467" s="43"/>
+      <c r="F467" s="45"/>
       <c r="J467" s="4"/>
     </row>
     <row r="468">
       <c r="A468" s="4"/>
-      <c r="F468" s="43"/>
+      <c r="F468" s="45"/>
       <c r="J468" s="4"/>
     </row>
     <row r="469">
       <c r="A469" s="4"/>
-      <c r="F469" s="43"/>
+      <c r="F469" s="45"/>
       <c r="J469" s="4"/>
     </row>
     <row r="470">
       <c r="A470" s="4"/>
-      <c r="F470" s="43"/>
+      <c r="F470" s="45"/>
       <c r="J470" s="4"/>
     </row>
     <row r="471">
       <c r="A471" s="4"/>
-      <c r="F471" s="43"/>
+      <c r="F471" s="45"/>
       <c r="J471" s="4"/>
     </row>
     <row r="472">
       <c r="A472" s="4"/>
-      <c r="F472" s="43"/>
+      <c r="F472" s="45"/>
       <c r="J472" s="4"/>
     </row>
     <row r="473">
       <c r="A473" s="4"/>
-      <c r="F473" s="43"/>
+      <c r="F473" s="45"/>
       <c r="J473" s="4"/>
     </row>
     <row r="474">
       <c r="A474" s="4"/>
-      <c r="F474" s="43"/>
+      <c r="F474" s="45"/>
       <c r="J474" s="4"/>
     </row>
     <row r="475">
       <c r="A475" s="4"/>
-      <c r="F475" s="43"/>
+      <c r="F475" s="45"/>
       <c r="J475" s="4"/>
     </row>
     <row r="476">
       <c r="A476" s="4"/>
-      <c r="F476" s="43"/>
+      <c r="F476" s="45"/>
       <c r="J476" s="4"/>
     </row>
     <row r="477">
       <c r="A477" s="4"/>
-      <c r="F477" s="43"/>
+      <c r="F477" s="45"/>
       <c r="J477" s="4"/>
     </row>
     <row r="478">
       <c r="A478" s="4"/>
-      <c r="F478" s="43"/>
+      <c r="F478" s="45"/>
       <c r="J478" s="4"/>
     </row>
     <row r="479">
       <c r="A479" s="4"/>
-      <c r="F479" s="43"/>
+      <c r="F479" s="45"/>
       <c r="J479" s="4"/>
     </row>
     <row r="480">
       <c r="A480" s="4"/>
-      <c r="F480" s="43"/>
+      <c r="F480" s="45"/>
       <c r="J480" s="4"/>
     </row>
     <row r="481">
       <c r="A481" s="4"/>
-      <c r="F481" s="43"/>
+      <c r="F481" s="45"/>
       <c r="J481" s="4"/>
     </row>
     <row r="482">
       <c r="A482" s="4"/>
-      <c r="F482" s="43"/>
+      <c r="F482" s="45"/>
       <c r="J482" s="4"/>
     </row>
     <row r="483">
       <c r="A483" s="4"/>
-      <c r="F483" s="43"/>
+      <c r="F483" s="45"/>
       <c r="J483" s="4"/>
     </row>
     <row r="484">
       <c r="A484" s="4"/>
-      <c r="F484" s="43"/>
+      <c r="F484" s="45"/>
       <c r="J484" s="4"/>
     </row>
     <row r="485">
       <c r="A485" s="4"/>
-      <c r="F485" s="43"/>
+      <c r="F485" s="45"/>
       <c r="J485" s="4"/>
     </row>
     <row r="486">
       <c r="A486" s="4"/>
-      <c r="F486" s="43"/>
+      <c r="F486" s="45"/>
       <c r="J486" s="4"/>
     </row>
     <row r="487">
       <c r="A487" s="4"/>
-      <c r="F487" s="43"/>
+      <c r="F487" s="45"/>
       <c r="J487" s="4"/>
     </row>
     <row r="488">
       <c r="A488" s="4"/>
-      <c r="F488" s="43"/>
+      <c r="F488" s="45"/>
       <c r="J488" s="4"/>
     </row>
     <row r="489">
       <c r="A489" s="4"/>
-      <c r="F489" s="43"/>
+      <c r="F489" s="45"/>
       <c r="J489" s="4"/>
     </row>
     <row r="490">
       <c r="A490" s="4"/>
-      <c r="F490" s="43"/>
+      <c r="F490" s="45"/>
       <c r="J490" s="4"/>
     </row>
     <row r="491">
       <c r="A491" s="4"/>
-      <c r="F491" s="43"/>
+      <c r="F491" s="45"/>
       <c r="J491" s="4"/>
     </row>
     <row r="492">
       <c r="A492" s="4"/>
-      <c r="F492" s="43"/>
+      <c r="F492" s="45"/>
       <c r="J492" s="4"/>
     </row>
     <row r="493">
       <c r="A493" s="4"/>
-      <c r="F493" s="43"/>
+      <c r="F493" s="45"/>
       <c r="J493" s="4"/>
     </row>
     <row r="494">
       <c r="A494" s="4"/>
-      <c r="F494" s="43"/>
+      <c r="F494" s="45"/>
       <c r="J494" s="4"/>
     </row>
     <row r="495">
       <c r="A495" s="4"/>
-      <c r="F495" s="43"/>
+      <c r="F495" s="45"/>
       <c r="J495" s="4"/>
     </row>
     <row r="496">
       <c r="A496" s="4"/>
-      <c r="F496" s="43"/>
+      <c r="F496" s="45"/>
       <c r="J496" s="4"/>
     </row>
     <row r="497">
       <c r="A497" s="4"/>
-      <c r="F497" s="43"/>
+      <c r="F497" s="45"/>
       <c r="J497" s="4"/>
     </row>
     <row r="498">
       <c r="A498" s="4"/>
-      <c r="F498" s="43"/>
+      <c r="F498" s="45"/>
       <c r="J498" s="4"/>
     </row>
     <row r="499">
       <c r="A499" s="4"/>
-      <c r="F499" s="43"/>
+      <c r="F499" s="45"/>
       <c r="J499" s="4"/>
     </row>
     <row r="500">
       <c r="A500" s="4"/>
-      <c r="F500" s="43"/>
+      <c r="F500" s="45"/>
       <c r="J500" s="4"/>
     </row>
     <row r="501">
       <c r="A501" s="4"/>
-      <c r="F501" s="43"/>
+      <c r="F501" s="45"/>
       <c r="J501" s="4"/>
     </row>
     <row r="502">
       <c r="A502" s="4"/>
-      <c r="F502" s="43"/>
+      <c r="F502" s="45"/>
       <c r="J502" s="4"/>
     </row>
     <row r="503">
       <c r="A503" s="4"/>
-      <c r="F503" s="43"/>
+      <c r="F503" s="45"/>
       <c r="J503" s="4"/>
     </row>
     <row r="504">
       <c r="A504" s="4"/>
-      <c r="F504" s="43"/>
+      <c r="F504" s="45"/>
       <c r="J504" s="4"/>
     </row>
     <row r="505">
       <c r="A505" s="4"/>
-      <c r="F505" s="43"/>
+      <c r="F505" s="45"/>
       <c r="J505" s="4"/>
     </row>
     <row r="506">
       <c r="A506" s="4"/>
-      <c r="F506" s="43"/>
+      <c r="F506" s="45"/>
       <c r="J506" s="4"/>
     </row>
     <row r="507">
       <c r="A507" s="4"/>
-      <c r="F507" s="43"/>
+      <c r="F507" s="45"/>
       <c r="J507" s="4"/>
     </row>
     <row r="508">
       <c r="A508" s="4"/>
-      <c r="F508" s="43"/>
+      <c r="F508" s="45"/>
       <c r="J508" s="4"/>
     </row>
     <row r="509">
       <c r="A509" s="4"/>
-      <c r="F509" s="43"/>
+      <c r="F509" s="45"/>
       <c r="J509" s="4"/>
     </row>
     <row r="510">
       <c r="A510" s="4"/>
-      <c r="F510" s="43"/>
+      <c r="F510" s="45"/>
       <c r="J510" s="4"/>
     </row>
     <row r="511">
       <c r="A511" s="4"/>
-      <c r="F511" s="43"/>
+      <c r="F511" s="45"/>
       <c r="J511" s="4"/>
     </row>
     <row r="512">
       <c r="A512" s="4"/>
-      <c r="F512" s="43"/>
+      <c r="F512" s="45"/>
       <c r="J512" s="4"/>
     </row>
     <row r="513">
       <c r="A513" s="4"/>
-      <c r="F513" s="43"/>
+      <c r="F513" s="45"/>
       <c r="J513" s="4"/>
     </row>
     <row r="514">
       <c r="A514" s="4"/>
-      <c r="F514" s="43"/>
+      <c r="F514" s="45"/>
       <c r="J514" s="4"/>
     </row>
     <row r="515">
       <c r="A515" s="4"/>
-      <c r="F515" s="43"/>
+      <c r="F515" s="45"/>
       <c r="J515" s="4"/>
     </row>
     <row r="516">
       <c r="A516" s="4"/>
-      <c r="F516" s="43"/>
+      <c r="F516" s="45"/>
       <c r="J516" s="4"/>
     </row>
     <row r="517">
       <c r="A517" s="4"/>
-      <c r="F517" s="43"/>
+      <c r="F517" s="45"/>
       <c r="J517" s="4"/>
     </row>
     <row r="518">
       <c r="A518" s="4"/>
-      <c r="F518" s="43"/>
+      <c r="F518" s="45"/>
       <c r="J518" s="4"/>
     </row>
     <row r="519">
       <c r="A519" s="4"/>
-      <c r="F519" s="43"/>
+      <c r="F519" s="45"/>
       <c r="J519" s="4"/>
     </row>
     <row r="520">
       <c r="A520" s="4"/>
-      <c r="F520" s="43"/>
+      <c r="F520" s="45"/>
       <c r="J520" s="4"/>
     </row>
     <row r="521">
       <c r="A521" s="4"/>
-      <c r="F521" s="43"/>
+      <c r="F521" s="45"/>
       <c r="J521" s="4"/>
     </row>
     <row r="522">
       <c r="A522" s="4"/>
-      <c r="F522" s="43"/>
+      <c r="F522" s="45"/>
       <c r="J522" s="4"/>
     </row>
     <row r="523">
       <c r="A523" s="4"/>
-      <c r="F523" s="43"/>
+      <c r="F523" s="45"/>
       <c r="J523" s="4"/>
     </row>
     <row r="524">
       <c r="A524" s="4"/>
-      <c r="F524" s="43"/>
+      <c r="F524" s="45"/>
       <c r="J524" s="4"/>
     </row>
     <row r="525">
       <c r="A525" s="4"/>
-      <c r="F525" s="43"/>
+      <c r="F525" s="45"/>
       <c r="J525" s="4"/>
     </row>
     <row r="526">
       <c r="A526" s="4"/>
-      <c r="F526" s="43"/>
+      <c r="F526" s="45"/>
       <c r="J526" s="4"/>
     </row>
     <row r="527">
       <c r="A527" s="4"/>
-      <c r="F527" s="43"/>
+      <c r="F527" s="45"/>
       <c r="J527" s="4"/>
     </row>
     <row r="528">
       <c r="A528" s="4"/>
-      <c r="F528" s="43"/>
+      <c r="F528" s="45"/>
       <c r="J528" s="4"/>
     </row>
     <row r="529">
       <c r="A529" s="4"/>
-      <c r="F529" s="43"/>
+      <c r="F529" s="45"/>
       <c r="J529" s="4"/>
     </row>
     <row r="530">
       <c r="A530" s="4"/>
-      <c r="F530" s="43"/>
+      <c r="F530" s="45"/>
       <c r="J530" s="4"/>
     </row>
     <row r="531">
       <c r="A531" s="4"/>
-      <c r="F531" s="43"/>
+      <c r="F531" s="45"/>
       <c r="J531" s="4"/>
     </row>
     <row r="532">
       <c r="A532" s="4"/>
-      <c r="F532" s="43"/>
+      <c r="F532" s="45"/>
       <c r="J532" s="4"/>
     </row>
     <row r="533">
       <c r="A533" s="4"/>
-      <c r="F533" s="43"/>
+      <c r="F533" s="45"/>
       <c r="J533" s="4"/>
     </row>
     <row r="534">
       <c r="A534" s="4"/>
-      <c r="F534" s="43"/>
+      <c r="F534" s="45"/>
       <c r="J534" s="4"/>
     </row>
     <row r="535">
       <c r="A535" s="4"/>
-      <c r="F535" s="43"/>
+      <c r="F535" s="45"/>
       <c r="J535" s="4"/>
     </row>
     <row r="536">
       <c r="A536" s="4"/>
-      <c r="F536" s="43"/>
+      <c r="F536" s="45"/>
       <c r="J536" s="4"/>
     </row>
     <row r="537">
       <c r="A537" s="4"/>
-      <c r="F537" s="43"/>
+      <c r="F537" s="45"/>
       <c r="J537" s="4"/>
     </row>
     <row r="538">
       <c r="A538" s="4"/>
-      <c r="F538" s="43"/>
+      <c r="F538" s="45"/>
       <c r="J538" s="4"/>
     </row>
     <row r="539">
       <c r="A539" s="4"/>
-      <c r="F539" s="43"/>
+      <c r="F539" s="45"/>
       <c r="J539" s="4"/>
     </row>
     <row r="540">
       <c r="A540" s="4"/>
-      <c r="F540" s="43"/>
+      <c r="F540" s="45"/>
       <c r="J540" s="4"/>
     </row>
     <row r="541">
       <c r="A541" s="4"/>
-      <c r="F541" s="43"/>
+      <c r="F541" s="45"/>
       <c r="J541" s="4"/>
     </row>
     <row r="542">
       <c r="A542" s="4"/>
-      <c r="F542" s="43"/>
+      <c r="F542" s="45"/>
       <c r="J542" s="4"/>
     </row>
     <row r="543">
       <c r="A543" s="4"/>
-      <c r="F543" s="43"/>
+      <c r="F543" s="45"/>
       <c r="J543" s="4"/>
     </row>
     <row r="544">
       <c r="A544" s="4"/>
-      <c r="F544" s="43"/>
+      <c r="F544" s="45"/>
       <c r="J544" s="4"/>
     </row>
     <row r="545">
       <c r="A545" s="4"/>
-      <c r="F545" s="43"/>
+      <c r="F545" s="45"/>
       <c r="J545" s="4"/>
     </row>
     <row r="546">
       <c r="A546" s="4"/>
-      <c r="F546" s="43"/>
+      <c r="F546" s="45"/>
       <c r="J546" s="4"/>
     </row>
     <row r="547">
       <c r="A547" s="4"/>
-      <c r="F547" s="43"/>
+      <c r="F547" s="45"/>
       <c r="J547" s="4"/>
     </row>
     <row r="548">
       <c r="A548" s="4"/>
-      <c r="F548" s="43"/>
+      <c r="F548" s="45"/>
       <c r="J548" s="4"/>
     </row>
     <row r="549">
       <c r="A549" s="4"/>
-      <c r="F549" s="43"/>
+      <c r="F549" s="45"/>
       <c r="J549" s="4"/>
     </row>
     <row r="550">
       <c r="A550" s="4"/>
-      <c r="F550" s="43"/>
+      <c r="F550" s="45"/>
       <c r="J550" s="4"/>
     </row>
     <row r="551">
       <c r="A551" s="4"/>
-      <c r="F551" s="43"/>
+      <c r="F551" s="45"/>
       <c r="J551" s="4"/>
     </row>
     <row r="552">
       <c r="A552" s="4"/>
-      <c r="F552" s="43"/>
+      <c r="F552" s="45"/>
       <c r="J552" s="4"/>
     </row>
     <row r="553">
       <c r="A553" s="4"/>
-      <c r="F553" s="43"/>
+      <c r="F553" s="45"/>
       <c r="J553" s="4"/>
     </row>
     <row r="554">
       <c r="A554" s="4"/>
-      <c r="F554" s="43"/>
+      <c r="F554" s="45"/>
       <c r="J554" s="4"/>
     </row>
     <row r="555">
       <c r="A555" s="4"/>
-      <c r="F555" s="43"/>
+      <c r="F555" s="45"/>
       <c r="J555" s="4"/>
     </row>
     <row r="556">
       <c r="A556" s="4"/>
-      <c r="F556" s="43"/>
+      <c r="F556" s="45"/>
       <c r="J556" s="4"/>
     </row>
     <row r="557">
       <c r="A557" s="4"/>
-      <c r="F557" s="43"/>
+      <c r="F557" s="45"/>
       <c r="J557" s="4"/>
     </row>
     <row r="558">
       <c r="A558" s="4"/>
-      <c r="F558" s="43"/>
+      <c r="F558" s="45"/>
       <c r="J558" s="4"/>
     </row>
     <row r="559">
       <c r="A559" s="4"/>
-      <c r="F559" s="43"/>
+      <c r="F559" s="45"/>
       <c r="J559" s="4"/>
     </row>
     <row r="560">
       <c r="A560" s="4"/>
-      <c r="F560" s="43"/>
+      <c r="F560" s="45"/>
       <c r="J560" s="4"/>
     </row>
     <row r="561">
       <c r="A561" s="4"/>
-      <c r="F561" s="43"/>
+      <c r="F561" s="45"/>
       <c r="J561" s="4"/>
     </row>
     <row r="562">
       <c r="A562" s="4"/>
-      <c r="F562" s="43"/>
+      <c r="F562" s="45"/>
       <c r="J562" s="4"/>
     </row>
     <row r="563">
       <c r="A563" s="4"/>
-      <c r="F563" s="43"/>
+      <c r="F563" s="45"/>
       <c r="J563" s="4"/>
     </row>
     <row r="564">
       <c r="A564" s="4"/>
-      <c r="F564" s="43"/>
+      <c r="F564" s="45"/>
       <c r="J564" s="4"/>
     </row>
     <row r="565">
       <c r="A565" s="4"/>
-      <c r="F565" s="43"/>
+      <c r="F565" s="45"/>
       <c r="J565" s="4"/>
     </row>
     <row r="566">
       <c r="A566" s="4"/>
-      <c r="F566" s="43"/>
+      <c r="F566" s="45"/>
       <c r="J566" s="4"/>
     </row>
     <row r="567">
       <c r="A567" s="4"/>
-      <c r="F567" s="43"/>
+      <c r="F567" s="45"/>
       <c r="J567" s="4"/>
     </row>
     <row r="568">
       <c r="A568" s="4"/>
-      <c r="F568" s="43"/>
+      <c r="F568" s="45"/>
       <c r="J568" s="4"/>
     </row>
     <row r="569">
       <c r="A569" s="4"/>
-      <c r="F569" s="43"/>
+      <c r="F569" s="45"/>
       <c r="J569" s="4"/>
     </row>
     <row r="570">
       <c r="A570" s="4"/>
-      <c r="F570" s="43"/>
+      <c r="F570" s="45"/>
       <c r="J570" s="4"/>
     </row>
     <row r="571">
       <c r="A571" s="4"/>
-      <c r="F571" s="43"/>
+      <c r="F571" s="45"/>
       <c r="J571" s="4"/>
     </row>
     <row r="572">
       <c r="A572" s="4"/>
-      <c r="F572" s="43"/>
+      <c r="F572" s="45"/>
       <c r="J572" s="4"/>
     </row>
     <row r="573">
       <c r="A573" s="4"/>
-      <c r="F573" s="43"/>
+      <c r="F573" s="45"/>
       <c r="J573" s="4"/>
     </row>
     <row r="574">
       <c r="A574" s="4"/>
-      <c r="F574" s="43"/>
+      <c r="F574" s="45"/>
       <c r="J574" s="4"/>
     </row>
     <row r="575">
       <c r="A575" s="4"/>
-      <c r="F575" s="43"/>
+      <c r="F575" s="45"/>
       <c r="J575" s="4"/>
     </row>
     <row r="576">
       <c r="A576" s="4"/>
-      <c r="F576" s="43"/>
+      <c r="F576" s="45"/>
       <c r="J576" s="4"/>
     </row>
     <row r="577">
       <c r="A577" s="4"/>
-      <c r="F577" s="43"/>
+      <c r="F577" s="45"/>
       <c r="J577" s="4"/>
     </row>
     <row r="578">
       <c r="A578" s="4"/>
-      <c r="F578" s="43"/>
+      <c r="F578" s="45"/>
       <c r="J578" s="4"/>
     </row>
     <row r="579">
       <c r="A579" s="4"/>
-      <c r="F579" s="43"/>
+      <c r="F579" s="45"/>
       <c r="J579" s="4"/>
     </row>
     <row r="580">
       <c r="A580" s="4"/>
-      <c r="F580" s="43"/>
+      <c r="F580" s="45"/>
       <c r="J580" s="4"/>
     </row>
     <row r="581">
       <c r="A581" s="4"/>
-      <c r="F581" s="43"/>
+      <c r="F581" s="45"/>
       <c r="J581" s="4"/>
     </row>
     <row r="582">
       <c r="A582" s="4"/>
-      <c r="F582" s="43"/>
+      <c r="F582" s="45"/>
       <c r="J582" s="4"/>
     </row>
     <row r="583">
       <c r="A583" s="4"/>
-      <c r="F583" s="43"/>
+      <c r="F583" s="45"/>
       <c r="J583" s="4"/>
     </row>
     <row r="584">
       <c r="A584" s="4"/>
-      <c r="F584" s="43"/>
+      <c r="F584" s="45"/>
       <c r="J584" s="4"/>
     </row>
     <row r="585">
       <c r="A585" s="4"/>
-      <c r="F585" s="43"/>
+      <c r="F585" s="45"/>
       <c r="J585" s="4"/>
     </row>
     <row r="586">
       <c r="A586" s="4"/>
-      <c r="F586" s="43"/>
+      <c r="F586" s="45"/>
       <c r="J586" s="4"/>
     </row>
     <row r="587">
       <c r="A587" s="4"/>
-      <c r="F587" s="43"/>
+      <c r="F587" s="45"/>
       <c r="J587" s="4"/>
     </row>
     <row r="588">
       <c r="A588" s="4"/>
-      <c r="F588" s="43"/>
+      <c r="F588" s="45"/>
       <c r="J588" s="4"/>
     </row>
     <row r="589">
       <c r="A589" s="4"/>
-      <c r="F589" s="43"/>
+      <c r="F589" s="45"/>
       <c r="J589" s="4"/>
     </row>
     <row r="590">
       <c r="A590" s="4"/>
-      <c r="F590" s="43"/>
+      <c r="F590" s="45"/>
       <c r="J590" s="4"/>
     </row>
     <row r="591">
       <c r="A591" s="4"/>
-      <c r="F591" s="43"/>
+      <c r="F591" s="45"/>
       <c r="J591" s="4"/>
     </row>
     <row r="592">
       <c r="A592" s="4"/>
-      <c r="F592" s="43"/>
+      <c r="F592" s="45"/>
       <c r="J592" s="4"/>
     </row>
     <row r="593">
       <c r="A593" s="4"/>
-      <c r="F593" s="43"/>
+      <c r="F593" s="45"/>
       <c r="J593" s="4"/>
     </row>
     <row r="594">
       <c r="A594" s="4"/>
-      <c r="F594" s="43"/>
+      <c r="F594" s="45"/>
       <c r="J594" s="4"/>
     </row>
     <row r="595">
       <c r="A595" s="4"/>
-      <c r="F595" s="43"/>
+      <c r="F595" s="45"/>
       <c r="J595" s="4"/>
     </row>
     <row r="596">
       <c r="A596" s="4"/>
-      <c r="F596" s="43"/>
+      <c r="F596" s="45"/>
       <c r="J596" s="4"/>
     </row>
     <row r="597">
       <c r="A597" s="4"/>
-      <c r="F597" s="43"/>
+      <c r="F597" s="45"/>
       <c r="J597" s="4"/>
     </row>
     <row r="598">
       <c r="A598" s="4"/>
-      <c r="F598" s="43"/>
+      <c r="F598" s="45"/>
       <c r="J598" s="4"/>
     </row>
     <row r="599">
       <c r="A599" s="4"/>
-      <c r="F599" s="43"/>
+      <c r="F599" s="45"/>
       <c r="J599" s="4"/>
     </row>
     <row r="600">
       <c r="A600" s="4"/>
-      <c r="F600" s="43"/>
+      <c r="F600" s="45"/>
       <c r="J600" s="4"/>
     </row>
     <row r="601">
       <c r="A601" s="4"/>
-      <c r="F601" s="43"/>
+      <c r="F601" s="45"/>
       <c r="J601" s="4"/>
     </row>
     <row r="602">
       <c r="A602" s="4"/>
-      <c r="F602" s="43"/>
+      <c r="F602" s="45"/>
       <c r="J602" s="4"/>
     </row>
     <row r="603">
       <c r="A603" s="4"/>
-      <c r="F603" s="43"/>
+      <c r="F603" s="45"/>
       <c r="J603" s="4"/>
     </row>
     <row r="604">
       <c r="A604" s="4"/>
-      <c r="F604" s="43"/>
+      <c r="F604" s="45"/>
       <c r="J604" s="4"/>
     </row>
     <row r="605">
       <c r="A605" s="4"/>
-      <c r="F605" s="43"/>
+      <c r="F605" s="45"/>
       <c r="J605" s="4"/>
     </row>
     <row r="606">
       <c r="A606" s="4"/>
-      <c r="F606" s="43"/>
+      <c r="F606" s="45"/>
       <c r="J606" s="4"/>
     </row>
     <row r="607">
       <c r="A607" s="4"/>
-      <c r="F607" s="43"/>
+      <c r="F607" s="45"/>
       <c r="J607" s="4"/>
     </row>
     <row r="608">
       <c r="A608" s="4"/>
-      <c r="F608" s="43"/>
+      <c r="F608" s="45"/>
       <c r="J608" s="4"/>
     </row>
     <row r="609">
       <c r="A609" s="4"/>
-      <c r="F609" s="43"/>
+      <c r="F609" s="45"/>
       <c r="J609" s="4"/>
     </row>
     <row r="610">
       <c r="A610" s="4"/>
-      <c r="F610" s="43"/>
+      <c r="F610" s="45"/>
       <c r="J610" s="4"/>
     </row>
     <row r="611">
       <c r="A611" s="4"/>
-      <c r="F611" s="43"/>
+      <c r="F611" s="45"/>
       <c r="J611" s="4"/>
     </row>
     <row r="612">
       <c r="A612" s="4"/>
-      <c r="F612" s="43"/>
+      <c r="F612" s="45"/>
       <c r="J612" s="4"/>
     </row>
     <row r="613">
       <c r="A613" s="4"/>
-      <c r="F613" s="43"/>
+      <c r="F613" s="45"/>
       <c r="J613" s="4"/>
     </row>
     <row r="614">
       <c r="A614" s="4"/>
-      <c r="F614" s="43"/>
+      <c r="F614" s="45"/>
       <c r="J614" s="4"/>
     </row>
     <row r="615">
       <c r="A615" s="4"/>
-      <c r="F615" s="43"/>
+      <c r="F615" s="45"/>
       <c r="J615" s="4"/>
     </row>
     <row r="616">
       <c r="A616" s="4"/>
-      <c r="F616" s="43"/>
+      <c r="F616" s="45"/>
       <c r="J616" s="4"/>
     </row>
     <row r="617">
       <c r="A617" s="4"/>
-      <c r="F617" s="43"/>
+      <c r="F617" s="45"/>
       <c r="J617" s="4"/>
     </row>
     <row r="618">
       <c r="A618" s="4"/>
-      <c r="F618" s="43"/>
+      <c r="F618" s="45"/>
       <c r="J618" s="4"/>
     </row>
     <row r="619">
       <c r="A619" s="4"/>
-      <c r="F619" s="43"/>
+      <c r="F619" s="45"/>
       <c r="J619" s="4"/>
     </row>
     <row r="620">
       <c r="A620" s="4"/>
-      <c r="F620" s="43"/>
+      <c r="F620" s="45"/>
       <c r="J620" s="4"/>
     </row>
     <row r="621">
       <c r="A621" s="4"/>
-      <c r="F621" s="43"/>
+      <c r="F621" s="45"/>
       <c r="J621" s="4"/>
     </row>
     <row r="622">
       <c r="A622" s="4"/>
-      <c r="F622" s="43"/>
+      <c r="F622" s="45"/>
       <c r="J622" s="4"/>
     </row>
     <row r="623">
       <c r="A623" s="4"/>
-      <c r="F623" s="43"/>
+      <c r="F623" s="45"/>
       <c r="J623" s="4"/>
     </row>
     <row r="624">
       <c r="A624" s="4"/>
-      <c r="F624" s="43"/>
+      <c r="F624" s="45"/>
       <c r="J624" s="4"/>
     </row>
     <row r="625">
       <c r="A625" s="4"/>
-      <c r="F625" s="43"/>
+      <c r="F625" s="45"/>
       <c r="J625" s="4"/>
     </row>
     <row r="626">
       <c r="A626" s="4"/>
-      <c r="F626" s="43"/>
+      <c r="F626" s="45"/>
       <c r="J626" s="4"/>
     </row>
     <row r="627">
       <c r="A627" s="4"/>
-      <c r="F627" s="43"/>
+      <c r="F627" s="45"/>
       <c r="J627" s="4"/>
     </row>
     <row r="628">
       <c r="A628" s="4"/>
-      <c r="F628" s="43"/>
+      <c r="F628" s="45"/>
       <c r="J628" s="4"/>
     </row>
     <row r="629">
       <c r="A629" s="4"/>
-      <c r="F629" s="43"/>
+      <c r="F629" s="45"/>
       <c r="J629" s="4"/>
     </row>
     <row r="630">
       <c r="A630" s="4"/>
-      <c r="F630" s="43"/>
+      <c r="F630" s="45"/>
       <c r="J630" s="4"/>
     </row>
     <row r="631">
       <c r="A631" s="4"/>
-      <c r="F631" s="43"/>
+      <c r="F631" s="45"/>
       <c r="J631" s="4"/>
     </row>
     <row r="632">
       <c r="A632" s="4"/>
-      <c r="F632" s="43"/>
+      <c r="F632" s="45"/>
       <c r="J632" s="4"/>
     </row>
     <row r="633">
       <c r="A633" s="4"/>
-      <c r="F633" s="43"/>
+      <c r="F633" s="45"/>
       <c r="J633" s="4"/>
     </row>
     <row r="634">
       <c r="A634" s="4"/>
-      <c r="F634" s="43"/>
+      <c r="F634" s="45"/>
       <c r="J634" s="4"/>
     </row>
     <row r="635">
       <c r="A635" s="4"/>
-      <c r="F635" s="43"/>
+      <c r="F635" s="45"/>
       <c r="J635" s="4"/>
     </row>
     <row r="636">
       <c r="A636" s="4"/>
-      <c r="F636" s="43"/>
+      <c r="F636" s="45"/>
       <c r="J636" s="4"/>
     </row>
     <row r="637">
       <c r="A637" s="4"/>
-      <c r="F637" s="43"/>
+      <c r="F637" s="45"/>
       <c r="J637" s="4"/>
     </row>
     <row r="638">
       <c r="A638" s="4"/>
-      <c r="F638" s="43"/>
+      <c r="F638" s="45"/>
       <c r="J638" s="4"/>
     </row>
     <row r="639">
       <c r="A639" s="4"/>
-      <c r="F639" s="43"/>
+      <c r="F639" s="45"/>
       <c r="J639" s="4"/>
     </row>
     <row r="640">
       <c r="A640" s="4"/>
-      <c r="F640" s="43"/>
+      <c r="F640" s="45"/>
       <c r="J640" s="4"/>
     </row>
     <row r="641">
       <c r="A641" s="4"/>
-      <c r="F641" s="43"/>
+      <c r="F641" s="45"/>
       <c r="J641" s="4"/>
     </row>
     <row r="642">
       <c r="A642" s="4"/>
-      <c r="F642" s="43"/>
+      <c r="F642" s="45"/>
       <c r="J642" s="4"/>
     </row>
     <row r="643">
       <c r="A643" s="4"/>
-      <c r="F643" s="43"/>
+      <c r="F643" s="45"/>
       <c r="J643" s="4"/>
     </row>
     <row r="644">
       <c r="A644" s="4"/>
-      <c r="F644" s="43"/>
+      <c r="F644" s="45"/>
       <c r="J644" s="4"/>
     </row>
     <row r="645">
       <c r="A645" s="4"/>
-      <c r="F645" s="43"/>
+      <c r="F645" s="45"/>
       <c r="J645" s="4"/>
     </row>
     <row r="646">
       <c r="A646" s="4"/>
-      <c r="F646" s="43"/>
+      <c r="F646" s="45"/>
       <c r="J646" s="4"/>
     </row>
     <row r="647">
       <c r="A647" s="4"/>
-      <c r="F647" s="43"/>
+      <c r="F647" s="45"/>
       <c r="J647" s="4"/>
     </row>
     <row r="648">
       <c r="A648" s="4"/>
-      <c r="F648" s="43"/>
+      <c r="F648" s="45"/>
       <c r="J648" s="4"/>
     </row>
     <row r="649">
       <c r="A649" s="4"/>
-      <c r="F649" s="43"/>
+      <c r="F649" s="45"/>
       <c r="J649" s="4"/>
     </row>
     <row r="650">
       <c r="A650" s="4"/>
-      <c r="F650" s="43"/>
+      <c r="F650" s="45"/>
       <c r="J650" s="4"/>
     </row>
     <row r="651">
       <c r="A651" s="4"/>
-      <c r="F651" s="43"/>
+      <c r="F651" s="45"/>
       <c r="J651" s="4"/>
     </row>
     <row r="652">
       <c r="A652" s="4"/>
-      <c r="F652" s="43"/>
+      <c r="F652" s="45"/>
       <c r="J652" s="4"/>
     </row>
     <row r="653">
       <c r="A653" s="4"/>
-      <c r="F653" s="43"/>
+      <c r="F653" s="45"/>
       <c r="J653" s="4"/>
     </row>
     <row r="654">
       <c r="A654" s="4"/>
-      <c r="F654" s="43"/>
+      <c r="F654" s="45"/>
       <c r="J654" s="4"/>
     </row>
     <row r="655">
       <c r="A655" s="4"/>
-      <c r="F655" s="43"/>
+      <c r="F655" s="45"/>
       <c r="J655" s="4"/>
     </row>
     <row r="656">
       <c r="A656" s="4"/>
-      <c r="F656" s="43"/>
+      <c r="F656" s="45"/>
       <c r="J656" s="4"/>
     </row>
     <row r="657">
       <c r="A657" s="4"/>
-      <c r="F657" s="43"/>
+      <c r="F657" s="45"/>
       <c r="J657" s="4"/>
     </row>
     <row r="658">
       <c r="A658" s="4"/>
-      <c r="F658" s="43"/>
+      <c r="F658" s="45"/>
       <c r="J658" s="4"/>
     </row>
     <row r="659">
       <c r="A659" s="4"/>
-      <c r="F659" s="43"/>
+      <c r="F659" s="45"/>
       <c r="J659" s="4"/>
     </row>
     <row r="660">
       <c r="A660" s="4"/>
-      <c r="F660" s="43"/>
+      <c r="F660" s="45"/>
       <c r="J660" s="4"/>
     </row>
     <row r="661">
       <c r="A661" s="4"/>
-      <c r="F661" s="43"/>
+      <c r="F661" s="45"/>
       <c r="J661" s="4"/>
     </row>
     <row r="662">
       <c r="A662" s="4"/>
-      <c r="F662" s="43"/>
+      <c r="F662" s="45"/>
       <c r="J662" s="4"/>
     </row>
     <row r="663">
       <c r="A663" s="4"/>
-      <c r="F663" s="43"/>
+      <c r="F663" s="45"/>
       <c r="J663" s="4"/>
     </row>
     <row r="664">
       <c r="A664" s="4"/>
-      <c r="F664" s="43"/>
+      <c r="F664" s="45"/>
       <c r="J664" s="4"/>
     </row>
     <row r="665">
       <c r="A665" s="4"/>
-      <c r="F665" s="43"/>
+      <c r="F665" s="45"/>
       <c r="J665" s="4"/>
     </row>
     <row r="666">
       <c r="A666" s="4"/>
-      <c r="F666" s="43"/>
+      <c r="F666" s="45"/>
       <c r="J666" s="4"/>
     </row>
     <row r="667">
       <c r="A667" s="4"/>
-      <c r="F667" s="43"/>
+      <c r="F667" s="45"/>
       <c r="J667" s="4"/>
     </row>
     <row r="668">
       <c r="A668" s="4"/>
-      <c r="F668" s="43"/>
+      <c r="F668" s="45"/>
       <c r="J668" s="4"/>
     </row>
     <row r="669">
       <c r="A669" s="4"/>
-      <c r="F669" s="43"/>
+      <c r="F669" s="45"/>
       <c r="J669" s="4"/>
     </row>
     <row r="670">
       <c r="A670" s="4"/>
-      <c r="F670" s="43"/>
+      <c r="F670" s="45"/>
       <c r="J670" s="4"/>
     </row>
     <row r="671">
       <c r="A671" s="4"/>
-      <c r="F671" s="43"/>
+      <c r="F671" s="45"/>
       <c r="J671" s="4"/>
     </row>
     <row r="672">
       <c r="A672" s="4"/>
-      <c r="F672" s="43"/>
+      <c r="F672" s="45"/>
       <c r="J672" s="4"/>
     </row>
     <row r="673">
       <c r="A673" s="4"/>
-      <c r="F673" s="43"/>
+      <c r="F673" s="45"/>
       <c r="J673" s="4"/>
     </row>
     <row r="674">
       <c r="A674" s="4"/>
-      <c r="F674" s="43"/>
+      <c r="F674" s="45"/>
       <c r="J674" s="4"/>
     </row>
     <row r="675">
       <c r="A675" s="4"/>
-      <c r="F675" s="43"/>
+      <c r="F675" s="45"/>
       <c r="J675" s="4"/>
     </row>
     <row r="676">
       <c r="A676" s="4"/>
-      <c r="F676" s="43"/>
+      <c r="F676" s="45"/>
       <c r="J676" s="4"/>
     </row>
     <row r="677">
       <c r="A677" s="4"/>
-      <c r="F677" s="43"/>
+      <c r="F677" s="45"/>
       <c r="J677" s="4"/>
     </row>
     <row r="678">
       <c r="A678" s="4"/>
-      <c r="F678" s="43"/>
+      <c r="F678" s="45"/>
       <c r="J678" s="4"/>
     </row>
     <row r="679">
       <c r="A679" s="4"/>
-      <c r="F679" s="43"/>
+      <c r="F679" s="45"/>
       <c r="J679" s="4"/>
     </row>
     <row r="680">
       <c r="A680" s="4"/>
-      <c r="F680" s="43"/>
+      <c r="F680" s="45"/>
       <c r="J680" s="4"/>
     </row>
     <row r="681">
       <c r="A681" s="4"/>
-      <c r="F681" s="43"/>
+      <c r="F681" s="45"/>
       <c r="J681" s="4"/>
     </row>
     <row r="682">
       <c r="A682" s="4"/>
-      <c r="F682" s="43"/>
+      <c r="F682" s="45"/>
       <c r="J682" s="4"/>
     </row>
     <row r="683">
       <c r="A683" s="4"/>
-      <c r="F683" s="43"/>
+      <c r="F683" s="45"/>
       <c r="J683" s="4"/>
     </row>
     <row r="684">
       <c r="A684" s="4"/>
-      <c r="F684" s="43"/>
+      <c r="F684" s="45"/>
       <c r="J684" s="4"/>
     </row>
     <row r="685">
       <c r="A685" s="4"/>
-      <c r="F685" s="43"/>
+      <c r="F685" s="45"/>
       <c r="J685" s="4"/>
     </row>
     <row r="686">
       <c r="A686" s="4"/>
-      <c r="F686" s="43"/>
+      <c r="F686" s="45"/>
       <c r="J686" s="4"/>
     </row>
     <row r="687">
       <c r="A687" s="4"/>
-      <c r="F687" s="43"/>
+      <c r="F687" s="45"/>
       <c r="J687" s="4"/>
     </row>
     <row r="688">
       <c r="A688" s="4"/>
-      <c r="F688" s="43"/>
+      <c r="F688" s="45"/>
       <c r="J688" s="4"/>
     </row>
     <row r="689">
       <c r="A689" s="4"/>
-      <c r="F689" s="43"/>
+      <c r="F689" s="45"/>
       <c r="J689" s="4"/>
     </row>
     <row r="690">
       <c r="A690" s="4"/>
-      <c r="F690" s="43"/>
+      <c r="F690" s="45"/>
       <c r="J690" s="4"/>
     </row>
     <row r="691">
       <c r="A691" s="4"/>
-      <c r="F691" s="43"/>
+      <c r="F691" s="45"/>
       <c r="J691" s="4"/>
     </row>
     <row r="692">
       <c r="A692" s="4"/>
-      <c r="F692" s="43"/>
+      <c r="F692" s="45"/>
       <c r="J692" s="4"/>
     </row>
     <row r="693">
       <c r="A693" s="4"/>
-      <c r="F693" s="43"/>
+      <c r="F693" s="45"/>
       <c r="J693" s="4"/>
     </row>
     <row r="694">
       <c r="A694" s="4"/>
-      <c r="F694" s="43"/>
+      <c r="F694" s="45"/>
       <c r="J694" s="4"/>
     </row>
     <row r="695">
       <c r="A695" s="4"/>
-      <c r="F695" s="43"/>
+      <c r="F695" s="45"/>
       <c r="J695" s="4"/>
     </row>
     <row r="696">
       <c r="A696" s="4"/>
-      <c r="F696" s="43"/>
+      <c r="F696" s="45"/>
       <c r="J696" s="4"/>
     </row>
     <row r="697">
       <c r="A697" s="4"/>
-      <c r="F697" s="43"/>
+      <c r="F697" s="45"/>
       <c r="J697" s="4"/>
     </row>
     <row r="698">
       <c r="A698" s="4"/>
-      <c r="F698" s="43"/>
+      <c r="F698" s="45"/>
       <c r="J698" s="4"/>
     </row>
     <row r="699">
       <c r="A699" s="4"/>
-      <c r="F699" s="43"/>
+      <c r="F699" s="45"/>
       <c r="J699" s="4"/>
     </row>
     <row r="700">
       <c r="A700" s="4"/>
-      <c r="F700" s="43"/>
+      <c r="F700" s="45"/>
       <c r="J700" s="4"/>
     </row>
     <row r="701">
       <c r="A701" s="4"/>
-      <c r="F701" s="43"/>
+      <c r="F701" s="45"/>
       <c r="J701" s="4"/>
     </row>
     <row r="702">
       <c r="A702" s="4"/>
-      <c r="F702" s="43"/>
+      <c r="F702" s="45"/>
       <c r="J702" s="4"/>
     </row>
     <row r="703">
       <c r="A703" s="4"/>
-      <c r="F703" s="43"/>
+      <c r="F703" s="45"/>
       <c r="J703" s="4"/>
     </row>
     <row r="704">
       <c r="A704" s="4"/>
-      <c r="F704" s="43"/>
+      <c r="F704" s="45"/>
       <c r="J704" s="4"/>
     </row>
     <row r="705">
       <c r="A705" s="4"/>
-      <c r="F705" s="43"/>
+      <c r="F705" s="45"/>
       <c r="J705" s="4"/>
     </row>
     <row r="706">
       <c r="A706" s="4"/>
-      <c r="F706" s="43"/>
+      <c r="F706" s="45"/>
       <c r="J706" s="4"/>
     </row>
     <row r="707">
       <c r="A707" s="4"/>
-      <c r="F707" s="43"/>
+      <c r="F707" s="45"/>
       <c r="J707" s="4"/>
     </row>
     <row r="708">
       <c r="A708" s="4"/>
-      <c r="F708" s="43"/>
+      <c r="F708" s="45"/>
       <c r="J708" s="4"/>
     </row>
     <row r="709">
       <c r="A709" s="4"/>
-      <c r="F709" s="43"/>
+      <c r="F709" s="45"/>
       <c r="J709" s="4"/>
     </row>
     <row r="710">
       <c r="A710" s="4"/>
-      <c r="F710" s="43"/>
+      <c r="F710" s="45"/>
       <c r="J710" s="4"/>
     </row>
     <row r="711">
       <c r="A711" s="4"/>
-      <c r="F711" s="43"/>
+      <c r="F711" s="45"/>
       <c r="J711" s="4"/>
     </row>
     <row r="712">
       <c r="A712" s="4"/>
-      <c r="F712" s="43"/>
+      <c r="F712" s="45"/>
       <c r="J712" s="4"/>
     </row>
     <row r="713">
       <c r="A713" s="4"/>
-      <c r="F713" s="43"/>
+      <c r="F713" s="45"/>
       <c r="J713" s="4"/>
     </row>
     <row r="714">
       <c r="A714" s="4"/>
-      <c r="F714" s="43"/>
+      <c r="F714" s="45"/>
       <c r="J714" s="4"/>
     </row>
     <row r="715">
       <c r="A715" s="4"/>
-      <c r="F715" s="43"/>
+      <c r="F715" s="45"/>
       <c r="J715" s="4"/>
     </row>
     <row r="716">
       <c r="A716" s="4"/>
-      <c r="F716" s="43"/>
+      <c r="F716" s="45"/>
       <c r="J716" s="4"/>
     </row>
     <row r="717">
       <c r="A717" s="4"/>
-      <c r="F717" s="43"/>
+      <c r="F717" s="45"/>
       <c r="J717" s="4"/>
     </row>
     <row r="718">
       <c r="A718" s="4"/>
-      <c r="F718" s="43"/>
+      <c r="F718" s="45"/>
       <c r="J718" s="4"/>
     </row>
     <row r="719">
       <c r="A719" s="4"/>
-      <c r="F719" s="43"/>
+      <c r="F719" s="45"/>
       <c r="J719" s="4"/>
     </row>
     <row r="720">
       <c r="A720" s="4"/>
-      <c r="F720" s="43"/>
+      <c r="F720" s="45"/>
       <c r="J720" s="4"/>
     </row>
     <row r="721">
       <c r="A721" s="4"/>
-      <c r="F721" s="43"/>
+      <c r="F721" s="45"/>
       <c r="J721" s="4"/>
     </row>
     <row r="722">
       <c r="A722" s="4"/>
-      <c r="F722" s="43"/>
+      <c r="F722" s="45"/>
       <c r="J722" s="4"/>
     </row>
     <row r="723">
       <c r="A723" s="4"/>
-      <c r="F723" s="43"/>
+      <c r="F723" s="45"/>
       <c r="J723" s="4"/>
     </row>
     <row r="724">
       <c r="A724" s="4"/>
-      <c r="F724" s="43"/>
+      <c r="F724" s="45"/>
       <c r="J724" s="4"/>
     </row>
     <row r="725">
       <c r="A725" s="4"/>
-      <c r="F725" s="43"/>
+      <c r="F725" s="45"/>
       <c r="J725" s="4"/>
     </row>
     <row r="726">
       <c r="A726" s="4"/>
-      <c r="F726" s="43"/>
+      <c r="F726" s="45"/>
       <c r="J726" s="4"/>
     </row>
     <row r="727">
       <c r="A727" s="4"/>
-      <c r="F727" s="43"/>
+      <c r="F727" s="45"/>
       <c r="J727" s="4"/>
     </row>
     <row r="728">
       <c r="A728" s="4"/>
-      <c r="F728" s="43"/>
+      <c r="F728" s="45"/>
       <c r="J728" s="4"/>
     </row>
     <row r="729">
       <c r="A729" s="4"/>
-      <c r="F729" s="43"/>
+      <c r="F729" s="45"/>
       <c r="J729" s="4"/>
     </row>
     <row r="730">
       <c r="A730" s="4"/>
-      <c r="F730" s="43"/>
+      <c r="F730" s="45"/>
       <c r="J730" s="4"/>
     </row>
     <row r="731">
       <c r="A731" s="4"/>
-      <c r="F731" s="43"/>
+      <c r="F731" s="45"/>
       <c r="J731" s="4"/>
     </row>
     <row r="732">
       <c r="A732" s="4"/>
-      <c r="F732" s="43"/>
+      <c r="F732" s="45"/>
       <c r="J732" s="4"/>
     </row>
     <row r="733">
       <c r="A733" s="4"/>
-      <c r="F733" s="43"/>
+      <c r="F733" s="45"/>
       <c r="J733" s="4"/>
     </row>
     <row r="734">
       <c r="A734" s="4"/>
-      <c r="F734" s="43"/>
+      <c r="F734" s="45"/>
       <c r="J734" s="4"/>
     </row>
     <row r="735">
       <c r="A735" s="4"/>
-      <c r="F735" s="43"/>
+      <c r="F735" s="45"/>
       <c r="J735" s="4"/>
     </row>
     <row r="736">
       <c r="A736" s="4"/>
-      <c r="F736" s="43"/>
+      <c r="F736" s="45"/>
       <c r="J736" s="4"/>
     </row>
     <row r="737">
       <c r="A737" s="4"/>
-      <c r="F737" s="43"/>
+      <c r="F737" s="45"/>
       <c r="J737" s="4"/>
     </row>
     <row r="738">
       <c r="A738" s="4"/>
-      <c r="F738" s="43"/>
+      <c r="F738" s="45"/>
       <c r="J738" s="4"/>
     </row>
     <row r="739">
       <c r="A739" s="4"/>
-      <c r="F739" s="43"/>
+      <c r="F739" s="45"/>
       <c r="J739" s="4"/>
     </row>
     <row r="740">
       <c r="A740" s="4"/>
-      <c r="F740" s="43"/>
+      <c r="F740" s="45"/>
       <c r="J740" s="4"/>
     </row>
     <row r="741">
       <c r="A741" s="4"/>
-      <c r="F741" s="43"/>
+      <c r="F741" s="45"/>
       <c r="J741" s="4"/>
     </row>
     <row r="742">
       <c r="A742" s="4"/>
-      <c r="F742" s="43"/>
+      <c r="F742" s="45"/>
       <c r="J742" s="4"/>
     </row>
     <row r="743">
       <c r="A743" s="4"/>
-      <c r="F743" s="43"/>
+      <c r="F743" s="45"/>
       <c r="J743" s="4"/>
     </row>
     <row r="744">
       <c r="A744" s="4"/>
-      <c r="F744" s="43"/>
+      <c r="F744" s="45"/>
       <c r="J744" s="4"/>
     </row>
     <row r="745">
       <c r="A745" s="4"/>
-      <c r="F745" s="43"/>
+      <c r="F745" s="45"/>
       <c r="J745" s="4"/>
     </row>
     <row r="746">
       <c r="A746" s="4"/>
-      <c r="F746" s="43"/>
+      <c r="F746" s="45"/>
       <c r="J746" s="4"/>
     </row>
     <row r="747">
       <c r="A747" s="4"/>
-      <c r="F747" s="43"/>
+      <c r="F747" s="45"/>
       <c r="J747" s="4"/>
     </row>
     <row r="748">
       <c r="A748" s="4"/>
-      <c r="F748" s="43"/>
+      <c r="F748" s="45"/>
       <c r="J748" s="4"/>
     </row>
     <row r="749">
       <c r="A749" s="4"/>
-      <c r="F749" s="43"/>
+      <c r="F749" s="45"/>
       <c r="J749" s="4"/>
     </row>
     <row r="750">
       <c r="A750" s="4"/>
-      <c r="F750" s="43"/>
+      <c r="F750" s="45"/>
       <c r="J750" s="4"/>
     </row>
     <row r="751">
       <c r="A751" s="4"/>
-      <c r="F751" s="43"/>
+      <c r="F751" s="45"/>
       <c r="J751" s="4"/>
     </row>
     <row r="752">
       <c r="A752" s="4"/>
-      <c r="F752" s="43"/>
+      <c r="F752" s="45"/>
       <c r="J752" s="4"/>
     </row>
     <row r="753">
       <c r="A753" s="4"/>
-      <c r="F753" s="43"/>
+      <c r="F753" s="45"/>
       <c r="J753" s="4"/>
     </row>
     <row r="754">
       <c r="A754" s="4"/>
-      <c r="F754" s="43"/>
+      <c r="F754" s="45"/>
       <c r="J754" s="4"/>
     </row>
     <row r="755">
       <c r="A755" s="4"/>
-      <c r="F755" s="43"/>
+      <c r="F755" s="45"/>
       <c r="J755" s="4"/>
     </row>
     <row r="756">
       <c r="A756" s="4"/>
-      <c r="F756" s="43"/>
+      <c r="F756" s="45"/>
       <c r="J756" s="4"/>
     </row>
     <row r="757">
       <c r="A757" s="4"/>
-      <c r="F757" s="43"/>
+      <c r="F757" s="45"/>
       <c r="J757" s="4"/>
     </row>
     <row r="758">
       <c r="A758" s="4"/>
-      <c r="F758" s="43"/>
+      <c r="F758" s="45"/>
       <c r="J758" s="4"/>
     </row>
     <row r="759">
       <c r="A759" s="4"/>
-      <c r="F759" s="43"/>
+      <c r="F759" s="45"/>
       <c r="J759" s="4"/>
     </row>
     <row r="760">
       <c r="A760" s="4"/>
-      <c r="F760" s="43"/>
+      <c r="F760" s="45"/>
       <c r="J760" s="4"/>
     </row>
     <row r="761">
       <c r="A761" s="4"/>
-      <c r="F761" s="43"/>
+      <c r="F761" s="45"/>
       <c r="J761" s="4"/>
     </row>
     <row r="762">
       <c r="A762" s="4"/>
-      <c r="F762" s="43"/>
+      <c r="F762" s="45"/>
       <c r="J762" s="4"/>
     </row>
     <row r="763">
       <c r="A763" s="4"/>
-      <c r="F763" s="43"/>
+      <c r="F763" s="45"/>
       <c r="J763" s="4"/>
     </row>
     <row r="764">
       <c r="A764" s="4"/>
-      <c r="F764" s="43"/>
+      <c r="F764" s="45"/>
       <c r="J764" s="4"/>
     </row>
     <row r="765">
       <c r="A765" s="4"/>
-      <c r="F765" s="43"/>
+      <c r="F765" s="45"/>
       <c r="J765" s="4"/>
     </row>
     <row r="766">
       <c r="A766" s="4"/>
-      <c r="F766" s="43"/>
+      <c r="F766" s="45"/>
       <c r="J766" s="4"/>
     </row>
     <row r="767">
       <c r="A767" s="4"/>
-      <c r="F767" s="43"/>
+      <c r="F767" s="45"/>
       <c r="J767" s="4"/>
     </row>
     <row r="768">
       <c r="A768" s="4"/>
-      <c r="F768" s="43"/>
+      <c r="F768" s="45"/>
       <c r="J768" s="4"/>
     </row>
     <row r="769">
       <c r="A769" s="4"/>
-      <c r="F769" s="43"/>
+      <c r="F769" s="45"/>
       <c r="J769" s="4"/>
     </row>
     <row r="770">
       <c r="A770" s="4"/>
-      <c r="F770" s="43"/>
+      <c r="F770" s="45"/>
       <c r="J770" s="4"/>
     </row>
     <row r="771">
       <c r="A771" s="4"/>
-      <c r="F771" s="43"/>
+      <c r="F771" s="45"/>
       <c r="J771" s="4"/>
     </row>
     <row r="772">
       <c r="A772" s="4"/>
-      <c r="F772" s="43"/>
+      <c r="F772" s="45"/>
       <c r="J772" s="4"/>
     </row>
     <row r="773">
       <c r="A773" s="4"/>
-      <c r="F773" s="43"/>
+      <c r="F773" s="45"/>
       <c r="J773" s="4"/>
     </row>
     <row r="774">
       <c r="A774" s="4"/>
-      <c r="F774" s="43"/>
+      <c r="F774" s="45"/>
       <c r="J774" s="4"/>
     </row>
     <row r="775">
       <c r="A775" s="4"/>
-      <c r="F775" s="43"/>
+      <c r="F775" s="45"/>
       <c r="J775" s="4"/>
     </row>
     <row r="776">
       <c r="A776" s="4"/>
-      <c r="F776" s="43"/>
+      <c r="F776" s="45"/>
       <c r="J776" s="4"/>
     </row>
     <row r="777">
       <c r="A777" s="4"/>
-      <c r="F777" s="43"/>
+      <c r="F777" s="45"/>
       <c r="J777" s="4"/>
     </row>
     <row r="778">
       <c r="A778" s="4"/>
-      <c r="F778" s="43"/>
+      <c r="F778" s="45"/>
       <c r="J778" s="4"/>
     </row>
     <row r="779">
       <c r="A779" s="4"/>
-      <c r="F779" s="43"/>
+      <c r="F779" s="45"/>
       <c r="J779" s="4"/>
     </row>
     <row r="780">
       <c r="A780" s="4"/>
-      <c r="F780" s="43"/>
+      <c r="F780" s="45"/>
       <c r="J780" s="4"/>
     </row>
     <row r="781">
       <c r="A781" s="4"/>
-      <c r="F781" s="43"/>
+      <c r="F781" s="45"/>
       <c r="J781" s="4"/>
     </row>
     <row r="782">
       <c r="A782" s="4"/>
-      <c r="F782" s="43"/>
+      <c r="F782" s="45"/>
       <c r="J782" s="4"/>
     </row>
     <row r="783">
       <c r="A783" s="4"/>
-      <c r="F783" s="43"/>
+      <c r="F783" s="45"/>
       <c r="J783" s="4"/>
     </row>
     <row r="784">
       <c r="A784" s="4"/>
-      <c r="F784" s="43"/>
+      <c r="F784" s="45"/>
       <c r="J784" s="4"/>
     </row>
     <row r="785">
       <c r="A785" s="4"/>
-      <c r="F785" s="43"/>
+      <c r="F785" s="45"/>
       <c r="J785" s="4"/>
     </row>
     <row r="786">
       <c r="A786" s="4"/>
-      <c r="F786" s="43"/>
+      <c r="F786" s="45"/>
       <c r="J786" s="4"/>
     </row>
     <row r="787">
       <c r="A787" s="4"/>
-      <c r="F787" s="43"/>
+      <c r="F787" s="45"/>
       <c r="J787" s="4"/>
     </row>
     <row r="788">
       <c r="A788" s="4"/>
-      <c r="F788" s="43"/>
+      <c r="F788" s="45"/>
       <c r="J788" s="4"/>
     </row>
     <row r="789">
       <c r="A789" s="4"/>
-      <c r="F789" s="43"/>
+      <c r="F789" s="45"/>
       <c r="J789" s="4"/>
     </row>
     <row r="790">
       <c r="A790" s="4"/>
-      <c r="F790" s="43"/>
+      <c r="F790" s="45"/>
       <c r="J790" s="4"/>
     </row>
     <row r="791">
       <c r="A791" s="4"/>
-      <c r="F791" s="43"/>
+      <c r="F791" s="45"/>
       <c r="J791" s="4"/>
     </row>
     <row r="792">
       <c r="A792" s="4"/>
-      <c r="F792" s="43"/>
+      <c r="F792" s="45"/>
       <c r="J792" s="4"/>
     </row>
     <row r="793">
       <c r="A793" s="4"/>
-      <c r="F793" s="43"/>
+      <c r="F793" s="45"/>
       <c r="J793" s="4"/>
     </row>
     <row r="794">
       <c r="A794" s="4"/>
-      <c r="F794" s="43"/>
+      <c r="F794" s="45"/>
       <c r="J794" s="4"/>
     </row>
     <row r="795">
       <c r="A795" s="4"/>
-      <c r="F795" s="43"/>
+      <c r="F795" s="45"/>
       <c r="J795" s="4"/>
     </row>
     <row r="796">
       <c r="A796" s="4"/>
-      <c r="F796" s="43"/>
+      <c r="F796" s="45"/>
       <c r="J796" s="4"/>
     </row>
     <row r="797">
       <c r="A797" s="4"/>
-      <c r="F797" s="43"/>
+      <c r="F797" s="45"/>
       <c r="J797" s="4"/>
     </row>
     <row r="798">
       <c r="A798" s="4"/>
-      <c r="F798" s="43"/>
+      <c r="F798" s="45"/>
       <c r="J798" s="4"/>
     </row>
     <row r="799">
       <c r="A799" s="4"/>
-      <c r="F799" s="43"/>
+      <c r="F799" s="45"/>
       <c r="J799" s="4"/>
     </row>
     <row r="800">
       <c r="A800" s="4"/>
-      <c r="F800" s="43"/>
+      <c r="F800" s="45"/>
       <c r="J800" s="4"/>
     </row>
     <row r="801">
       <c r="A801" s="4"/>
-      <c r="F801" s="43"/>
+      <c r="F801" s="45"/>
       <c r="J801" s="4"/>
     </row>
     <row r="802">
       <c r="A802" s="4"/>
-      <c r="F802" s="43"/>
+      <c r="F802" s="45"/>
       <c r="J802" s="4"/>
     </row>
     <row r="803">
       <c r="A803" s="4"/>
-      <c r="F803" s="43"/>
+      <c r="F803" s="45"/>
       <c r="J803" s="4"/>
     </row>
     <row r="804">
       <c r="A804" s="4"/>
-      <c r="F804" s="43"/>
+      <c r="F804" s="45"/>
       <c r="J804" s="4"/>
     </row>
     <row r="805">
       <c r="A805" s="4"/>
-      <c r="F805" s="43"/>
+      <c r="F805" s="45"/>
       <c r="J805" s="4"/>
     </row>
     <row r="806">
       <c r="A806" s="4"/>
-      <c r="F806" s="43"/>
+      <c r="F806" s="45"/>
       <c r="J806" s="4"/>
     </row>
     <row r="807">
       <c r="A807" s="4"/>
-      <c r="F807" s="43"/>
+      <c r="F807" s="45"/>
       <c r="J807" s="4"/>
     </row>
     <row r="808">
       <c r="A808" s="4"/>
-      <c r="F808" s="43"/>
+      <c r="F808" s="45"/>
       <c r="J808" s="4"/>
     </row>
     <row r="809">
       <c r="A809" s="4"/>
-      <c r="F809" s="43"/>
+      <c r="F809" s="45"/>
       <c r="J809" s="4"/>
     </row>
     <row r="810">
       <c r="A810" s="4"/>
-      <c r="F810" s="43"/>
+      <c r="F810" s="45"/>
       <c r="J810" s="4"/>
     </row>
     <row r="811">
       <c r="A811" s="4"/>
-      <c r="F811" s="43"/>
+      <c r="F811" s="45"/>
       <c r="J811" s="4"/>
     </row>
     <row r="812">
       <c r="A812" s="4"/>
-      <c r="F812" s="43"/>
+      <c r="F812" s="45"/>
       <c r="J812" s="4"/>
     </row>
     <row r="813">
       <c r="A813" s="4"/>
-      <c r="F813" s="43"/>
+      <c r="F813" s="45"/>
       <c r="J813" s="4"/>
     </row>
     <row r="814">
       <c r="A814" s="4"/>
-      <c r="F814" s="43"/>
+      <c r="F814" s="45"/>
       <c r="J814" s="4"/>
     </row>
     <row r="815">
       <c r="A815" s="4"/>
-      <c r="F815" s="43"/>
+      <c r="F815" s="45"/>
       <c r="J815" s="4"/>
     </row>
     <row r="816">
       <c r="A816" s="4"/>
-      <c r="F816" s="43"/>
+      <c r="F816" s="45"/>
       <c r="J816" s="4"/>
     </row>
     <row r="817">
       <c r="A817" s="4"/>
-      <c r="F817" s="43"/>
+      <c r="F817" s="45"/>
       <c r="J817" s="4"/>
     </row>
     <row r="818">
       <c r="A818" s="4"/>
-      <c r="F818" s="43"/>
+      <c r="F818" s="45"/>
       <c r="J818" s="4"/>
     </row>
     <row r="819">
       <c r="A819" s="4"/>
-      <c r="F819" s="43"/>
+      <c r="F819" s="45"/>
       <c r="J819" s="4"/>
     </row>
     <row r="820">
       <c r="A820" s="4"/>
-      <c r="F820" s="43"/>
+      <c r="F820" s="45"/>
       <c r="J820" s="4"/>
     </row>
     <row r="821">
       <c r="A821" s="4"/>
-      <c r="F821" s="43"/>
+      <c r="F821" s="45"/>
       <c r="J821" s="4"/>
     </row>
     <row r="822">
       <c r="A822" s="4"/>
-      <c r="F822" s="43"/>
+      <c r="F822" s="45"/>
       <c r="J822" s="4"/>
     </row>
     <row r="823">
       <c r="A823" s="4"/>
-      <c r="F823" s="43"/>
+      <c r="F823" s="45"/>
       <c r="J823" s="4"/>
     </row>
     <row r="824">
       <c r="A824" s="4"/>
-      <c r="F824" s="43"/>
+      <c r="F824" s="45"/>
       <c r="J824" s="4"/>
     </row>
     <row r="825">
       <c r="A825" s="4"/>
-      <c r="F825" s="43"/>
+      <c r="F825" s="45"/>
       <c r="J825" s="4"/>
     </row>
     <row r="826">
       <c r="A826" s="4"/>
-      <c r="F826" s="43"/>
+      <c r="F826" s="45"/>
       <c r="J826" s="4"/>
     </row>
     <row r="827">
       <c r="A827" s="4"/>
-      <c r="F827" s="43"/>
+      <c r="F827" s="45"/>
       <c r="J827" s="4"/>
     </row>
     <row r="828">
       <c r="A828" s="4"/>
-      <c r="F828" s="43"/>
+      <c r="F828" s="45"/>
       <c r="J828" s="4"/>
     </row>
     <row r="829">
       <c r="A829" s="4"/>
-      <c r="F829" s="43"/>
+      <c r="F829" s="45"/>
       <c r="J829" s="4"/>
     </row>
     <row r="830">
       <c r="A830" s="4"/>
-      <c r="F830" s="43"/>
+      <c r="F830" s="45"/>
       <c r="J830" s="4"/>
     </row>
     <row r="831">
       <c r="A831" s="4"/>
-      <c r="F831" s="43"/>
+      <c r="F831" s="45"/>
       <c r="J831" s="4"/>
     </row>
     <row r="832">
       <c r="A832" s="4"/>
-      <c r="F832" s="43"/>
+      <c r="F832" s="45"/>
       <c r="J832" s="4"/>
     </row>
     <row r="833">
       <c r="A833" s="4"/>
-      <c r="F833" s="43"/>
+      <c r="F833" s="45"/>
       <c r="J833" s="4"/>
     </row>
     <row r="834">
       <c r="A834" s="4"/>
-      <c r="F834" s="43"/>
+      <c r="F834" s="45"/>
       <c r="J834" s="4"/>
     </row>
     <row r="835">
       <c r="A835" s="4"/>
-      <c r="F835" s="43"/>
+      <c r="F835" s="45"/>
       <c r="J835" s="4"/>
     </row>
     <row r="836">
       <c r="A836" s="4"/>
-      <c r="F836" s="43"/>
+      <c r="F836" s="45"/>
       <c r="J836" s="4"/>
     </row>
     <row r="837">
       <c r="A837" s="4"/>
-      <c r="F837" s="43"/>
+      <c r="F837" s="45"/>
       <c r="J837" s="4"/>
     </row>
     <row r="838">
       <c r="A838" s="4"/>
-      <c r="F838" s="43"/>
+      <c r="F838" s="45"/>
       <c r="J838" s="4"/>
     </row>
     <row r="839">
       <c r="A839" s="4"/>
-      <c r="F839" s="43"/>
+      <c r="F839" s="45"/>
       <c r="J839" s="4"/>
     </row>
     <row r="840">
       <c r="A840" s="4"/>
-      <c r="F840" s="43"/>
+      <c r="F840" s="45"/>
       <c r="J840" s="4"/>
     </row>
     <row r="841">
       <c r="A841" s="4"/>
-      <c r="F841" s="43"/>
+      <c r="F841" s="45"/>
       <c r="J841" s="4"/>
     </row>
     <row r="842">
       <c r="A842" s="4"/>
-      <c r="F842" s="43"/>
+      <c r="F842" s="45"/>
       <c r="J842" s="4"/>
     </row>
     <row r="843">
       <c r="A843" s="4"/>
-      <c r="F843" s="43"/>
+      <c r="F843" s="45"/>
       <c r="J843" s="4"/>
     </row>
     <row r="844">
       <c r="A844" s="4"/>
-      <c r="F844" s="43"/>
+      <c r="F844" s="45"/>
       <c r="J844" s="4"/>
     </row>
     <row r="845">
       <c r="A845" s="4"/>
-      <c r="F845" s="43"/>
+      <c r="F845" s="45"/>
       <c r="J845" s="4"/>
     </row>
     <row r="846">
       <c r="A846" s="4"/>
-      <c r="F846" s="43"/>
+      <c r="F846" s="45"/>
       <c r="J846" s="4"/>
     </row>
     <row r="847">
       <c r="A847" s="4"/>
-      <c r="F847" s="43"/>
+      <c r="F847" s="45"/>
       <c r="J847" s="4"/>
     </row>
     <row r="848">
       <c r="A848" s="4"/>
-      <c r="F848" s="43"/>
+      <c r="F848" s="45"/>
       <c r="J848" s="4"/>
     </row>
     <row r="849">
       <c r="A849" s="4"/>
-      <c r="F849" s="43"/>
+      <c r="F849" s="45"/>
       <c r="J849" s="4"/>
     </row>
     <row r="850">
       <c r="A850" s="4"/>
-      <c r="F850" s="43"/>
+      <c r="F850" s="45"/>
       <c r="J850" s="4"/>
     </row>
     <row r="851">
       <c r="A851" s="4"/>
-      <c r="F851" s="43"/>
+      <c r="F851" s="45"/>
       <c r="J851" s="4"/>
     </row>
     <row r="852">
       <c r="A852" s="4"/>
-      <c r="F852" s="43"/>
+      <c r="F852" s="45"/>
       <c r="J852" s="4"/>
     </row>
     <row r="853">
       <c r="A853" s="4"/>
-      <c r="F853" s="43"/>
+      <c r="F853" s="45"/>
       <c r="J853" s="4"/>
     </row>
     <row r="854">
       <c r="A854" s="4"/>
-      <c r="F854" s="43"/>
+      <c r="F854" s="45"/>
       <c r="J854" s="4"/>
     </row>
     <row r="855">
       <c r="A855" s="4"/>
-      <c r="F855" s="43"/>
+      <c r="F855" s="45"/>
       <c r="J855" s="4"/>
     </row>
     <row r="856">
       <c r="A856" s="4"/>
-      <c r="F856" s="43"/>
+      <c r="F856" s="45"/>
       <c r="J856" s="4"/>
     </row>
     <row r="857">
       <c r="A857" s="4"/>
-      <c r="F857" s="43"/>
+      <c r="F857" s="45"/>
       <c r="J857" s="4"/>
     </row>
     <row r="858">
       <c r="A858" s="4"/>
-      <c r="F858" s="43"/>
+      <c r="F858" s="45"/>
       <c r="J858" s="4"/>
     </row>
     <row r="859">
       <c r="A859" s="4"/>
-      <c r="F859" s="43"/>
+      <c r="F859" s="45"/>
       <c r="J859" s="4"/>
     </row>
     <row r="860">
       <c r="A860" s="4"/>
-      <c r="F860" s="43"/>
+      <c r="F860" s="45"/>
       <c r="J860" s="4"/>
     </row>
     <row r="861">
       <c r="A861" s="4"/>
-      <c r="F861" s="43"/>
+      <c r="F861" s="45"/>
       <c r="J861" s="4"/>
     </row>
     <row r="862">
       <c r="A862" s="4"/>
-      <c r="F862" s="43"/>
+      <c r="F862" s="45"/>
       <c r="J862" s="4"/>
     </row>
     <row r="863">
       <c r="A863" s="4"/>
-      <c r="F863" s="43"/>
+      <c r="F863" s="45"/>
       <c r="J863" s="4"/>
     </row>
     <row r="864">
       <c r="A864" s="4"/>
-      <c r="F864" s="43"/>
+      <c r="F864" s="45"/>
       <c r="J864" s="4"/>
     </row>
     <row r="865">
       <c r="A865" s="4"/>
-      <c r="F865" s="43"/>
+      <c r="F865" s="45"/>
       <c r="J865" s="4"/>
     </row>
     <row r="866">
       <c r="A866" s="4"/>
-      <c r="F866" s="43"/>
+      <c r="F866" s="45"/>
       <c r="J866" s="4"/>
     </row>
     <row r="867">
       <c r="A867" s="4"/>
-      <c r="F867" s="43"/>
+      <c r="F867" s="45"/>
       <c r="J867" s="4"/>
     </row>
     <row r="868">
       <c r="A868" s="4"/>
-      <c r="F868" s="43"/>
+      <c r="F868" s="45"/>
       <c r="J868" s="4"/>
     </row>
     <row r="869">
       <c r="A869" s="4"/>
-      <c r="F869" s="43"/>
+      <c r="F869" s="45"/>
       <c r="J869" s="4"/>
     </row>
     <row r="870">
       <c r="A870" s="4"/>
-      <c r="F870" s="43"/>
+      <c r="F870" s="45"/>
       <c r="J870" s="4"/>
     </row>
     <row r="871">
       <c r="A871" s="4"/>
-      <c r="F871" s="43"/>
+      <c r="F871" s="45"/>
       <c r="J871" s="4"/>
     </row>
     <row r="872">
       <c r="A872" s="4"/>
-      <c r="F872" s="43"/>
+      <c r="F872" s="45"/>
       <c r="J872" s="4"/>
     </row>
     <row r="873">
       <c r="A873" s="4"/>
-      <c r="F873" s="43"/>
+      <c r="F873" s="45"/>
       <c r="J873" s="4"/>
     </row>
     <row r="874">
       <c r="A874" s="4"/>
-      <c r="F874" s="43"/>
+      <c r="F874" s="45"/>
       <c r="J874" s="4"/>
     </row>
     <row r="875">
       <c r="A875" s="4"/>
-      <c r="F875" s="43"/>
+      <c r="F875" s="45"/>
       <c r="J875" s="4"/>
     </row>
     <row r="876">
       <c r="A876" s="4"/>
-      <c r="F876" s="43"/>
+      <c r="F876" s="45"/>
       <c r="J876" s="4"/>
     </row>
     <row r="877">
       <c r="A877" s="4"/>
-      <c r="F877" s="43"/>
+      <c r="F877" s="45"/>
       <c r="J877" s="4"/>
     </row>
     <row r="878">
       <c r="A878" s="4"/>
-      <c r="F878" s="43"/>
+      <c r="F878" s="45"/>
       <c r="J878" s="4"/>
     </row>
     <row r="879">
       <c r="A879" s="4"/>
-      <c r="F879" s="43"/>
+      <c r="F879" s="45"/>
       <c r="J879" s="4"/>
     </row>
     <row r="880">
       <c r="A880" s="4"/>
-      <c r="F880" s="43"/>
+      <c r="F880" s="45"/>
       <c r="J880" s="4"/>
     </row>
     <row r="881">
       <c r="A881" s="4"/>
-      <c r="F881" s="43"/>
+      <c r="F881" s="45"/>
       <c r="J881" s="4"/>
     </row>
     <row r="882">
       <c r="A882" s="4"/>
-      <c r="F882" s="43"/>
+      <c r="F882" s="45"/>
       <c r="J882" s="4"/>
     </row>
     <row r="883">
       <c r="A883" s="4"/>
-      <c r="F883" s="43"/>
+      <c r="F883" s="45"/>
       <c r="J883" s="4"/>
     </row>
     <row r="884">
       <c r="A884" s="4"/>
-      <c r="F884" s="43"/>
+      <c r="F884" s="45"/>
       <c r="J884" s="4"/>
     </row>
     <row r="885">
       <c r="A885" s="4"/>
-      <c r="F885" s="43"/>
+      <c r="F885" s="45"/>
       <c r="J885" s="4"/>
     </row>
     <row r="886">
       <c r="A886" s="4"/>
-      <c r="F886" s="43"/>
+      <c r="F886" s="45"/>
       <c r="J886" s="4"/>
     </row>
     <row r="887">
       <c r="A887" s="4"/>
-      <c r="F887" s="43"/>
+      <c r="F887" s="45"/>
       <c r="J887" s="4"/>
     </row>
     <row r="888">
       <c r="A888" s="4"/>
-      <c r="F888" s="43"/>
+      <c r="F888" s="45"/>
       <c r="J888" s="4"/>
     </row>
     <row r="889">
       <c r="A889" s="4"/>
-      <c r="F889" s="43"/>
+      <c r="F889" s="45"/>
       <c r="J889" s="4"/>
     </row>
     <row r="890">
       <c r="A890" s="4"/>
-      <c r="F890" s="43"/>
+      <c r="F890" s="45"/>
       <c r="J890" s="4"/>
     </row>
     <row r="891">
       <c r="A891" s="4"/>
-      <c r="F891" s="43"/>
+      <c r="F891" s="45"/>
       <c r="J891" s="4"/>
     </row>
     <row r="892">
       <c r="A892" s="4"/>
-      <c r="F892" s="43"/>
+      <c r="F892" s="45"/>
       <c r="J892" s="4"/>
     </row>
     <row r="893">
       <c r="A893" s="4"/>
-      <c r="F893" s="43"/>
+      <c r="F893" s="45"/>
       <c r="J893" s="4"/>
     </row>
     <row r="894">
       <c r="A894" s="4"/>
-      <c r="F894" s="43"/>
+      <c r="F894" s="45"/>
       <c r="J894" s="4"/>
     </row>
     <row r="895">
       <c r="A895" s="4"/>
-      <c r="F895" s="43"/>
+      <c r="F895" s="45"/>
       <c r="J895" s="4"/>
     </row>
     <row r="896">
       <c r="A896" s="4"/>
-      <c r="F896" s="43"/>
+      <c r="F896" s="45"/>
       <c r="J896" s="4"/>
     </row>
     <row r="897">
       <c r="A897" s="4"/>
-      <c r="F897" s="43"/>
+      <c r="F897" s="45"/>
       <c r="J897" s="4"/>
     </row>
     <row r="898">
       <c r="A898" s="4"/>
-      <c r="F898" s="43"/>
+      <c r="F898" s="45"/>
       <c r="J898" s="4"/>
     </row>
     <row r="899">
       <c r="A899" s="4"/>
-      <c r="F899" s="43"/>
+      <c r="F899" s="45"/>
       <c r="J899" s="4"/>
     </row>
     <row r="900">
       <c r="A900" s="4"/>
-      <c r="F900" s="43"/>
+      <c r="F900" s="45"/>
       <c r="J900" s="4"/>
     </row>
     <row r="901">
       <c r="A901" s="4"/>
-      <c r="F901" s="43"/>
+      <c r="F901" s="45"/>
       <c r="J901" s="4"/>
     </row>
     <row r="902">
       <c r="A902" s="4"/>
-      <c r="F902" s="43"/>
+      <c r="F902" s="45"/>
       <c r="J902" s="4"/>
     </row>
     <row r="903">
       <c r="A903" s="4"/>
-      <c r="F903" s="43"/>
+      <c r="F903" s="45"/>
       <c r="J903" s="4"/>
     </row>
     <row r="904">
       <c r="A904" s="4"/>
-      <c r="F904" s="43"/>
+      <c r="F904" s="45"/>
       <c r="J904" s="4"/>
     </row>
     <row r="905">
       <c r="A905" s="4"/>
-      <c r="F905" s="43"/>
+      <c r="F905" s="45"/>
       <c r="J905" s="4"/>
     </row>
     <row r="906">
       <c r="A906" s="4"/>
-      <c r="F906" s="43"/>
+      <c r="F906" s="45"/>
       <c r="J906" s="4"/>
     </row>
     <row r="907">
       <c r="A907" s="4"/>
-      <c r="F907" s="43"/>
+      <c r="F907" s="45"/>
       <c r="J907" s="4"/>
     </row>
     <row r="908">
       <c r="A908" s="4"/>
-      <c r="F908" s="43"/>
+      <c r="F908" s="45"/>
       <c r="J908" s="4"/>
     </row>
     <row r="909">
       <c r="A909" s="4"/>
-      <c r="F909" s="43"/>
+      <c r="F909" s="45"/>
       <c r="J909" s="4"/>
     </row>
     <row r="910">
       <c r="A910" s="4"/>
-      <c r="F910" s="43"/>
+      <c r="F910" s="45"/>
       <c r="J910" s="4"/>
     </row>
     <row r="911">
       <c r="A911" s="4"/>
-      <c r="F911" s="43"/>
+      <c r="F911" s="45"/>
       <c r="J911" s="4"/>
     </row>
     <row r="912">
       <c r="A912" s="4"/>
-      <c r="F912" s="43"/>
+      <c r="F912" s="45"/>
       <c r="J912" s="4"/>
     </row>
     <row r="913">
       <c r="A913" s="4"/>
-      <c r="F913" s="43"/>
+      <c r="F913" s="45"/>
       <c r="J913" s="4"/>
     </row>
     <row r="914">
       <c r="A914" s="4"/>
-      <c r="F914" s="43"/>
+      <c r="F914" s="45"/>
       <c r="J914" s="4"/>
     </row>
     <row r="915">
       <c r="A915" s="4"/>
-      <c r="F915" s="43"/>
+      <c r="F915" s="45"/>
       <c r="J915" s="4"/>
     </row>
     <row r="916">
       <c r="A916" s="4"/>
-      <c r="F916" s="43"/>
+      <c r="F916" s="45"/>
       <c r="J916" s="4"/>
     </row>
     <row r="917">
       <c r="A917" s="4"/>
-      <c r="F917" s="43"/>
+      <c r="F917" s="45"/>
       <c r="J917" s="4"/>
     </row>
     <row r="918">
       <c r="A918" s="4"/>
-      <c r="F918" s="43"/>
+      <c r="F918" s="45"/>
       <c r="J918" s="4"/>
     </row>
     <row r="919">
       <c r="A919" s="4"/>
-      <c r="F919" s="43"/>
+      <c r="F919" s="45"/>
       <c r="J919" s="4"/>
     </row>
     <row r="920">
       <c r="A920" s="4"/>
-      <c r="F920" s="43"/>
+      <c r="F920" s="45"/>
       <c r="J920" s="4"/>
     </row>
     <row r="921">
       <c r="A921" s="4"/>
-      <c r="F921" s="43"/>
+      <c r="F921" s="45"/>
       <c r="J921" s="4"/>
     </row>
     <row r="922">
       <c r="A922" s="4"/>
-      <c r="F922" s="43"/>
+      <c r="F922" s="45"/>
       <c r="J922" s="4"/>
     </row>
     <row r="923">
       <c r="A923" s="4"/>
-      <c r="F923" s="43"/>
+      <c r="F923" s="45"/>
       <c r="J923" s="4"/>
     </row>
     <row r="924">
       <c r="A924" s="4"/>
-      <c r="F924" s="43"/>
+      <c r="F924" s="45"/>
       <c r="J924" s="4"/>
     </row>
     <row r="925">
       <c r="A925" s="4"/>
-      <c r="F925" s="43"/>
+      <c r="F925" s="45"/>
       <c r="J925" s="4"/>
     </row>
     <row r="926">
       <c r="A926" s="4"/>
-      <c r="F926" s="43"/>
+      <c r="F926" s="45"/>
       <c r="J926" s="4"/>
     </row>
     <row r="927">
       <c r="A927" s="4"/>
-      <c r="F927" s="43"/>
+      <c r="F927" s="45"/>
       <c r="J927" s="4"/>
     </row>
     <row r="928">
       <c r="A928" s="4"/>
-      <c r="F928" s="43"/>
+      <c r="F928" s="45"/>
       <c r="J928" s="4"/>
     </row>
     <row r="929">
       <c r="A929" s="4"/>
-      <c r="F929" s="43"/>
+      <c r="F929" s="45"/>
       <c r="J929" s="4"/>
     </row>
     <row r="930">
       <c r="A930" s="4"/>
-      <c r="F930" s="43"/>
+      <c r="F930" s="45"/>
       <c r="J930" s="4"/>
     </row>
     <row r="931">
       <c r="A931" s="4"/>
-      <c r="F931" s="43"/>
+      <c r="F931" s="45"/>
       <c r="J931" s="4"/>
     </row>
     <row r="932">
       <c r="A932" s="4"/>
-      <c r="F932" s="43"/>
+      <c r="F932" s="45"/>
       <c r="J932" s="4"/>
     </row>
     <row r="933">
       <c r="A933" s="4"/>
-      <c r="F933" s="43"/>
+      <c r="F933" s="45"/>
       <c r="J933" s="4"/>
     </row>
     <row r="934">
       <c r="A934" s="4"/>
-      <c r="F934" s="43"/>
+      <c r="F934" s="45"/>
       <c r="J934" s="4"/>
     </row>
     <row r="935">
       <c r="A935" s="4"/>
-      <c r="F935" s="43"/>
+      <c r="F935" s="45"/>
       <c r="J935" s="4"/>
     </row>
     <row r="936">
       <c r="A936" s="4"/>
-      <c r="F936" s="43"/>
+      <c r="F936" s="45"/>
       <c r="J936" s="4"/>
     </row>
     <row r="937">
       <c r="A937" s="4"/>
-      <c r="F937" s="43"/>
+      <c r="F937" s="45"/>
       <c r="J937" s="4"/>
     </row>
     <row r="938">
       <c r="A938" s="4"/>
-      <c r="F938" s="43"/>
+      <c r="F938" s="45"/>
       <c r="J938" s="4"/>
     </row>
     <row r="939">
       <c r="A939" s="4"/>
-      <c r="F939" s="43"/>
+      <c r="F939" s="45"/>
       <c r="J939" s="4"/>
     </row>
     <row r="940">
       <c r="A940" s="4"/>
-      <c r="F940" s="43"/>
+      <c r="F940" s="45"/>
       <c r="J940" s="4"/>
     </row>
     <row r="941">
       <c r="A941" s="4"/>
-      <c r="F941" s="43"/>
+      <c r="F941" s="45"/>
       <c r="J941" s="4"/>
     </row>
     <row r="942">
       <c r="A942" s="4"/>
-      <c r="F942" s="43"/>
+      <c r="F942" s="45"/>
       <c r="J942" s="4"/>
     </row>
     <row r="943">
       <c r="A943" s="4"/>
-      <c r="F943" s="43"/>
+      <c r="F943" s="45"/>
       <c r="J943" s="4"/>
     </row>
     <row r="944">
       <c r="A944" s="4"/>
-      <c r="F944" s="43"/>
+      <c r="F944" s="45"/>
       <c r="J944" s="4"/>
     </row>
     <row r="945">
       <c r="A945" s="4"/>
-      <c r="F945" s="43"/>
+      <c r="F945" s="45"/>
       <c r="J945" s="4"/>
     </row>
     <row r="946">
       <c r="A946" s="4"/>
-      <c r="F946" s="43"/>
+      <c r="F946" s="45"/>
       <c r="J946" s="4"/>
     </row>
     <row r="947">
       <c r="A947" s="4"/>
-      <c r="F947" s="43"/>
+      <c r="F947" s="45"/>
       <c r="J947" s="4"/>
     </row>
     <row r="948">
       <c r="A948" s="4"/>
-      <c r="F948" s="43"/>
+      <c r="F948" s="45"/>
       <c r="J948" s="4"/>
     </row>
     <row r="949">
       <c r="A949" s="4"/>
-      <c r="F949" s="43"/>
+      <c r="F949" s="45"/>
       <c r="J949" s="4"/>
     </row>
     <row r="950">
       <c r="A950" s="4"/>
-      <c r="F950" s="43"/>
+      <c r="F950" s="45"/>
       <c r="J950" s="4"/>
     </row>
     <row r="951">
       <c r="A951" s="4"/>
-      <c r="F951" s="43"/>
+      <c r="F951" s="45"/>
       <c r="J951" s="4"/>
     </row>
     <row r="952">
       <c r="A952" s="4"/>
-      <c r="F952" s="43"/>
+      <c r="F952" s="45"/>
       <c r="J952" s="4"/>
     </row>
     <row r="953">
       <c r="A953" s="4"/>
-      <c r="F953" s="43"/>
+      <c r="F953" s="45"/>
       <c r="J953" s="4"/>
     </row>
     <row r="954">
       <c r="A954" s="4"/>
-      <c r="F954" s="43"/>
+      <c r="F954" s="45"/>
       <c r="J954" s="4"/>
     </row>
     <row r="955">
       <c r="A955" s="4"/>
-      <c r="F955" s="43"/>
+      <c r="F955" s="45"/>
       <c r="J955" s="4"/>
     </row>
     <row r="956">
       <c r="A956" s="4"/>
-      <c r="F956" s="43"/>
+      <c r="F956" s="45"/>
       <c r="J956" s="4"/>
     </row>
     <row r="957">
       <c r="A957" s="4"/>
-      <c r="F957" s="43"/>
+      <c r="F957" s="45"/>
       <c r="J957" s="4"/>
     </row>
     <row r="958">
       <c r="A958" s="4"/>
-      <c r="F958" s="43"/>
+      <c r="F958" s="45"/>
       <c r="J958" s="4"/>
     </row>
     <row r="959">
       <c r="A959" s="4"/>
-      <c r="F959" s="43"/>
+      <c r="F959" s="45"/>
       <c r="J959" s="4"/>
     </row>
     <row r="960">
       <c r="A960" s="4"/>
-      <c r="F960" s="43"/>
+      <c r="F960" s="45"/>
       <c r="J960" s="4"/>
     </row>
     <row r="961">
       <c r="A961" s="4"/>
-      <c r="F961" s="43"/>
+      <c r="F961" s="45"/>
       <c r="J961" s="4"/>
     </row>
     <row r="962">
       <c r="A962" s="4"/>
-      <c r="F962" s="43"/>
+      <c r="F962" s="45"/>
       <c r="J962" s="4"/>
     </row>
     <row r="963">
       <c r="A963" s="4"/>
-      <c r="F963" s="43"/>
+      <c r="F963" s="45"/>
       <c r="J963" s="4"/>
     </row>
     <row r="964">
       <c r="A964" s="4"/>
-      <c r="F964" s="43"/>
+      <c r="F964" s="45"/>
       <c r="J964" s="4"/>
     </row>
     <row r="965">
       <c r="A965" s="4"/>
-      <c r="F965" s="43"/>
+      <c r="F965" s="45"/>
       <c r="J965" s="4"/>
     </row>
     <row r="966">
       <c r="A966" s="4"/>
-      <c r="F966" s="43"/>
+      <c r="F966" s="45"/>
       <c r="J966" s="4"/>
     </row>
     <row r="967">
       <c r="A967" s="4"/>
-      <c r="F967" s="43"/>
+      <c r="F967" s="45"/>
       <c r="J967" s="4"/>
     </row>
     <row r="968">
       <c r="A968" s="4"/>
-      <c r="F968" s="43"/>
+      <c r="F968" s="45"/>
       <c r="J968" s="4"/>
     </row>
     <row r="969">
       <c r="A969" s="4"/>
-      <c r="F969" s="43"/>
+      <c r="F969" s="45"/>
       <c r="J969" s="4"/>
     </row>
     <row r="970">
       <c r="A970" s="4"/>
-      <c r="F970" s="43"/>
+      <c r="F970" s="45"/>
       <c r="J970" s="4"/>
     </row>
     <row r="971">
       <c r="A971" s="4"/>
-      <c r="F971" s="43"/>
+      <c r="F971" s="45"/>
       <c r="J971" s="4"/>
     </row>
     <row r="972">
       <c r="A972" s="4"/>
-      <c r="F972" s="43"/>
+      <c r="F972" s="45"/>
       <c r="J972" s="4"/>
     </row>
     <row r="973">
       <c r="A973" s="4"/>
-      <c r="F973" s="43"/>
+      <c r="F973" s="45"/>
       <c r="J973" s="4"/>
     </row>
     <row r="974">
       <c r="A974" s="4"/>
-      <c r="F974" s="43"/>
+      <c r="F974" s="45"/>
       <c r="J974" s="4"/>
     </row>
     <row r="975">
       <c r="A975" s="4"/>
-      <c r="F975" s="43"/>
+      <c r="F975" s="45"/>
       <c r="J975" s="4"/>
     </row>
     <row r="976">
       <c r="A976" s="4"/>
-      <c r="F976" s="43"/>
+      <c r="F976" s="45"/>
       <c r="J976" s="4"/>
     </row>
     <row r="977">
       <c r="A977" s="4"/>
-      <c r="F977" s="43"/>
+      <c r="F977" s="45"/>
       <c r="J977" s="4"/>
     </row>
     <row r="978">
       <c r="A978" s="4"/>
-      <c r="F978" s="43"/>
+      <c r="F978" s="45"/>
       <c r="J978" s="4"/>
     </row>
     <row r="979">
       <c r="A979" s="4"/>
-      <c r="F979" s="43"/>
+      <c r="F979" s="45"/>
       <c r="J979" s="4"/>
     </row>
     <row r="980">
       <c r="A980" s="4"/>
-      <c r="F980" s="43"/>
+      <c r="F980" s="45"/>
       <c r="J980" s="4"/>
     </row>
     <row r="981">
       <c r="A981" s="4"/>
-      <c r="F981" s="43"/>
+      <c r="F981" s="45"/>
       <c r="J981" s="4"/>
     </row>
     <row r="982">
       <c r="A982" s="4"/>
-      <c r="F982" s="43"/>
+      <c r="F982" s="45"/>
       <c r="J982" s="4"/>
     </row>
     <row r="983">
       <c r="A983" s="4"/>
-      <c r="F983" s="43"/>
+      <c r="F983" s="45"/>
       <c r="J983" s="4"/>
     </row>
     <row r="984">
       <c r="A984" s="4"/>
-      <c r="F984" s="43"/>
+      <c r="F984" s="45"/>
       <c r="J984" s="4"/>
     </row>
     <row r="985">
       <c r="A985" s="4"/>
-      <c r="F985" s="43"/>
+      <c r="F985" s="45"/>
       <c r="J985" s="4"/>
     </row>
     <row r="986">
       <c r="A986" s="4"/>
-      <c r="F986" s="43"/>
+      <c r="F986" s="45"/>
       <c r="J986" s="4"/>
     </row>
     <row r="987">
       <c r="A987" s="4"/>
-      <c r="F987" s="43"/>
+      <c r="F987" s="45"/>
       <c r="J987" s="4"/>
     </row>
     <row r="988">
       <c r="A988" s="4"/>
-      <c r="F988" s="43"/>
+      <c r="F988" s="45"/>
       <c r="J988" s="4"/>
     </row>
     <row r="989">
       <c r="A989" s="4"/>
-      <c r="F989" s="43"/>
+      <c r="F989" s="45"/>
       <c r="J989" s="4"/>
     </row>
     <row r="990">
       <c r="A990" s="4"/>
-      <c r="F990" s="43"/>
+      <c r="F990" s="45"/>
       <c r="J990" s="4"/>
     </row>
     <row r="991">
       <c r="A991" s="4"/>
-      <c r="F991" s="43"/>
+      <c r="F991" s="45"/>
       <c r="J991" s="4"/>
     </row>
     <row r="992">
       <c r="A992" s="4"/>
-      <c r="F992" s="43"/>
+      <c r="F992" s="45"/>
       <c r="J992" s="4"/>
     </row>
     <row r="993">
       <c r="A993" s="4"/>
-      <c r="F993" s="43"/>
+      <c r="F993" s="45"/>
       <c r="J993" s="4"/>
     </row>
     <row r="994">
       <c r="A994" s="4"/>
-      <c r="F994" s="43"/>
+      <c r="F994" s="45"/>
       <c r="J994" s="4"/>
     </row>
     <row r="995">
       <c r="A995" s="4"/>
-      <c r="F995" s="43"/>
+      <c r="F995" s="45"/>
       <c r="J995" s="4"/>
     </row>
     <row r="996">
       <c r="A996" s="4"/>
-      <c r="F996" s="43"/>
+      <c r="F996" s="45"/>
       <c r="J996" s="4"/>
     </row>
     <row r="997">
       <c r="A997" s="4"/>
-      <c r="F997" s="43"/>
+      <c r="F997" s="45"/>
       <c r="J997" s="4"/>
     </row>
     <row r="998">
       <c r="A998" s="4"/>
-      <c r="F998" s="43"/>
+      <c r="F998" s="45"/>
       <c r="J998" s="4"/>
     </row>
     <row r="999">
       <c r="A999" s="4"/>
-      <c r="F999" s="43"/>
+      <c r="F999" s="45"/>
       <c r="J999" s="4"/>
     </row>
   </sheetData>
   <mergeCells count="19">
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="A2:G2"/>
+    <mergeCell ref="C33:D33"/>
     <mergeCell ref="F33:G33"/>
     <mergeCell ref="C34:D34"/>
     <mergeCell ref="F34:G34"/>
+    <mergeCell ref="F35:G35"/>
+    <mergeCell ref="C77:D77"/>
+    <mergeCell ref="C78:D78"/>
+    <mergeCell ref="C79:D79"/>
+    <mergeCell ref="F78:G78"/>
+    <mergeCell ref="F79:G79"/>
     <mergeCell ref="C35:D35"/>
     <mergeCell ref="C36:D36"/>
     <mergeCell ref="C37:G37"/>
-    <mergeCell ref="F77:G77"/>
-    <mergeCell ref="F78:G78"/>
-    <mergeCell ref="C79:D79"/>
-    <mergeCell ref="F79:G79"/>
-    <mergeCell ref="F35:G35"/>
-    <mergeCell ref="F36:G36"/>
     <mergeCell ref="C48:G48"/>
     <mergeCell ref="C76:D76"/>
     <mergeCell ref="F76:G76"/>
-    <mergeCell ref="C77:D77"/>
-    <mergeCell ref="C78:D78"/>
+    <mergeCell ref="F77:G77"/>
   </mergeCells>
   <drawing r:id="rId1"/>
 </worksheet>

--- a/MBA BA 2026-28 Term I Schedule .xlsx
+++ b/MBA BA 2026-28 Term I Schedule .xlsx
@@ -218,14 +218,16 @@
     <t>MC - 8 (Prof Kakoli Sen)</t>
   </si>
   <si>
-    <t>DS-I - 9 (Guest Session)</t>
+    <t>DS-I - 9 (Guest Session) by 
+ Dr. Muralidhara (JMP)</t>
   </si>
   <si>
     <t>Prof. Kaushik Bhattacharya
 BE_07</t>
   </si>
   <si>
-    <t>DS-I - 10 (Guest Session)</t>
+    <t>DS-I - 10 (Guest Session) by
+Dr. Muralidhara (JMP)</t>
   </si>
   <si>
     <t xml:space="preserve">MM - 9 (Prof. Atul Prashar) </t>
@@ -891,7 +893,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="84">
+  <cellXfs count="85">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -974,6 +976,9 @@
     </xf>
     <xf borderId="5" fillId="11" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" vertical="center"/>
+    </xf>
+    <xf borderId="5" fillId="8" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="5" fillId="10" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
@@ -1833,7 +1838,7 @@
         <v>65</v>
       </c>
       <c r="E25" s="15"/>
-      <c r="F25" s="19" t="s">
+      <c r="F25" s="29" t="s">
         <v>66</v>
       </c>
       <c r="G25" s="17"/>
@@ -1849,7 +1854,7 @@
       <c r="C26" s="28" t="s">
         <v>67</v>
       </c>
-      <c r="D26" s="19" t="s">
+      <c r="D26" s="29" t="s">
         <v>68</v>
       </c>
       <c r="E26" s="15"/>
@@ -1947,7 +1952,7 @@
       <c r="B31" s="12" t="s">
         <v>31</v>
       </c>
-      <c r="C31" s="29" t="s">
+      <c r="C31" s="30" t="s">
         <v>83</v>
       </c>
       <c r="D31" s="28" t="s">
@@ -1977,81 +1982,81 @@
       <c r="J32" s="4"/>
     </row>
     <row r="33">
-      <c r="A33" s="30">
+      <c r="A33" s="31">
         <v>46245.0</v>
       </c>
-      <c r="B33" s="31" t="s">
+      <c r="B33" s="32" t="s">
         <v>13</v>
       </c>
-      <c r="C33" s="32" t="s">
+      <c r="C33" s="33" t="s">
         <v>87</v>
       </c>
       <c r="D33" s="3"/>
-      <c r="E33" s="33"/>
-      <c r="F33" s="32" t="s">
+      <c r="E33" s="34"/>
+      <c r="F33" s="33" t="s">
         <v>88</v>
       </c>
       <c r="G33" s="3"/>
       <c r="J33" s="4"/>
     </row>
     <row r="34">
-      <c r="A34" s="30">
+      <c r="A34" s="31">
         <v>46246.0</v>
       </c>
-      <c r="B34" s="31" t="s">
+      <c r="B34" s="32" t="s">
         <v>17</v>
       </c>
-      <c r="C34" s="32" t="s">
+      <c r="C34" s="33" t="s">
         <v>89</v>
       </c>
       <c r="D34" s="3"/>
-      <c r="E34" s="33"/>
-      <c r="F34" s="32" t="s">
+      <c r="E34" s="34"/>
+      <c r="F34" s="33" t="s">
         <v>90</v>
       </c>
       <c r="G34" s="3"/>
       <c r="J34" s="4"/>
     </row>
     <row r="35">
-      <c r="A35" s="30">
+      <c r="A35" s="31">
         <v>46247.0</v>
       </c>
-      <c r="B35" s="31" t="s">
+      <c r="B35" s="32" t="s">
         <v>21</v>
       </c>
-      <c r="C35" s="32" t="s">
+      <c r="C35" s="33" t="s">
         <v>91</v>
       </c>
       <c r="D35" s="3"/>
-      <c r="E35" s="33"/>
-      <c r="F35" s="32" t="s">
+      <c r="E35" s="34"/>
+      <c r="F35" s="33" t="s">
         <v>92</v>
       </c>
       <c r="G35" s="3"/>
       <c r="J35" s="4"/>
     </row>
     <row r="36">
-      <c r="A36" s="30">
+      <c r="A36" s="31">
         <v>46248.0</v>
       </c>
-      <c r="B36" s="31" t="s">
+      <c r="B36" s="32" t="s">
         <v>25</v>
       </c>
-      <c r="C36" s="32" t="s">
+      <c r="C36" s="33" t="s">
         <v>93</v>
       </c>
       <c r="D36" s="3"/>
-      <c r="E36" s="33"/>
+      <c r="E36" s="34"/>
       <c r="J36" s="4"/>
     </row>
     <row r="37" ht="21.0" customHeight="1">
-      <c r="A37" s="34">
+      <c r="A37" s="35">
         <v>46249.0</v>
       </c>
-      <c r="B37" s="35" t="s">
+      <c r="B37" s="36" t="s">
         <v>28</v>
       </c>
-      <c r="C37" s="36" t="s">
+      <c r="C37" s="37" t="s">
         <v>94</v>
       </c>
       <c r="D37" s="2"/>
@@ -2081,7 +2086,7 @@
       <c r="B39" s="12" t="s">
         <v>32</v>
       </c>
-      <c r="C39" s="37" t="s">
+      <c r="C39" s="38" t="s">
         <v>95</v>
       </c>
       <c r="D39" s="18" t="s">
@@ -2101,7 +2106,7 @@
       <c r="B40" s="12" t="s">
         <v>13</v>
       </c>
-      <c r="C40" s="37" t="s">
+      <c r="C40" s="38" t="s">
         <v>98</v>
       </c>
       <c r="D40" s="16" t="s">
@@ -2121,7 +2126,7 @@
       <c r="B41" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="C41" s="37" t="s">
+      <c r="C41" s="38" t="s">
         <v>101</v>
       </c>
       <c r="D41" s="18" t="s">
@@ -2141,7 +2146,7 @@
       <c r="B42" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="C42" s="37" t="s">
+      <c r="C42" s="38" t="s">
         <v>104</v>
       </c>
       <c r="D42" s="26" t="s">
@@ -2215,7 +2220,7 @@
       <c r="B46" s="12" t="s">
         <v>32</v>
       </c>
-      <c r="C46" s="38" t="s">
+      <c r="C46" s="39" t="s">
         <v>113</v>
       </c>
       <c r="D46" s="16" t="s">
@@ -2247,13 +2252,13 @@
       <c r="J47" s="4"/>
     </row>
     <row r="48" ht="27.75" customHeight="1">
-      <c r="A48" s="39">
+      <c r="A48" s="40">
         <v>46260.0</v>
       </c>
-      <c r="B48" s="40" t="s">
+      <c r="B48" s="41" t="s">
         <v>17</v>
       </c>
-      <c r="C48" s="41" t="s">
+      <c r="C48" s="42" t="s">
         <v>118</v>
       </c>
       <c r="D48" s="2"/>
@@ -2269,7 +2274,7 @@
       <c r="B49" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="C49" s="38" t="s">
+      <c r="C49" s="39" t="s">
         <v>119</v>
       </c>
       <c r="D49" s="16" t="s">
@@ -2333,7 +2338,7 @@
       <c r="B53" s="12" t="s">
         <v>32</v>
       </c>
-      <c r="C53" s="37" t="s">
+      <c r="C53" s="38" t="s">
         <v>123</v>
       </c>
       <c r="D53" s="16" t="s">
@@ -2353,10 +2358,10 @@
       <c r="B54" s="12" t="s">
         <v>13</v>
       </c>
-      <c r="C54" s="37" t="s">
+      <c r="C54" s="38" t="s">
         <v>126</v>
       </c>
-      <c r="D54" s="38" t="s">
+      <c r="D54" s="39" t="s">
         <v>127</v>
       </c>
       <c r="E54" s="15"/>
@@ -2373,7 +2378,7 @@
       <c r="B55" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="C55" s="37" t="s">
+      <c r="C55" s="38" t="s">
         <v>129</v>
       </c>
       <c r="D55" s="13" t="s">
@@ -2421,7 +2426,7 @@
       <c r="F57" s="19" t="s">
         <v>136</v>
       </c>
-      <c r="G57" s="42"/>
+      <c r="G57" s="43"/>
       <c r="J57" s="4"/>
     </row>
     <row r="58">
@@ -2465,7 +2470,7 @@
       <c r="B60" s="12" t="s">
         <v>32</v>
       </c>
-      <c r="C60" s="38" t="s">
+      <c r="C60" s="39" t="s">
         <v>140</v>
       </c>
       <c r="D60" s="16" t="s">
@@ -2486,7 +2491,7 @@
         <v>13</v>
       </c>
       <c r="C61" s="9"/>
-      <c r="D61" s="38" t="s">
+      <c r="D61" s="39" t="s">
         <v>143</v>
       </c>
       <c r="E61" s="15"/>
@@ -2501,7 +2506,7 @@
       <c r="B62" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="C62" s="37" t="s">
+      <c r="C62" s="38" t="s">
         <v>144</v>
       </c>
       <c r="D62" s="16" t="s">
@@ -2521,14 +2526,14 @@
       <c r="B63" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="C63" s="38" t="s">
+      <c r="C63" s="39" t="s">
         <v>147</v>
       </c>
       <c r="D63" s="13" t="s">
         <v>148</v>
       </c>
       <c r="E63" s="15"/>
-      <c r="F63" s="37" t="s">
+      <c r="F63" s="38" t="s">
         <v>149</v>
       </c>
       <c r="G63" s="17"/>
@@ -2541,7 +2546,7 @@
       <c r="B64" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="C64" s="37" t="s">
+      <c r="C64" s="38" t="s">
         <v>150</v>
       </c>
       <c r="D64" s="18" t="s">
@@ -2587,7 +2592,7 @@
       <c r="B67" s="12" t="s">
         <v>32</v>
       </c>
-      <c r="C67" s="38" t="s">
+      <c r="C67" s="39" t="s">
         <v>152</v>
       </c>
       <c r="D67" s="18" t="s">
@@ -2605,7 +2610,7 @@
       <c r="B68" s="12" t="s">
         <v>13</v>
       </c>
-      <c r="C68" s="38" t="s">
+      <c r="C68" s="39" t="s">
         <v>154</v>
       </c>
       <c r="D68" s="18" t="s">
@@ -2668,7 +2673,7 @@
         <v>162</v>
       </c>
       <c r="E71" s="15"/>
-      <c r="F71" s="38" t="s">
+      <c r="F71" s="39" t="s">
         <v>163</v>
       </c>
       <c r="G71" s="17"/>
@@ -2681,7 +2686,7 @@
       <c r="B72" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="C72" s="38" t="s">
+      <c r="C72" s="39" t="s">
         <v>164</v>
       </c>
       <c r="D72" s="18" t="s">
@@ -2716,7 +2721,7 @@
       <c r="C74" s="17"/>
       <c r="D74" s="17"/>
       <c r="E74" s="15"/>
-      <c r="F74" s="43"/>
+      <c r="F74" s="44"/>
       <c r="G74" s="17"/>
       <c r="J74" s="4"/>
     </row>
@@ -2730,140 +2735,140 @@
       <c r="C75" s="17"/>
       <c r="D75" s="17"/>
       <c r="E75" s="15"/>
-      <c r="F75" s="43"/>
+      <c r="F75" s="44"/>
       <c r="G75" s="17"/>
       <c r="J75" s="4"/>
     </row>
     <row r="76">
-      <c r="A76" s="30">
+      <c r="A76" s="31">
         <v>46288.0</v>
       </c>
-      <c r="B76" s="31" t="s">
+      <c r="B76" s="32" t="s">
         <v>17</v>
       </c>
-      <c r="C76" s="32" t="s">
+      <c r="C76" s="33" t="s">
         <v>166</v>
       </c>
       <c r="D76" s="3"/>
-      <c r="E76" s="33"/>
-      <c r="F76" s="32" t="s">
+      <c r="E76" s="34"/>
+      <c r="F76" s="33" t="s">
         <v>166</v>
       </c>
       <c r="G76" s="3"/>
       <c r="J76" s="4"/>
     </row>
     <row r="77">
-      <c r="A77" s="30">
+      <c r="A77" s="31">
         <v>46289.0</v>
       </c>
-      <c r="B77" s="31" t="s">
+      <c r="B77" s="32" t="s">
         <v>21</v>
       </c>
-      <c r="C77" s="32" t="s">
+      <c r="C77" s="33" t="s">
         <v>166</v>
       </c>
       <c r="D77" s="3"/>
-      <c r="E77" s="33"/>
-      <c r="F77" s="32" t="s">
+      <c r="E77" s="34"/>
+      <c r="F77" s="33" t="s">
         <v>166</v>
       </c>
       <c r="G77" s="3"/>
       <c r="J77" s="4"/>
     </row>
     <row r="78">
-      <c r="A78" s="30">
+      <c r="A78" s="31">
         <v>46290.0</v>
       </c>
-      <c r="B78" s="31" t="s">
+      <c r="B78" s="32" t="s">
         <v>25</v>
       </c>
-      <c r="C78" s="32" t="s">
+      <c r="C78" s="33" t="s">
         <v>166</v>
       </c>
       <c r="D78" s="3"/>
-      <c r="E78" s="33"/>
-      <c r="F78" s="32" t="s">
+      <c r="E78" s="34"/>
+      <c r="F78" s="33" t="s">
         <v>166</v>
       </c>
       <c r="G78" s="3"/>
       <c r="J78" s="4"/>
     </row>
     <row r="79">
-      <c r="A79" s="30">
+      <c r="A79" s="31">
         <v>46291.0</v>
       </c>
-      <c r="B79" s="31" t="s">
+      <c r="B79" s="32" t="s">
         <v>28</v>
       </c>
-      <c r="C79" s="32" t="s">
+      <c r="C79" s="33" t="s">
         <v>167</v>
       </c>
       <c r="D79" s="3"/>
-      <c r="E79" s="33"/>
-      <c r="F79" s="32"/>
+      <c r="E79" s="34"/>
+      <c r="F79" s="33"/>
       <c r="G79" s="3"/>
       <c r="J79" s="4"/>
     </row>
     <row r="80">
-      <c r="A80" s="44"/>
-      <c r="F80" s="45"/>
+      <c r="A80" s="45"/>
+      <c r="F80" s="46"/>
       <c r="J80" s="4"/>
     </row>
     <row r="81">
-      <c r="A81" s="44"/>
-      <c r="F81" s="45"/>
+      <c r="A81" s="45"/>
+      <c r="F81" s="46"/>
       <c r="J81" s="4"/>
     </row>
     <row r="82">
-      <c r="A82" s="46" t="s">
+      <c r="A82" s="47" t="s">
         <v>168</v>
       </c>
-      <c r="B82" s="47" t="s">
+      <c r="B82" s="48" t="s">
         <v>169</v>
       </c>
-      <c r="C82" s="46" t="s">
+      <c r="C82" s="47" t="s">
         <v>170</v>
       </c>
-      <c r="D82" s="46" t="s">
+      <c r="D82" s="47" t="s">
         <v>171</v>
       </c>
-      <c r="E82" s="46" t="s">
+      <c r="E82" s="47" t="s">
         <v>172</v>
       </c>
-      <c r="F82" s="47" t="s">
+      <c r="F82" s="48" t="s">
         <v>173</v>
       </c>
-      <c r="G82" s="48" t="s">
+      <c r="G82" s="49" t="s">
         <v>174</v>
       </c>
-      <c r="H82" s="48" t="s">
+      <c r="H82" s="49" t="s">
         <v>175</v>
       </c>
-      <c r="I82" s="48" t="s">
+      <c r="I82" s="49" t="s">
         <v>176</v>
       </c>
       <c r="J82" s="4"/>
     </row>
     <row r="83">
-      <c r="A83" s="49">
+      <c r="A83" s="50">
         <v>1.0</v>
       </c>
-      <c r="B83" s="50" t="s">
+      <c r="B83" s="51" t="s">
         <v>177</v>
       </c>
-      <c r="C83" s="49">
+      <c r="C83" s="50">
         <v>3.0</v>
       </c>
-      <c r="D83" s="51" t="s">
+      <c r="D83" s="52" t="s">
         <v>178</v>
       </c>
-      <c r="E83" s="51" t="s">
+      <c r="E83" s="52" t="s">
         <v>179</v>
       </c>
-      <c r="F83" s="52" t="s">
+      <c r="F83" s="53" t="s">
         <v>180</v>
       </c>
-      <c r="G83" s="37"/>
+      <c r="G83" s="38"/>
       <c r="H83" s="17"/>
       <c r="I83" s="12" t="s">
         <v>181</v>
@@ -2884,48 +2889,48 @@
       <c r="W83" s="9"/>
     </row>
     <row r="84">
-      <c r="A84" s="53">
+      <c r="A84" s="54">
         <v>2.0</v>
       </c>
-      <c r="B84" s="54" t="s">
+      <c r="B84" s="55" t="s">
         <v>182</v>
       </c>
-      <c r="C84" s="53">
+      <c r="C84" s="54">
         <v>3.0</v>
       </c>
-      <c r="D84" s="55" t="s">
+      <c r="D84" s="56" t="s">
         <v>183</v>
       </c>
-      <c r="E84" s="55" t="s">
+      <c r="E84" s="56" t="s">
         <v>184</v>
       </c>
-      <c r="F84" s="54" t="s">
+      <c r="F84" s="55" t="s">
         <v>185</v>
       </c>
-      <c r="G84" s="56"/>
-      <c r="H84" s="42"/>
-      <c r="I84" s="48" t="s">
+      <c r="G84" s="57"/>
+      <c r="H84" s="43"/>
+      <c r="I84" s="49" t="s">
         <v>186</v>
       </c>
       <c r="J84" s="4"/>
     </row>
     <row r="85">
-      <c r="A85" s="57">
+      <c r="A85" s="58">
         <v>3.0</v>
       </c>
-      <c r="B85" s="58" t="s">
+      <c r="B85" s="59" t="s">
         <v>187</v>
       </c>
-      <c r="C85" s="57">
+      <c r="C85" s="58">
         <v>3.0</v>
       </c>
-      <c r="D85" s="59" t="s">
+      <c r="D85" s="60" t="s">
         <v>188</v>
       </c>
-      <c r="E85" s="59" t="s">
+      <c r="E85" s="60" t="s">
         <v>189</v>
       </c>
-      <c r="F85" s="60" t="s">
+      <c r="F85" s="61" t="s">
         <v>190</v>
       </c>
       <c r="G85" s="13"/>
@@ -2949,4678 +2954,4678 @@
       <c r="W85" s="9"/>
     </row>
     <row r="86">
-      <c r="A86" s="61">
+      <c r="A86" s="62">
         <v>4.0</v>
       </c>
-      <c r="B86" s="62" t="s">
+      <c r="B86" s="63" t="s">
         <v>192</v>
       </c>
-      <c r="C86" s="61">
+      <c r="C86" s="62">
         <v>1.5</v>
       </c>
-      <c r="D86" s="63" t="s">
+      <c r="D86" s="64" t="s">
         <v>193</v>
       </c>
-      <c r="E86" s="63" t="s">
+      <c r="E86" s="64" t="s">
         <v>194</v>
       </c>
-      <c r="F86" s="62" t="s">
+      <c r="F86" s="63" t="s">
         <v>195</v>
       </c>
-      <c r="G86" s="64"/>
-      <c r="H86" s="42"/>
-      <c r="I86" s="48" t="s">
+      <c r="G86" s="65"/>
+      <c r="H86" s="43"/>
+      <c r="I86" s="49" t="s">
         <v>196</v>
       </c>
       <c r="J86" s="4"/>
     </row>
     <row r="87">
-      <c r="A87" s="65">
+      <c r="A87" s="66">
         <v>5.0</v>
       </c>
-      <c r="B87" s="66" t="s">
+      <c r="B87" s="67" t="s">
         <v>197</v>
       </c>
-      <c r="C87" s="65">
+      <c r="C87" s="66">
         <v>3.0</v>
       </c>
-      <c r="D87" s="67" t="s">
+      <c r="D87" s="68" t="s">
         <v>178</v>
       </c>
-      <c r="E87" s="67" t="s">
+      <c r="E87" s="68" t="s">
         <v>198</v>
       </c>
-      <c r="F87" s="68" t="s">
+      <c r="F87" s="69" t="s">
         <v>199</v>
       </c>
-      <c r="G87" s="69"/>
-      <c r="H87" s="42"/>
-      <c r="I87" s="48" t="s">
+      <c r="G87" s="70"/>
+      <c r="H87" s="43"/>
+      <c r="I87" s="49" t="s">
         <v>200</v>
       </c>
       <c r="J87" s="4"/>
     </row>
     <row r="88">
-      <c r="A88" s="70">
+      <c r="A88" s="71">
         <v>6.0</v>
       </c>
-      <c r="B88" s="71" t="s">
+      <c r="B88" s="72" t="s">
         <v>201</v>
       </c>
-      <c r="C88" s="70">
+      <c r="C88" s="71">
         <v>1.5</v>
       </c>
-      <c r="D88" s="72" t="s">
+      <c r="D88" s="73" t="s">
         <v>193</v>
       </c>
-      <c r="E88" s="72" t="s">
+      <c r="E88" s="73" t="s">
         <v>202</v>
       </c>
-      <c r="F88" s="71" t="s">
+      <c r="F88" s="72" t="s">
         <v>203</v>
       </c>
-      <c r="G88" s="73"/>
-      <c r="H88" s="42"/>
-      <c r="I88" s="48" t="s">
+      <c r="G88" s="74"/>
+      <c r="H88" s="43"/>
+      <c r="I88" s="49" t="s">
         <v>204</v>
       </c>
       <c r="J88" s="4"/>
     </row>
     <row r="89">
-      <c r="A89" s="74">
+      <c r="A89" s="75">
         <v>7.0</v>
       </c>
-      <c r="B89" s="75" t="s">
+      <c r="B89" s="76" t="s">
         <v>205</v>
       </c>
-      <c r="C89" s="74">
+      <c r="C89" s="75">
         <v>3.0</v>
       </c>
-      <c r="D89" s="76" t="s">
+      <c r="D89" s="77" t="s">
         <v>206</v>
       </c>
-      <c r="E89" s="76" t="s">
+      <c r="E89" s="77" t="s">
         <v>207</v>
       </c>
-      <c r="F89" s="77" t="s">
+      <c r="F89" s="78" t="s">
         <v>208</v>
       </c>
-      <c r="G89" s="78"/>
-      <c r="H89" s="42"/>
-      <c r="I89" s="48" t="s">
+      <c r="G89" s="79"/>
+      <c r="H89" s="43"/>
+      <c r="I89" s="49" t="s">
         <v>209</v>
       </c>
       <c r="J89" s="4"/>
     </row>
     <row r="90">
-      <c r="A90" s="79">
+      <c r="A90" s="80">
         <v>8.0</v>
       </c>
-      <c r="B90" s="80" t="s">
+      <c r="B90" s="81" t="s">
         <v>210</v>
       </c>
-      <c r="C90" s="79">
+      <c r="C90" s="80">
         <v>3.0</v>
       </c>
-      <c r="D90" s="81" t="s">
+      <c r="D90" s="82" t="s">
         <v>211</v>
       </c>
-      <c r="E90" s="81" t="s">
+      <c r="E90" s="82" t="s">
         <v>212</v>
       </c>
-      <c r="F90" s="82" t="s">
+      <c r="F90" s="83" t="s">
         <v>213</v>
       </c>
-      <c r="G90" s="83"/>
-      <c r="H90" s="42"/>
-      <c r="I90" s="48" t="s">
+      <c r="G90" s="84"/>
+      <c r="H90" s="43"/>
+      <c r="I90" s="49" t="s">
         <v>214</v>
       </c>
       <c r="J90" s="4"/>
     </row>
     <row r="91">
-      <c r="A91" s="44"/>
-      <c r="F91" s="45"/>
+      <c r="A91" s="45"/>
+      <c r="F91" s="46"/>
       <c r="J91" s="4"/>
     </row>
     <row r="92">
-      <c r="A92" s="44"/>
-      <c r="F92" s="45"/>
+      <c r="A92" s="45"/>
+      <c r="F92" s="46"/>
       <c r="J92" s="4"/>
     </row>
     <row r="93">
-      <c r="A93" s="44"/>
-      <c r="F93" s="45"/>
+      <c r="A93" s="45"/>
+      <c r="F93" s="46"/>
       <c r="J93" s="4"/>
     </row>
     <row r="94">
-      <c r="A94" s="44"/>
-      <c r="F94" s="45"/>
+      <c r="A94" s="45"/>
+      <c r="F94" s="46"/>
       <c r="J94" s="4"/>
     </row>
     <row r="95">
-      <c r="A95" s="44"/>
-      <c r="F95" s="45"/>
+      <c r="A95" s="45"/>
+      <c r="F95" s="46"/>
       <c r="J95" s="4"/>
     </row>
     <row r="96">
-      <c r="A96" s="44"/>
-      <c r="F96" s="45"/>
+      <c r="A96" s="45"/>
+      <c r="F96" s="46"/>
       <c r="J96" s="4"/>
     </row>
     <row r="97">
-      <c r="A97" s="44"/>
-      <c r="F97" s="45"/>
+      <c r="A97" s="45"/>
+      <c r="F97" s="46"/>
       <c r="J97" s="4"/>
     </row>
     <row r="98">
-      <c r="A98" s="44"/>
-      <c r="F98" s="45"/>
+      <c r="A98" s="45"/>
+      <c r="F98" s="46"/>
       <c r="J98" s="4"/>
     </row>
     <row r="99">
-      <c r="A99" s="44"/>
-      <c r="F99" s="45"/>
+      <c r="A99" s="45"/>
+      <c r="F99" s="46"/>
       <c r="J99" s="4"/>
     </row>
     <row r="100">
-      <c r="A100" s="44"/>
-      <c r="F100" s="45"/>
+      <c r="A100" s="45"/>
+      <c r="F100" s="46"/>
       <c r="J100" s="4"/>
     </row>
     <row r="101">
-      <c r="A101" s="44"/>
-      <c r="F101" s="45"/>
+      <c r="A101" s="45"/>
+      <c r="F101" s="46"/>
       <c r="J101" s="4"/>
     </row>
     <row r="102">
-      <c r="A102" s="44"/>
-      <c r="F102" s="45"/>
+      <c r="A102" s="45"/>
+      <c r="F102" s="46"/>
       <c r="J102" s="4"/>
     </row>
     <row r="103">
-      <c r="A103" s="44"/>
-      <c r="F103" s="45"/>
+      <c r="A103" s="45"/>
+      <c r="F103" s="46"/>
       <c r="J103" s="4"/>
     </row>
     <row r="104">
-      <c r="A104" s="44"/>
-      <c r="F104" s="45"/>
+      <c r="A104" s="45"/>
+      <c r="F104" s="46"/>
       <c r="J104" s="4"/>
     </row>
     <row r="105">
-      <c r="A105" s="44"/>
-      <c r="F105" s="45"/>
+      <c r="A105" s="45"/>
+      <c r="F105" s="46"/>
       <c r="J105" s="4"/>
     </row>
     <row r="106">
-      <c r="A106" s="44"/>
-      <c r="F106" s="45"/>
+      <c r="A106" s="45"/>
+      <c r="F106" s="46"/>
       <c r="J106" s="4"/>
     </row>
     <row r="107">
-      <c r="A107" s="44"/>
-      <c r="F107" s="45"/>
+      <c r="A107" s="45"/>
+      <c r="F107" s="46"/>
       <c r="J107" s="4"/>
     </row>
     <row r="108">
-      <c r="A108" s="44"/>
-      <c r="F108" s="45"/>
+      <c r="A108" s="45"/>
+      <c r="F108" s="46"/>
       <c r="J108" s="4"/>
     </row>
     <row r="109">
-      <c r="A109" s="44"/>
-      <c r="F109" s="45"/>
+      <c r="A109" s="45"/>
+      <c r="F109" s="46"/>
       <c r="J109" s="4"/>
     </row>
     <row r="110">
-      <c r="A110" s="44"/>
-      <c r="F110" s="45"/>
+      <c r="A110" s="45"/>
+      <c r="F110" s="46"/>
       <c r="J110" s="4"/>
     </row>
     <row r="111">
-      <c r="A111" s="44"/>
-      <c r="F111" s="45"/>
+      <c r="A111" s="45"/>
+      <c r="F111" s="46"/>
       <c r="J111" s="4"/>
     </row>
     <row r="112">
-      <c r="A112" s="44"/>
-      <c r="F112" s="45"/>
+      <c r="A112" s="45"/>
+      <c r="F112" s="46"/>
       <c r="J112" s="4"/>
     </row>
     <row r="113">
-      <c r="A113" s="44"/>
-      <c r="F113" s="45"/>
+      <c r="A113" s="45"/>
+      <c r="F113" s="46"/>
       <c r="J113" s="4"/>
     </row>
     <row r="114">
-      <c r="A114" s="44"/>
-      <c r="F114" s="45"/>
+      <c r="A114" s="45"/>
+      <c r="F114" s="46"/>
       <c r="J114" s="4"/>
     </row>
     <row r="115">
-      <c r="A115" s="44"/>
-      <c r="F115" s="45"/>
+      <c r="A115" s="45"/>
+      <c r="F115" s="46"/>
       <c r="J115" s="4"/>
     </row>
     <row r="116">
-      <c r="A116" s="44"/>
-      <c r="F116" s="45"/>
+      <c r="A116" s="45"/>
+      <c r="F116" s="46"/>
       <c r="J116" s="4"/>
     </row>
     <row r="117">
-      <c r="A117" s="44"/>
-      <c r="F117" s="45"/>
+      <c r="A117" s="45"/>
+      <c r="F117" s="46"/>
       <c r="J117" s="4"/>
     </row>
     <row r="118">
       <c r="A118" s="4"/>
-      <c r="F118" s="45"/>
+      <c r="F118" s="46"/>
       <c r="J118" s="4"/>
     </row>
     <row r="119">
       <c r="A119" s="4"/>
-      <c r="F119" s="45"/>
+      <c r="F119" s="46"/>
       <c r="J119" s="4"/>
     </row>
     <row r="120">
       <c r="A120" s="4"/>
-      <c r="F120" s="45"/>
+      <c r="F120" s="46"/>
       <c r="J120" s="4"/>
     </row>
     <row r="121">
       <c r="A121" s="4"/>
-      <c r="F121" s="45"/>
+      <c r="F121" s="46"/>
       <c r="J121" s="4"/>
     </row>
     <row r="122">
       <c r="A122" s="4"/>
-      <c r="F122" s="45"/>
+      <c r="F122" s="46"/>
       <c r="J122" s="4"/>
     </row>
     <row r="123">
       <c r="A123" s="4"/>
-      <c r="F123" s="45"/>
+      <c r="F123" s="46"/>
       <c r="J123" s="4"/>
     </row>
     <row r="124">
       <c r="A124" s="4"/>
-      <c r="F124" s="45"/>
+      <c r="F124" s="46"/>
       <c r="J124" s="4"/>
     </row>
     <row r="125">
       <c r="A125" s="4"/>
-      <c r="F125" s="45"/>
+      <c r="F125" s="46"/>
       <c r="J125" s="4"/>
     </row>
     <row r="126">
       <c r="A126" s="4"/>
-      <c r="F126" s="45"/>
+      <c r="F126" s="46"/>
       <c r="J126" s="4"/>
     </row>
     <row r="127">
       <c r="A127" s="4"/>
-      <c r="F127" s="45"/>
+      <c r="F127" s="46"/>
       <c r="J127" s="4"/>
     </row>
     <row r="128">
       <c r="A128" s="4"/>
-      <c r="F128" s="45"/>
+      <c r="F128" s="46"/>
       <c r="J128" s="4"/>
     </row>
     <row r="129">
       <c r="A129" s="4"/>
-      <c r="F129" s="45"/>
+      <c r="F129" s="46"/>
       <c r="J129" s="4"/>
     </row>
     <row r="130">
       <c r="A130" s="4"/>
-      <c r="F130" s="45"/>
+      <c r="F130" s="46"/>
       <c r="J130" s="4"/>
     </row>
     <row r="131">
       <c r="A131" s="4"/>
-      <c r="F131" s="45"/>
+      <c r="F131" s="46"/>
       <c r="J131" s="4"/>
     </row>
     <row r="132">
       <c r="A132" s="4"/>
-      <c r="F132" s="45"/>
+      <c r="F132" s="46"/>
       <c r="J132" s="4"/>
     </row>
     <row r="133">
       <c r="A133" s="4"/>
-      <c r="F133" s="45"/>
+      <c r="F133" s="46"/>
       <c r="J133" s="4"/>
     </row>
     <row r="134">
       <c r="A134" s="4"/>
-      <c r="F134" s="45"/>
+      <c r="F134" s="46"/>
       <c r="J134" s="4"/>
     </row>
     <row r="135">
       <c r="A135" s="4"/>
-      <c r="F135" s="45"/>
+      <c r="F135" s="46"/>
       <c r="J135" s="4"/>
     </row>
     <row r="136">
       <c r="A136" s="4"/>
-      <c r="F136" s="45"/>
+      <c r="F136" s="46"/>
       <c r="J136" s="4"/>
     </row>
     <row r="137">
       <c r="A137" s="4"/>
-      <c r="F137" s="45"/>
+      <c r="F137" s="46"/>
       <c r="J137" s="4"/>
     </row>
     <row r="138">
       <c r="A138" s="4"/>
-      <c r="F138" s="45"/>
+      <c r="F138" s="46"/>
       <c r="J138" s="4"/>
     </row>
     <row r="139">
       <c r="A139" s="4"/>
-      <c r="F139" s="45"/>
+      <c r="F139" s="46"/>
       <c r="J139" s="4"/>
     </row>
     <row r="140">
       <c r="A140" s="4"/>
-      <c r="F140" s="45"/>
+      <c r="F140" s="46"/>
       <c r="J140" s="4"/>
     </row>
     <row r="141">
       <c r="A141" s="4"/>
-      <c r="F141" s="45"/>
+      <c r="F141" s="46"/>
       <c r="J141" s="4"/>
     </row>
     <row r="142">
       <c r="A142" s="4"/>
-      <c r="F142" s="45"/>
+      <c r="F142" s="46"/>
       <c r="J142" s="4"/>
     </row>
     <row r="143">
       <c r="A143" s="4"/>
-      <c r="F143" s="45"/>
+      <c r="F143" s="46"/>
       <c r="J143" s="4"/>
     </row>
     <row r="144">
       <c r="A144" s="4"/>
-      <c r="F144" s="45"/>
+      <c r="F144" s="46"/>
       <c r="J144" s="4"/>
     </row>
     <row r="145">
       <c r="A145" s="4"/>
-      <c r="F145" s="45"/>
+      <c r="F145" s="46"/>
       <c r="J145" s="4"/>
     </row>
     <row r="146">
       <c r="A146" s="4"/>
-      <c r="F146" s="45"/>
+      <c r="F146" s="46"/>
       <c r="J146" s="4"/>
     </row>
     <row r="147">
       <c r="A147" s="4"/>
-      <c r="F147" s="45"/>
+      <c r="F147" s="46"/>
       <c r="J147" s="4"/>
     </row>
     <row r="148">
       <c r="A148" s="4"/>
-      <c r="F148" s="45"/>
+      <c r="F148" s="46"/>
       <c r="J148" s="4"/>
     </row>
     <row r="149">
       <c r="A149" s="4"/>
-      <c r="F149" s="45"/>
+      <c r="F149" s="46"/>
       <c r="J149" s="4"/>
     </row>
     <row r="150">
       <c r="A150" s="4"/>
-      <c r="F150" s="45"/>
+      <c r="F150" s="46"/>
       <c r="J150" s="4"/>
     </row>
     <row r="151">
       <c r="A151" s="4"/>
-      <c r="F151" s="45"/>
+      <c r="F151" s="46"/>
       <c r="J151" s="4"/>
     </row>
     <row r="152">
       <c r="A152" s="4"/>
-      <c r="F152" s="45"/>
+      <c r="F152" s="46"/>
       <c r="J152" s="4"/>
     </row>
     <row r="153">
       <c r="A153" s="4"/>
-      <c r="F153" s="45"/>
+      <c r="F153" s="46"/>
       <c r="J153" s="4"/>
     </row>
     <row r="154">
       <c r="A154" s="4"/>
-      <c r="F154" s="45"/>
+      <c r="F154" s="46"/>
       <c r="J154" s="4"/>
     </row>
     <row r="155">
       <c r="A155" s="4"/>
-      <c r="F155" s="45"/>
+      <c r="F155" s="46"/>
       <c r="J155" s="4"/>
     </row>
     <row r="156">
       <c r="A156" s="4"/>
-      <c r="F156" s="45"/>
+      <c r="F156" s="46"/>
       <c r="J156" s="4"/>
     </row>
     <row r="157">
       <c r="A157" s="4"/>
-      <c r="F157" s="45"/>
+      <c r="F157" s="46"/>
       <c r="J157" s="4"/>
     </row>
     <row r="158">
       <c r="A158" s="4"/>
-      <c r="F158" s="45"/>
+      <c r="F158" s="46"/>
       <c r="J158" s="4"/>
     </row>
     <row r="159">
       <c r="A159" s="4"/>
-      <c r="F159" s="45"/>
+      <c r="F159" s="46"/>
       <c r="J159" s="4"/>
     </row>
     <row r="160">
       <c r="A160" s="4"/>
-      <c r="F160" s="45"/>
+      <c r="F160" s="46"/>
       <c r="J160" s="4"/>
     </row>
     <row r="161">
       <c r="A161" s="4"/>
-      <c r="F161" s="45"/>
+      <c r="F161" s="46"/>
       <c r="J161" s="4"/>
     </row>
     <row r="162">
       <c r="A162" s="4"/>
-      <c r="F162" s="45"/>
+      <c r="F162" s="46"/>
       <c r="J162" s="4"/>
     </row>
     <row r="163">
       <c r="A163" s="4"/>
-      <c r="F163" s="45"/>
+      <c r="F163" s="46"/>
       <c r="J163" s="4"/>
     </row>
     <row r="164">
       <c r="A164" s="4"/>
-      <c r="F164" s="45"/>
+      <c r="F164" s="46"/>
       <c r="J164" s="4"/>
     </row>
     <row r="165">
       <c r="A165" s="4"/>
-      <c r="F165" s="45"/>
+      <c r="F165" s="46"/>
       <c r="J165" s="4"/>
     </row>
     <row r="166">
       <c r="A166" s="4"/>
-      <c r="F166" s="45"/>
+      <c r="F166" s="46"/>
       <c r="J166" s="4"/>
     </row>
     <row r="167">
       <c r="A167" s="4"/>
-      <c r="F167" s="45"/>
+      <c r="F167" s="46"/>
       <c r="J167" s="4"/>
     </row>
     <row r="168">
       <c r="A168" s="4"/>
-      <c r="F168" s="45"/>
+      <c r="F168" s="46"/>
       <c r="J168" s="4"/>
     </row>
     <row r="169">
       <c r="A169" s="4"/>
-      <c r="F169" s="45"/>
+      <c r="F169" s="46"/>
       <c r="J169" s="4"/>
     </row>
     <row r="170">
       <c r="A170" s="4"/>
-      <c r="F170" s="45"/>
+      <c r="F170" s="46"/>
       <c r="J170" s="4"/>
     </row>
     <row r="171">
       <c r="A171" s="4"/>
-      <c r="F171" s="45"/>
+      <c r="F171" s="46"/>
       <c r="J171" s="4"/>
     </row>
     <row r="172">
       <c r="A172" s="4"/>
-      <c r="F172" s="45"/>
+      <c r="F172" s="46"/>
       <c r="J172" s="4"/>
     </row>
     <row r="173">
       <c r="A173" s="4"/>
-      <c r="F173" s="45"/>
+      <c r="F173" s="46"/>
       <c r="J173" s="4"/>
     </row>
     <row r="174">
       <c r="A174" s="4"/>
-      <c r="F174" s="45"/>
+      <c r="F174" s="46"/>
       <c r="J174" s="4"/>
     </row>
     <row r="175">
       <c r="A175" s="4"/>
-      <c r="F175" s="45"/>
+      <c r="F175" s="46"/>
       <c r="J175" s="4"/>
     </row>
     <row r="176">
       <c r="A176" s="4"/>
-      <c r="F176" s="45"/>
+      <c r="F176" s="46"/>
       <c r="J176" s="4"/>
     </row>
     <row r="177">
       <c r="A177" s="4"/>
-      <c r="F177" s="45"/>
+      <c r="F177" s="46"/>
       <c r="J177" s="4"/>
     </row>
     <row r="178">
       <c r="A178" s="4"/>
-      <c r="F178" s="45"/>
+      <c r="F178" s="46"/>
       <c r="J178" s="4"/>
     </row>
     <row r="179">
       <c r="A179" s="4"/>
-      <c r="F179" s="45"/>
+      <c r="F179" s="46"/>
       <c r="J179" s="4"/>
     </row>
     <row r="180">
       <c r="A180" s="4"/>
-      <c r="F180" s="45"/>
+      <c r="F180" s="46"/>
       <c r="J180" s="4"/>
     </row>
     <row r="181">
       <c r="A181" s="4"/>
-      <c r="F181" s="45"/>
+      <c r="F181" s="46"/>
       <c r="J181" s="4"/>
     </row>
     <row r="182">
       <c r="A182" s="4"/>
-      <c r="F182" s="45"/>
+      <c r="F182" s="46"/>
       <c r="J182" s="4"/>
     </row>
     <row r="183">
       <c r="A183" s="4"/>
-      <c r="F183" s="45"/>
+      <c r="F183" s="46"/>
       <c r="J183" s="4"/>
     </row>
     <row r="184">
       <c r="A184" s="4"/>
-      <c r="F184" s="45"/>
+      <c r="F184" s="46"/>
       <c r="J184" s="4"/>
     </row>
     <row r="185">
       <c r="A185" s="4"/>
-      <c r="F185" s="45"/>
+      <c r="F185" s="46"/>
       <c r="J185" s="4"/>
     </row>
     <row r="186">
       <c r="A186" s="4"/>
-      <c r="F186" s="45"/>
+      <c r="F186" s="46"/>
       <c r="J186" s="4"/>
     </row>
     <row r="187">
       <c r="A187" s="4"/>
-      <c r="F187" s="45"/>
+      <c r="F187" s="46"/>
       <c r="J187" s="4"/>
     </row>
     <row r="188">
       <c r="A188" s="4"/>
-      <c r="F188" s="45"/>
+      <c r="F188" s="46"/>
       <c r="J188" s="4"/>
     </row>
     <row r="189">
       <c r="A189" s="4"/>
-      <c r="F189" s="45"/>
+      <c r="F189" s="46"/>
       <c r="J189" s="4"/>
     </row>
     <row r="190">
       <c r="A190" s="4"/>
-      <c r="F190" s="45"/>
+      <c r="F190" s="46"/>
       <c r="J190" s="4"/>
     </row>
     <row r="191">
       <c r="A191" s="4"/>
-      <c r="F191" s="45"/>
+      <c r="F191" s="46"/>
       <c r="J191" s="4"/>
     </row>
     <row r="192">
       <c r="A192" s="4"/>
-      <c r="F192" s="45"/>
+      <c r="F192" s="46"/>
       <c r="J192" s="4"/>
     </row>
     <row r="193">
       <c r="A193" s="4"/>
-      <c r="F193" s="45"/>
+      <c r="F193" s="46"/>
       <c r="J193" s="4"/>
     </row>
     <row r="194">
       <c r="A194" s="4"/>
-      <c r="F194" s="45"/>
+      <c r="F194" s="46"/>
       <c r="J194" s="4"/>
     </row>
     <row r="195">
       <c r="A195" s="4"/>
-      <c r="F195" s="45"/>
+      <c r="F195" s="46"/>
       <c r="J195" s="4"/>
     </row>
     <row r="196">
       <c r="A196" s="4"/>
-      <c r="F196" s="45"/>
+      <c r="F196" s="46"/>
       <c r="J196" s="4"/>
     </row>
     <row r="197">
       <c r="A197" s="4"/>
-      <c r="F197" s="45"/>
+      <c r="F197" s="46"/>
       <c r="J197" s="4"/>
     </row>
     <row r="198">
       <c r="A198" s="4"/>
-      <c r="F198" s="45"/>
+      <c r="F198" s="46"/>
       <c r="J198" s="4"/>
     </row>
     <row r="199">
       <c r="A199" s="4"/>
-      <c r="F199" s="45"/>
+      <c r="F199" s="46"/>
       <c r="J199" s="4"/>
     </row>
     <row r="200">
       <c r="A200" s="4"/>
-      <c r="F200" s="45"/>
+      <c r="F200" s="46"/>
       <c r="J200" s="4"/>
     </row>
     <row r="201">
       <c r="A201" s="4"/>
-      <c r="F201" s="45"/>
+      <c r="F201" s="46"/>
       <c r="J201" s="4"/>
     </row>
     <row r="202">
       <c r="A202" s="4"/>
-      <c r="F202" s="45"/>
+      <c r="F202" s="46"/>
       <c r="J202" s="4"/>
     </row>
     <row r="203">
       <c r="A203" s="4"/>
-      <c r="F203" s="45"/>
+      <c r="F203" s="46"/>
       <c r="J203" s="4"/>
     </row>
     <row r="204">
       <c r="A204" s="4"/>
-      <c r="F204" s="45"/>
+      <c r="F204" s="46"/>
       <c r="J204" s="4"/>
     </row>
     <row r="205">
       <c r="A205" s="4"/>
-      <c r="F205" s="45"/>
+      <c r="F205" s="46"/>
       <c r="J205" s="4"/>
     </row>
     <row r="206">
       <c r="A206" s="4"/>
-      <c r="F206" s="45"/>
+      <c r="F206" s="46"/>
       <c r="J206" s="4"/>
     </row>
     <row r="207">
       <c r="A207" s="4"/>
-      <c r="F207" s="45"/>
+      <c r="F207" s="46"/>
       <c r="J207" s="4"/>
     </row>
     <row r="208">
       <c r="A208" s="4"/>
-      <c r="F208" s="45"/>
+      <c r="F208" s="46"/>
       <c r="J208" s="4"/>
     </row>
     <row r="209">
       <c r="A209" s="4"/>
-      <c r="F209" s="45"/>
+      <c r="F209" s="46"/>
       <c r="J209" s="4"/>
     </row>
     <row r="210">
       <c r="A210" s="4"/>
-      <c r="F210" s="45"/>
+      <c r="F210" s="46"/>
       <c r="J210" s="4"/>
     </row>
     <row r="211">
       <c r="A211" s="4"/>
-      <c r="F211" s="45"/>
+      <c r="F211" s="46"/>
       <c r="J211" s="4"/>
     </row>
     <row r="212">
       <c r="A212" s="4"/>
-      <c r="F212" s="45"/>
+      <c r="F212" s="46"/>
       <c r="J212" s="4"/>
     </row>
     <row r="213">
       <c r="A213" s="4"/>
-      <c r="F213" s="45"/>
+      <c r="F213" s="46"/>
       <c r="J213" s="4"/>
     </row>
     <row r="214">
       <c r="A214" s="4"/>
-      <c r="F214" s="45"/>
+      <c r="F214" s="46"/>
       <c r="J214" s="4"/>
     </row>
     <row r="215">
       <c r="A215" s="4"/>
-      <c r="F215" s="45"/>
+      <c r="F215" s="46"/>
       <c r="J215" s="4"/>
     </row>
     <row r="216">
       <c r="A216" s="4"/>
-      <c r="F216" s="45"/>
+      <c r="F216" s="46"/>
       <c r="J216" s="4"/>
     </row>
     <row r="217">
       <c r="A217" s="4"/>
-      <c r="F217" s="45"/>
+      <c r="F217" s="46"/>
       <c r="J217" s="4"/>
     </row>
     <row r="218">
       <c r="A218" s="4"/>
-      <c r="F218" s="45"/>
+      <c r="F218" s="46"/>
       <c r="J218" s="4"/>
     </row>
     <row r="219">
       <c r="A219" s="4"/>
-      <c r="F219" s="45"/>
+      <c r="F219" s="46"/>
       <c r="J219" s="4"/>
     </row>
     <row r="220">
       <c r="A220" s="4"/>
-      <c r="F220" s="45"/>
+      <c r="F220" s="46"/>
       <c r="J220" s="4"/>
     </row>
     <row r="221">
       <c r="A221" s="4"/>
-      <c r="F221" s="45"/>
+      <c r="F221" s="46"/>
       <c r="J221" s="4"/>
     </row>
     <row r="222">
       <c r="A222" s="4"/>
-      <c r="F222" s="45"/>
+      <c r="F222" s="46"/>
       <c r="J222" s="4"/>
     </row>
     <row r="223">
       <c r="A223" s="4"/>
-      <c r="F223" s="45"/>
+      <c r="F223" s="46"/>
       <c r="J223" s="4"/>
     </row>
     <row r="224">
       <c r="A224" s="4"/>
-      <c r="F224" s="45"/>
+      <c r="F224" s="46"/>
       <c r="J224" s="4"/>
     </row>
     <row r="225">
       <c r="A225" s="4"/>
-      <c r="F225" s="45"/>
+      <c r="F225" s="46"/>
       <c r="J225" s="4"/>
     </row>
     <row r="226">
       <c r="A226" s="4"/>
-      <c r="F226" s="45"/>
+      <c r="F226" s="46"/>
       <c r="J226" s="4"/>
     </row>
     <row r="227">
       <c r="A227" s="4"/>
-      <c r="F227" s="45"/>
+      <c r="F227" s="46"/>
       <c r="J227" s="4"/>
     </row>
     <row r="228">
       <c r="A228" s="4"/>
-      <c r="F228" s="45"/>
+      <c r="F228" s="46"/>
       <c r="J228" s="4"/>
     </row>
     <row r="229">
       <c r="A229" s="4"/>
-      <c r="F229" s="45"/>
+      <c r="F229" s="46"/>
       <c r="J229" s="4"/>
     </row>
     <row r="230">
       <c r="A230" s="4"/>
-      <c r="F230" s="45"/>
+      <c r="F230" s="46"/>
       <c r="J230" s="4"/>
     </row>
     <row r="231">
       <c r="A231" s="4"/>
-      <c r="F231" s="45"/>
+      <c r="F231" s="46"/>
       <c r="J231" s="4"/>
     </row>
     <row r="232">
       <c r="A232" s="4"/>
-      <c r="F232" s="45"/>
+      <c r="F232" s="46"/>
       <c r="J232" s="4"/>
     </row>
     <row r="233">
       <c r="A233" s="4"/>
-      <c r="F233" s="45"/>
+      <c r="F233" s="46"/>
       <c r="J233" s="4"/>
     </row>
     <row r="234">
       <c r="A234" s="4"/>
-      <c r="F234" s="45"/>
+      <c r="F234" s="46"/>
       <c r="J234" s="4"/>
     </row>
     <row r="235">
       <c r="A235" s="4"/>
-      <c r="F235" s="45"/>
+      <c r="F235" s="46"/>
       <c r="J235" s="4"/>
     </row>
     <row r="236">
       <c r="A236" s="4"/>
-      <c r="F236" s="45"/>
+      <c r="F236" s="46"/>
       <c r="J236" s="4"/>
     </row>
     <row r="237">
       <c r="A237" s="4"/>
-      <c r="F237" s="45"/>
+      <c r="F237" s="46"/>
       <c r="J237" s="4"/>
     </row>
     <row r="238">
       <c r="A238" s="4"/>
-      <c r="F238" s="45"/>
+      <c r="F238" s="46"/>
       <c r="J238" s="4"/>
     </row>
     <row r="239">
       <c r="A239" s="4"/>
-      <c r="F239" s="45"/>
+      <c r="F239" s="46"/>
       <c r="J239" s="4"/>
     </row>
     <row r="240">
       <c r="A240" s="4"/>
-      <c r="F240" s="45"/>
+      <c r="F240" s="46"/>
       <c r="J240" s="4"/>
     </row>
     <row r="241">
       <c r="A241" s="4"/>
-      <c r="F241" s="45"/>
+      <c r="F241" s="46"/>
       <c r="J241" s="4"/>
     </row>
     <row r="242">
       <c r="A242" s="4"/>
-      <c r="F242" s="45"/>
+      <c r="F242" s="46"/>
       <c r="J242" s="4"/>
     </row>
     <row r="243">
       <c r="A243" s="4"/>
-      <c r="F243" s="45"/>
+      <c r="F243" s="46"/>
       <c r="J243" s="4"/>
     </row>
     <row r="244">
       <c r="A244" s="4"/>
-      <c r="F244" s="45"/>
+      <c r="F244" s="46"/>
       <c r="J244" s="4"/>
     </row>
     <row r="245">
       <c r="A245" s="4"/>
-      <c r="F245" s="45"/>
+      <c r="F245" s="46"/>
       <c r="J245" s="4"/>
     </row>
     <row r="246">
       <c r="A246" s="4"/>
-      <c r="F246" s="45"/>
+      <c r="F246" s="46"/>
       <c r="J246" s="4"/>
     </row>
     <row r="247">
       <c r="A247" s="4"/>
-      <c r="F247" s="45"/>
+      <c r="F247" s="46"/>
       <c r="J247" s="4"/>
     </row>
     <row r="248">
       <c r="A248" s="4"/>
-      <c r="F248" s="45"/>
+      <c r="F248" s="46"/>
       <c r="J248" s="4"/>
     </row>
     <row r="249">
       <c r="A249" s="4"/>
-      <c r="F249" s="45"/>
+      <c r="F249" s="46"/>
       <c r="J249" s="4"/>
     </row>
     <row r="250">
       <c r="A250" s="4"/>
-      <c r="F250" s="45"/>
+      <c r="F250" s="46"/>
       <c r="J250" s="4"/>
     </row>
     <row r="251">
       <c r="A251" s="4"/>
-      <c r="F251" s="45"/>
+      <c r="F251" s="46"/>
       <c r="J251" s="4"/>
     </row>
     <row r="252">
       <c r="A252" s="4"/>
-      <c r="F252" s="45"/>
+      <c r="F252" s="46"/>
       <c r="J252" s="4"/>
     </row>
     <row r="253">
       <c r="A253" s="4"/>
-      <c r="F253" s="45"/>
+      <c r="F253" s="46"/>
       <c r="J253" s="4"/>
     </row>
     <row r="254">
       <c r="A254" s="4"/>
-      <c r="F254" s="45"/>
+      <c r="F254" s="46"/>
       <c r="J254" s="4"/>
     </row>
     <row r="255">
       <c r="A255" s="4"/>
-      <c r="F255" s="45"/>
+      <c r="F255" s="46"/>
       <c r="J255" s="4"/>
     </row>
     <row r="256">
       <c r="A256" s="4"/>
-      <c r="F256" s="45"/>
+      <c r="F256" s="46"/>
       <c r="J256" s="4"/>
     </row>
     <row r="257">
       <c r="A257" s="4"/>
-      <c r="F257" s="45"/>
+      <c r="F257" s="46"/>
       <c r="J257" s="4"/>
     </row>
     <row r="258">
       <c r="A258" s="4"/>
-      <c r="F258" s="45"/>
+      <c r="F258" s="46"/>
       <c r="J258" s="4"/>
     </row>
     <row r="259">
       <c r="A259" s="4"/>
-      <c r="F259" s="45"/>
+      <c r="F259" s="46"/>
       <c r="J259" s="4"/>
     </row>
     <row r="260">
       <c r="A260" s="4"/>
-      <c r="F260" s="45"/>
+      <c r="F260" s="46"/>
       <c r="J260" s="4"/>
     </row>
     <row r="261">
       <c r="A261" s="4"/>
-      <c r="F261" s="45"/>
+      <c r="F261" s="46"/>
       <c r="J261" s="4"/>
     </row>
     <row r="262">
       <c r="A262" s="4"/>
-      <c r="F262" s="45"/>
+      <c r="F262" s="46"/>
       <c r="J262" s="4"/>
     </row>
     <row r="263">
       <c r="A263" s="4"/>
-      <c r="F263" s="45"/>
+      <c r="F263" s="46"/>
       <c r="J263" s="4"/>
     </row>
     <row r="264">
       <c r="A264" s="4"/>
-      <c r="F264" s="45"/>
+      <c r="F264" s="46"/>
       <c r="J264" s="4"/>
     </row>
     <row r="265">
       <c r="A265" s="4"/>
-      <c r="F265" s="45"/>
+      <c r="F265" s="46"/>
       <c r="J265" s="4"/>
     </row>
     <row r="266">
       <c r="A266" s="4"/>
-      <c r="F266" s="45"/>
+      <c r="F266" s="46"/>
       <c r="J266" s="4"/>
     </row>
     <row r="267">
       <c r="A267" s="4"/>
-      <c r="F267" s="45"/>
+      <c r="F267" s="46"/>
       <c r="J267" s="4"/>
     </row>
     <row r="268">
       <c r="A268" s="4"/>
-      <c r="F268" s="45"/>
+      <c r="F268" s="46"/>
       <c r="J268" s="4"/>
     </row>
     <row r="269">
       <c r="A269" s="4"/>
-      <c r="F269" s="45"/>
+      <c r="F269" s="46"/>
       <c r="J269" s="4"/>
     </row>
     <row r="270">
       <c r="A270" s="4"/>
-      <c r="F270" s="45"/>
+      <c r="F270" s="46"/>
       <c r="J270" s="4"/>
     </row>
     <row r="271">
       <c r="A271" s="4"/>
-      <c r="F271" s="45"/>
+      <c r="F271" s="46"/>
       <c r="J271" s="4"/>
     </row>
     <row r="272">
       <c r="A272" s="4"/>
-      <c r="F272" s="45"/>
+      <c r="F272" s="46"/>
       <c r="J272" s="4"/>
     </row>
     <row r="273">
       <c r="A273" s="4"/>
-      <c r="F273" s="45"/>
+      <c r="F273" s="46"/>
       <c r="J273" s="4"/>
     </row>
     <row r="274">
       <c r="A274" s="4"/>
-      <c r="F274" s="45"/>
+      <c r="F274" s="46"/>
       <c r="J274" s="4"/>
     </row>
     <row r="275">
       <c r="A275" s="4"/>
-      <c r="F275" s="45"/>
+      <c r="F275" s="46"/>
       <c r="J275" s="4"/>
     </row>
     <row r="276">
       <c r="A276" s="4"/>
-      <c r="F276" s="45"/>
+      <c r="F276" s="46"/>
       <c r="J276" s="4"/>
     </row>
     <row r="277">
       <c r="A277" s="4"/>
-      <c r="F277" s="45"/>
+      <c r="F277" s="46"/>
       <c r="J277" s="4"/>
     </row>
     <row r="278">
       <c r="A278" s="4"/>
-      <c r="F278" s="45"/>
+      <c r="F278" s="46"/>
       <c r="J278" s="4"/>
     </row>
     <row r="279">
       <c r="A279" s="4"/>
-      <c r="F279" s="45"/>
+      <c r="F279" s="46"/>
       <c r="J279" s="4"/>
     </row>
     <row r="280">
       <c r="A280" s="4"/>
-      <c r="F280" s="45"/>
+      <c r="F280" s="46"/>
       <c r="J280" s="4"/>
     </row>
     <row r="281">
       <c r="A281" s="4"/>
-      <c r="F281" s="45"/>
+      <c r="F281" s="46"/>
       <c r="J281" s="4"/>
     </row>
     <row r="282">
       <c r="A282" s="4"/>
-      <c r="F282" s="45"/>
+      <c r="F282" s="46"/>
       <c r="J282" s="4"/>
     </row>
     <row r="283">
       <c r="A283" s="4"/>
-      <c r="F283" s="45"/>
+      <c r="F283" s="46"/>
       <c r="J283" s="4"/>
     </row>
     <row r="284">
       <c r="A284" s="4"/>
-      <c r="F284" s="45"/>
+      <c r="F284" s="46"/>
       <c r="J284" s="4"/>
     </row>
     <row r="285">
       <c r="A285" s="4"/>
-      <c r="F285" s="45"/>
+      <c r="F285" s="46"/>
       <c r="J285" s="4"/>
     </row>
     <row r="286">
       <c r="A286" s="4"/>
-      <c r="F286" s="45"/>
+      <c r="F286" s="46"/>
       <c r="J286" s="4"/>
     </row>
     <row r="287">
       <c r="A287" s="4"/>
-      <c r="F287" s="45"/>
+      <c r="F287" s="46"/>
       <c r="J287" s="4"/>
     </row>
     <row r="288">
       <c r="A288" s="4"/>
-      <c r="F288" s="45"/>
+      <c r="F288" s="46"/>
       <c r="J288" s="4"/>
     </row>
     <row r="289">
       <c r="A289" s="4"/>
-      <c r="F289" s="45"/>
+      <c r="F289" s="46"/>
       <c r="J289" s="4"/>
     </row>
     <row r="290">
       <c r="A290" s="4"/>
-      <c r="F290" s="45"/>
+      <c r="F290" s="46"/>
       <c r="J290" s="4"/>
     </row>
     <row r="291">
       <c r="A291" s="4"/>
-      <c r="F291" s="45"/>
+      <c r="F291" s="46"/>
       <c r="J291" s="4"/>
     </row>
     <row r="292">
       <c r="A292" s="4"/>
-      <c r="F292" s="45"/>
+      <c r="F292" s="46"/>
       <c r="J292" s="4"/>
     </row>
     <row r="293">
       <c r="A293" s="4"/>
-      <c r="F293" s="45"/>
+      <c r="F293" s="46"/>
       <c r="J293" s="4"/>
     </row>
     <row r="294">
       <c r="A294" s="4"/>
-      <c r="F294" s="45"/>
+      <c r="F294" s="46"/>
       <c r="J294" s="4"/>
     </row>
     <row r="295">
       <c r="A295" s="4"/>
-      <c r="F295" s="45"/>
+      <c r="F295" s="46"/>
       <c r="J295" s="4"/>
     </row>
     <row r="296">
       <c r="A296" s="4"/>
-      <c r="F296" s="45"/>
+      <c r="F296" s="46"/>
       <c r="J296" s="4"/>
     </row>
     <row r="297">
       <c r="A297" s="4"/>
-      <c r="F297" s="45"/>
+      <c r="F297" s="46"/>
       <c r="J297" s="4"/>
     </row>
     <row r="298">
       <c r="A298" s="4"/>
-      <c r="F298" s="45"/>
+      <c r="F298" s="46"/>
       <c r="J298" s="4"/>
     </row>
     <row r="299">
       <c r="A299" s="4"/>
-      <c r="F299" s="45"/>
+      <c r="F299" s="46"/>
       <c r="J299" s="4"/>
     </row>
     <row r="300">
       <c r="A300" s="4"/>
-      <c r="F300" s="45"/>
+      <c r="F300" s="46"/>
       <c r="J300" s="4"/>
     </row>
     <row r="301">
       <c r="A301" s="4"/>
-      <c r="F301" s="45"/>
+      <c r="F301" s="46"/>
       <c r="J301" s="4"/>
     </row>
     <row r="302">
       <c r="A302" s="4"/>
-      <c r="F302" s="45"/>
+      <c r="F302" s="46"/>
       <c r="J302" s="4"/>
     </row>
     <row r="303">
       <c r="A303" s="4"/>
-      <c r="F303" s="45"/>
+      <c r="F303" s="46"/>
       <c r="J303" s="4"/>
     </row>
     <row r="304">
       <c r="A304" s="4"/>
-      <c r="F304" s="45"/>
+      <c r="F304" s="46"/>
       <c r="J304" s="4"/>
     </row>
     <row r="305">
       <c r="A305" s="4"/>
-      <c r="F305" s="45"/>
+      <c r="F305" s="46"/>
       <c r="J305" s="4"/>
     </row>
     <row r="306">
       <c r="A306" s="4"/>
-      <c r="F306" s="45"/>
+      <c r="F306" s="46"/>
       <c r="J306" s="4"/>
     </row>
     <row r="307">
       <c r="A307" s="4"/>
-      <c r="F307" s="45"/>
+      <c r="F307" s="46"/>
       <c r="J307" s="4"/>
     </row>
     <row r="308">
       <c r="A308" s="4"/>
-      <c r="F308" s="45"/>
+      <c r="F308" s="46"/>
       <c r="J308" s="4"/>
     </row>
     <row r="309">
       <c r="A309" s="4"/>
-      <c r="F309" s="45"/>
+      <c r="F309" s="46"/>
       <c r="J309" s="4"/>
     </row>
     <row r="310">
       <c r="A310" s="4"/>
-      <c r="F310" s="45"/>
+      <c r="F310" s="46"/>
       <c r="J310" s="4"/>
     </row>
     <row r="311">
       <c r="A311" s="4"/>
-      <c r="F311" s="45"/>
+      <c r="F311" s="46"/>
       <c r="J311" s="4"/>
     </row>
     <row r="312">
       <c r="A312" s="4"/>
-      <c r="F312" s="45"/>
+      <c r="F312" s="46"/>
       <c r="J312" s="4"/>
     </row>
     <row r="313">
       <c r="A313" s="4"/>
-      <c r="F313" s="45"/>
+      <c r="F313" s="46"/>
       <c r="J313" s="4"/>
     </row>
     <row r="314">
       <c r="A314" s="4"/>
-      <c r="F314" s="45"/>
+      <c r="F314" s="46"/>
       <c r="J314" s="4"/>
     </row>
     <row r="315">
       <c r="A315" s="4"/>
-      <c r="F315" s="45"/>
+      <c r="F315" s="46"/>
       <c r="J315" s="4"/>
     </row>
     <row r="316">
       <c r="A316" s="4"/>
-      <c r="F316" s="45"/>
+      <c r="F316" s="46"/>
       <c r="J316" s="4"/>
     </row>
     <row r="317">
       <c r="A317" s="4"/>
-      <c r="F317" s="45"/>
+      <c r="F317" s="46"/>
       <c r="J317" s="4"/>
     </row>
     <row r="318">
       <c r="A318" s="4"/>
-      <c r="F318" s="45"/>
+      <c r="F318" s="46"/>
       <c r="J318" s="4"/>
     </row>
     <row r="319">
       <c r="A319" s="4"/>
-      <c r="F319" s="45"/>
+      <c r="F319" s="46"/>
       <c r="J319" s="4"/>
     </row>
     <row r="320">
       <c r="A320" s="4"/>
-      <c r="F320" s="45"/>
+      <c r="F320" s="46"/>
       <c r="J320" s="4"/>
     </row>
     <row r="321">
       <c r="A321" s="4"/>
-      <c r="F321" s="45"/>
+      <c r="F321" s="46"/>
       <c r="J321" s="4"/>
     </row>
     <row r="322">
       <c r="A322" s="4"/>
-      <c r="F322" s="45"/>
+      <c r="F322" s="46"/>
       <c r="J322" s="4"/>
     </row>
     <row r="323">
       <c r="A323" s="4"/>
-      <c r="F323" s="45"/>
+      <c r="F323" s="46"/>
       <c r="J323" s="4"/>
     </row>
     <row r="324">
       <c r="A324" s="4"/>
-      <c r="F324" s="45"/>
+      <c r="F324" s="46"/>
       <c r="J324" s="4"/>
     </row>
     <row r="325">
       <c r="A325" s="4"/>
-      <c r="F325" s="45"/>
+      <c r="F325" s="46"/>
       <c r="J325" s="4"/>
     </row>
     <row r="326">
       <c r="A326" s="4"/>
-      <c r="F326" s="45"/>
+      <c r="F326" s="46"/>
       <c r="J326" s="4"/>
     </row>
     <row r="327">
       <c r="A327" s="4"/>
-      <c r="F327" s="45"/>
+      <c r="F327" s="46"/>
       <c r="J327" s="4"/>
     </row>
     <row r="328">
       <c r="A328" s="4"/>
-      <c r="F328" s="45"/>
+      <c r="F328" s="46"/>
       <c r="J328" s="4"/>
     </row>
     <row r="329">
       <c r="A329" s="4"/>
-      <c r="F329" s="45"/>
+      <c r="F329" s="46"/>
       <c r="J329" s="4"/>
     </row>
     <row r="330">
       <c r="A330" s="4"/>
-      <c r="F330" s="45"/>
+      <c r="F330" s="46"/>
       <c r="J330" s="4"/>
     </row>
     <row r="331">
       <c r="A331" s="4"/>
-      <c r="F331" s="45"/>
+      <c r="F331" s="46"/>
       <c r="J331" s="4"/>
     </row>
     <row r="332">
       <c r="A332" s="4"/>
-      <c r="F332" s="45"/>
+      <c r="F332" s="46"/>
       <c r="J332" s="4"/>
     </row>
     <row r="333">
       <c r="A333" s="4"/>
-      <c r="F333" s="45"/>
+      <c r="F333" s="46"/>
       <c r="J333" s="4"/>
     </row>
     <row r="334">
       <c r="A334" s="4"/>
-      <c r="F334" s="45"/>
+      <c r="F334" s="46"/>
       <c r="J334" s="4"/>
     </row>
     <row r="335">
       <c r="A335" s="4"/>
-      <c r="F335" s="45"/>
+      <c r="F335" s="46"/>
       <c r="J335" s="4"/>
     </row>
     <row r="336">
       <c r="A336" s="4"/>
-      <c r="F336" s="45"/>
+      <c r="F336" s="46"/>
       <c r="J336" s="4"/>
     </row>
     <row r="337">
       <c r="A337" s="4"/>
-      <c r="F337" s="45"/>
+      <c r="F337" s="46"/>
       <c r="J337" s="4"/>
     </row>
     <row r="338">
       <c r="A338" s="4"/>
-      <c r="F338" s="45"/>
+      <c r="F338" s="46"/>
       <c r="J338" s="4"/>
     </row>
     <row r="339">
       <c r="A339" s="4"/>
-      <c r="F339" s="45"/>
+      <c r="F339" s="46"/>
       <c r="J339" s="4"/>
     </row>
     <row r="340">
       <c r="A340" s="4"/>
-      <c r="F340" s="45"/>
+      <c r="F340" s="46"/>
       <c r="J340" s="4"/>
     </row>
     <row r="341">
       <c r="A341" s="4"/>
-      <c r="F341" s="45"/>
+      <c r="F341" s="46"/>
       <c r="J341" s="4"/>
     </row>
     <row r="342">
       <c r="A342" s="4"/>
-      <c r="F342" s="45"/>
+      <c r="F342" s="46"/>
       <c r="J342" s="4"/>
     </row>
     <row r="343">
       <c r="A343" s="4"/>
-      <c r="F343" s="45"/>
+      <c r="F343" s="46"/>
       <c r="J343" s="4"/>
     </row>
     <row r="344">
       <c r="A344" s="4"/>
-      <c r="F344" s="45"/>
+      <c r="F344" s="46"/>
       <c r="J344" s="4"/>
     </row>
     <row r="345">
       <c r="A345" s="4"/>
-      <c r="F345" s="45"/>
+      <c r="F345" s="46"/>
       <c r="J345" s="4"/>
     </row>
     <row r="346">
       <c r="A346" s="4"/>
-      <c r="F346" s="45"/>
+      <c r="F346" s="46"/>
       <c r="J346" s="4"/>
     </row>
     <row r="347">
       <c r="A347" s="4"/>
-      <c r="F347" s="45"/>
+      <c r="F347" s="46"/>
       <c r="J347" s="4"/>
     </row>
     <row r="348">
       <c r="A348" s="4"/>
-      <c r="F348" s="45"/>
+      <c r="F348" s="46"/>
       <c r="J348" s="4"/>
     </row>
     <row r="349">
       <c r="A349" s="4"/>
-      <c r="F349" s="45"/>
+      <c r="F349" s="46"/>
       <c r="J349" s="4"/>
     </row>
     <row r="350">
       <c r="A350" s="4"/>
-      <c r="F350" s="45"/>
+      <c r="F350" s="46"/>
       <c r="J350" s="4"/>
     </row>
     <row r="351">
       <c r="A351" s="4"/>
-      <c r="F351" s="45"/>
+      <c r="F351" s="46"/>
       <c r="J351" s="4"/>
     </row>
     <row r="352">
       <c r="A352" s="4"/>
-      <c r="F352" s="45"/>
+      <c r="F352" s="46"/>
       <c r="J352" s="4"/>
     </row>
     <row r="353">
       <c r="A353" s="4"/>
-      <c r="F353" s="45"/>
+      <c r="F353" s="46"/>
       <c r="J353" s="4"/>
     </row>
     <row r="354">
       <c r="A354" s="4"/>
-      <c r="F354" s="45"/>
+      <c r="F354" s="46"/>
       <c r="J354" s="4"/>
     </row>
     <row r="355">
       <c r="A355" s="4"/>
-      <c r="F355" s="45"/>
+      <c r="F355" s="46"/>
       <c r="J355" s="4"/>
     </row>
     <row r="356">
       <c r="A356" s="4"/>
-      <c r="F356" s="45"/>
+      <c r="F356" s="46"/>
       <c r="J356" s="4"/>
     </row>
     <row r="357">
       <c r="A357" s="4"/>
-      <c r="F357" s="45"/>
+      <c r="F357" s="46"/>
       <c r="J357" s="4"/>
     </row>
     <row r="358">
       <c r="A358" s="4"/>
-      <c r="F358" s="45"/>
+      <c r="F358" s="46"/>
       <c r="J358" s="4"/>
     </row>
     <row r="359">
       <c r="A359" s="4"/>
-      <c r="F359" s="45"/>
+      <c r="F359" s="46"/>
       <c r="J359" s="4"/>
     </row>
     <row r="360">
       <c r="A360" s="4"/>
-      <c r="F360" s="45"/>
+      <c r="F360" s="46"/>
       <c r="J360" s="4"/>
     </row>
     <row r="361">
       <c r="A361" s="4"/>
-      <c r="F361" s="45"/>
+      <c r="F361" s="46"/>
       <c r="J361" s="4"/>
     </row>
     <row r="362">
       <c r="A362" s="4"/>
-      <c r="F362" s="45"/>
+      <c r="F362" s="46"/>
       <c r="J362" s="4"/>
     </row>
     <row r="363">
       <c r="A363" s="4"/>
-      <c r="F363" s="45"/>
+      <c r="F363" s="46"/>
       <c r="J363" s="4"/>
     </row>
     <row r="364">
       <c r="A364" s="4"/>
-      <c r="F364" s="45"/>
+      <c r="F364" s="46"/>
       <c r="J364" s="4"/>
     </row>
     <row r="365">
       <c r="A365" s="4"/>
-      <c r="F365" s="45"/>
+      <c r="F365" s="46"/>
       <c r="J365" s="4"/>
     </row>
     <row r="366">
       <c r="A366" s="4"/>
-      <c r="F366" s="45"/>
+      <c r="F366" s="46"/>
       <c r="J366" s="4"/>
     </row>
     <row r="367">
       <c r="A367" s="4"/>
-      <c r="F367" s="45"/>
+      <c r="F367" s="46"/>
       <c r="J367" s="4"/>
     </row>
     <row r="368">
       <c r="A368" s="4"/>
-      <c r="F368" s="45"/>
+      <c r="F368" s="46"/>
       <c r="J368" s="4"/>
     </row>
     <row r="369">
       <c r="A369" s="4"/>
-      <c r="F369" s="45"/>
+      <c r="F369" s="46"/>
       <c r="J369" s="4"/>
     </row>
     <row r="370">
       <c r="A370" s="4"/>
-      <c r="F370" s="45"/>
+      <c r="F370" s="46"/>
       <c r="J370" s="4"/>
     </row>
     <row r="371">
       <c r="A371" s="4"/>
-      <c r="F371" s="45"/>
+      <c r="F371" s="46"/>
       <c r="J371" s="4"/>
     </row>
     <row r="372">
       <c r="A372" s="4"/>
-      <c r="F372" s="45"/>
+      <c r="F372" s="46"/>
       <c r="J372" s="4"/>
     </row>
     <row r="373">
       <c r="A373" s="4"/>
-      <c r="F373" s="45"/>
+      <c r="F373" s="46"/>
       <c r="J373" s="4"/>
     </row>
     <row r="374">
       <c r="A374" s="4"/>
-      <c r="F374" s="45"/>
+      <c r="F374" s="46"/>
       <c r="J374" s="4"/>
     </row>
     <row r="375">
       <c r="A375" s="4"/>
-      <c r="F375" s="45"/>
+      <c r="F375" s="46"/>
       <c r="J375" s="4"/>
     </row>
     <row r="376">
       <c r="A376" s="4"/>
-      <c r="F376" s="45"/>
+      <c r="F376" s="46"/>
       <c r="J376" s="4"/>
     </row>
     <row r="377">
       <c r="A377" s="4"/>
-      <c r="F377" s="45"/>
+      <c r="F377" s="46"/>
       <c r="J377" s="4"/>
     </row>
     <row r="378">
       <c r="A378" s="4"/>
-      <c r="F378" s="45"/>
+      <c r="F378" s="46"/>
       <c r="J378" s="4"/>
     </row>
     <row r="379">
       <c r="A379" s="4"/>
-      <c r="F379" s="45"/>
+      <c r="F379" s="46"/>
       <c r="J379" s="4"/>
     </row>
     <row r="380">
       <c r="A380" s="4"/>
-      <c r="F380" s="45"/>
+      <c r="F380" s="46"/>
       <c r="J380" s="4"/>
     </row>
     <row r="381">
       <c r="A381" s="4"/>
-      <c r="F381" s="45"/>
+      <c r="F381" s="46"/>
       <c r="J381" s="4"/>
     </row>
     <row r="382">
       <c r="A382" s="4"/>
-      <c r="F382" s="45"/>
+      <c r="F382" s="46"/>
       <c r="J382" s="4"/>
     </row>
     <row r="383">
       <c r="A383" s="4"/>
-      <c r="F383" s="45"/>
+      <c r="F383" s="46"/>
       <c r="J383" s="4"/>
     </row>
     <row r="384">
       <c r="A384" s="4"/>
-      <c r="F384" s="45"/>
+      <c r="F384" s="46"/>
       <c r="J384" s="4"/>
     </row>
     <row r="385">
       <c r="A385" s="4"/>
-      <c r="F385" s="45"/>
+      <c r="F385" s="46"/>
       <c r="J385" s="4"/>
     </row>
     <row r="386">
       <c r="A386" s="4"/>
-      <c r="F386" s="45"/>
+      <c r="F386" s="46"/>
       <c r="J386" s="4"/>
     </row>
     <row r="387">
       <c r="A387" s="4"/>
-      <c r="F387" s="45"/>
+      <c r="F387" s="46"/>
       <c r="J387" s="4"/>
     </row>
     <row r="388">
       <c r="A388" s="4"/>
-      <c r="F388" s="45"/>
+      <c r="F388" s="46"/>
       <c r="J388" s="4"/>
     </row>
     <row r="389">
       <c r="A389" s="4"/>
-      <c r="F389" s="45"/>
+      <c r="F389" s="46"/>
       <c r="J389" s="4"/>
     </row>
     <row r="390">
       <c r="A390" s="4"/>
-      <c r="F390" s="45"/>
+      <c r="F390" s="46"/>
       <c r="J390" s="4"/>
     </row>
     <row r="391">
       <c r="A391" s="4"/>
-      <c r="F391" s="45"/>
+      <c r="F391" s="46"/>
       <c r="J391" s="4"/>
     </row>
     <row r="392">
       <c r="A392" s="4"/>
-      <c r="F392" s="45"/>
+      <c r="F392" s="46"/>
       <c r="J392" s="4"/>
     </row>
     <row r="393">
       <c r="A393" s="4"/>
-      <c r="F393" s="45"/>
+      <c r="F393" s="46"/>
       <c r="J393" s="4"/>
     </row>
     <row r="394">
       <c r="A394" s="4"/>
-      <c r="F394" s="45"/>
+      <c r="F394" s="46"/>
       <c r="J394" s="4"/>
     </row>
     <row r="395">
       <c r="A395" s="4"/>
-      <c r="F395" s="45"/>
+      <c r="F395" s="46"/>
       <c r="J395" s="4"/>
     </row>
     <row r="396">
       <c r="A396" s="4"/>
-      <c r="F396" s="45"/>
+      <c r="F396" s="46"/>
       <c r="J396" s="4"/>
     </row>
     <row r="397">
       <c r="A397" s="4"/>
-      <c r="F397" s="45"/>
+      <c r="F397" s="46"/>
       <c r="J397" s="4"/>
     </row>
     <row r="398">
       <c r="A398" s="4"/>
-      <c r="F398" s="45"/>
+      <c r="F398" s="46"/>
       <c r="J398" s="4"/>
     </row>
     <row r="399">
       <c r="A399" s="4"/>
-      <c r="F399" s="45"/>
+      <c r="F399" s="46"/>
       <c r="J399" s="4"/>
     </row>
     <row r="400">
       <c r="A400" s="4"/>
-      <c r="F400" s="45"/>
+      <c r="F400" s="46"/>
       <c r="J400" s="4"/>
     </row>
     <row r="401">
       <c r="A401" s="4"/>
-      <c r="F401" s="45"/>
+      <c r="F401" s="46"/>
       <c r="J401" s="4"/>
     </row>
     <row r="402">
       <c r="A402" s="4"/>
-      <c r="F402" s="45"/>
+      <c r="F402" s="46"/>
       <c r="J402" s="4"/>
     </row>
     <row r="403">
       <c r="A403" s="4"/>
-      <c r="F403" s="45"/>
+      <c r="F403" s="46"/>
       <c r="J403" s="4"/>
     </row>
     <row r="404">
       <c r="A404" s="4"/>
-      <c r="F404" s="45"/>
+      <c r="F404" s="46"/>
       <c r="J404" s="4"/>
     </row>
     <row r="405">
       <c r="A405" s="4"/>
-      <c r="F405" s="45"/>
+      <c r="F405" s="46"/>
       <c r="J405" s="4"/>
     </row>
     <row r="406">
       <c r="A406" s="4"/>
-      <c r="F406" s="45"/>
+      <c r="F406" s="46"/>
       <c r="J406" s="4"/>
     </row>
     <row r="407">
       <c r="A407" s="4"/>
-      <c r="F407" s="45"/>
+      <c r="F407" s="46"/>
       <c r="J407" s="4"/>
     </row>
     <row r="408">
       <c r="A408" s="4"/>
-      <c r="F408" s="45"/>
+      <c r="F408" s="46"/>
       <c r="J408" s="4"/>
     </row>
     <row r="409">
       <c r="A409" s="4"/>
-      <c r="F409" s="45"/>
+      <c r="F409" s="46"/>
       <c r="J409" s="4"/>
     </row>
     <row r="410">
       <c r="A410" s="4"/>
-      <c r="F410" s="45"/>
+      <c r="F410" s="46"/>
       <c r="J410" s="4"/>
     </row>
     <row r="411">
       <c r="A411" s="4"/>
-      <c r="F411" s="45"/>
+      <c r="F411" s="46"/>
       <c r="J411" s="4"/>
     </row>
     <row r="412">
       <c r="A412" s="4"/>
-      <c r="F412" s="45"/>
+      <c r="F412" s="46"/>
       <c r="J412" s="4"/>
     </row>
     <row r="413">
       <c r="A413" s="4"/>
-      <c r="F413" s="45"/>
+      <c r="F413" s="46"/>
       <c r="J413" s="4"/>
     </row>
     <row r="414">
       <c r="A414" s="4"/>
-      <c r="F414" s="45"/>
+      <c r="F414" s="46"/>
       <c r="J414" s="4"/>
     </row>
     <row r="415">
       <c r="A415" s="4"/>
-      <c r="F415" s="45"/>
+      <c r="F415" s="46"/>
       <c r="J415" s="4"/>
     </row>
     <row r="416">
       <c r="A416" s="4"/>
-      <c r="F416" s="45"/>
+      <c r="F416" s="46"/>
       <c r="J416" s="4"/>
     </row>
     <row r="417">
       <c r="A417" s="4"/>
-      <c r="F417" s="45"/>
+      <c r="F417" s="46"/>
       <c r="J417" s="4"/>
     </row>
     <row r="418">
       <c r="A418" s="4"/>
-      <c r="F418" s="45"/>
+      <c r="F418" s="46"/>
       <c r="J418" s="4"/>
     </row>
     <row r="419">
       <c r="A419" s="4"/>
-      <c r="F419" s="45"/>
+      <c r="F419" s="46"/>
       <c r="J419" s="4"/>
     </row>
     <row r="420">
       <c r="A420" s="4"/>
-      <c r="F420" s="45"/>
+      <c r="F420" s="46"/>
       <c r="J420" s="4"/>
     </row>
     <row r="421">
       <c r="A421" s="4"/>
-      <c r="F421" s="45"/>
+      <c r="F421" s="46"/>
       <c r="J421" s="4"/>
     </row>
     <row r="422">
       <c r="A422" s="4"/>
-      <c r="F422" s="45"/>
+      <c r="F422" s="46"/>
       <c r="J422" s="4"/>
     </row>
     <row r="423">
       <c r="A423" s="4"/>
-      <c r="F423" s="45"/>
+      <c r="F423" s="46"/>
       <c r="J423" s="4"/>
     </row>
     <row r="424">
       <c r="A424" s="4"/>
-      <c r="F424" s="45"/>
+      <c r="F424" s="46"/>
       <c r="J424" s="4"/>
     </row>
     <row r="425">
       <c r="A425" s="4"/>
-      <c r="F425" s="45"/>
+      <c r="F425" s="46"/>
       <c r="J425" s="4"/>
     </row>
     <row r="426">
       <c r="A426" s="4"/>
-      <c r="F426" s="45"/>
+      <c r="F426" s="46"/>
       <c r="J426" s="4"/>
     </row>
     <row r="427">
       <c r="A427" s="4"/>
-      <c r="F427" s="45"/>
+      <c r="F427" s="46"/>
       <c r="J427" s="4"/>
     </row>
     <row r="428">
       <c r="A428" s="4"/>
-      <c r="F428" s="45"/>
+      <c r="F428" s="46"/>
       <c r="J428" s="4"/>
     </row>
     <row r="429">
       <c r="A429" s="4"/>
-      <c r="F429" s="45"/>
+      <c r="F429" s="46"/>
       <c r="J429" s="4"/>
     </row>
     <row r="430">
       <c r="A430" s="4"/>
-      <c r="F430" s="45"/>
+      <c r="F430" s="46"/>
       <c r="J430" s="4"/>
     </row>
     <row r="431">
       <c r="A431" s="4"/>
-      <c r="F431" s="45"/>
+      <c r="F431" s="46"/>
       <c r="J431" s="4"/>
     </row>
     <row r="432">
       <c r="A432" s="4"/>
-      <c r="F432" s="45"/>
+      <c r="F432" s="46"/>
       <c r="J432" s="4"/>
     </row>
     <row r="433">
       <c r="A433" s="4"/>
-      <c r="F433" s="45"/>
+      <c r="F433" s="46"/>
       <c r="J433" s="4"/>
     </row>
     <row r="434">
       <c r="A434" s="4"/>
-      <c r="F434" s="45"/>
+      <c r="F434" s="46"/>
       <c r="J434" s="4"/>
     </row>
     <row r="435">
       <c r="A435" s="4"/>
-      <c r="F435" s="45"/>
+      <c r="F435" s="46"/>
       <c r="J435" s="4"/>
     </row>
     <row r="436">
       <c r="A436" s="4"/>
-      <c r="F436" s="45"/>
+      <c r="F436" s="46"/>
       <c r="J436" s="4"/>
     </row>
     <row r="437">
       <c r="A437" s="4"/>
-      <c r="F437" s="45"/>
+      <c r="F437" s="46"/>
       <c r="J437" s="4"/>
     </row>
     <row r="438">
       <c r="A438" s="4"/>
-      <c r="F438" s="45"/>
+      <c r="F438" s="46"/>
       <c r="J438" s="4"/>
     </row>
     <row r="439">
       <c r="A439" s="4"/>
-      <c r="F439" s="45"/>
+      <c r="F439" s="46"/>
       <c r="J439" s="4"/>
     </row>
     <row r="440">
       <c r="A440" s="4"/>
-      <c r="F440" s="45"/>
+      <c r="F440" s="46"/>
       <c r="J440" s="4"/>
     </row>
     <row r="441">
       <c r="A441" s="4"/>
-      <c r="F441" s="45"/>
+      <c r="F441" s="46"/>
       <c r="J441" s="4"/>
     </row>
     <row r="442">
       <c r="A442" s="4"/>
-      <c r="F442" s="45"/>
+      <c r="F442" s="46"/>
       <c r="J442" s="4"/>
     </row>
     <row r="443">
       <c r="A443" s="4"/>
-      <c r="F443" s="45"/>
+      <c r="F443" s="46"/>
       <c r="J443" s="4"/>
     </row>
     <row r="444">
       <c r="A444" s="4"/>
-      <c r="F444" s="45"/>
+      <c r="F444" s="46"/>
       <c r="J444" s="4"/>
     </row>
     <row r="445">
       <c r="A445" s="4"/>
-      <c r="F445" s="45"/>
+      <c r="F445" s="46"/>
       <c r="J445" s="4"/>
     </row>
     <row r="446">
       <c r="A446" s="4"/>
-      <c r="F446" s="45"/>
+      <c r="F446" s="46"/>
       <c r="J446" s="4"/>
     </row>
     <row r="447">
       <c r="A447" s="4"/>
-      <c r="F447" s="45"/>
+      <c r="F447" s="46"/>
       <c r="J447" s="4"/>
     </row>
     <row r="448">
       <c r="A448" s="4"/>
-      <c r="F448" s="45"/>
+      <c r="F448" s="46"/>
       <c r="J448" s="4"/>
     </row>
     <row r="449">
       <c r="A449" s="4"/>
-      <c r="F449" s="45"/>
+      <c r="F449" s="46"/>
       <c r="J449" s="4"/>
     </row>
     <row r="450">
       <c r="A450" s="4"/>
-      <c r="F450" s="45"/>
+      <c r="F450" s="46"/>
       <c r="J450" s="4"/>
     </row>
     <row r="451">
       <c r="A451" s="4"/>
-      <c r="F451" s="45"/>
+      <c r="F451" s="46"/>
       <c r="J451" s="4"/>
     </row>
     <row r="452">
       <c r="A452" s="4"/>
-      <c r="F452" s="45"/>
+      <c r="F452" s="46"/>
       <c r="J452" s="4"/>
     </row>
     <row r="453">
       <c r="A453" s="4"/>
-      <c r="F453" s="45"/>
+      <c r="F453" s="46"/>
       <c r="J453" s="4"/>
     </row>
     <row r="454">
       <c r="A454" s="4"/>
-      <c r="F454" s="45"/>
+      <c r="F454" s="46"/>
       <c r="J454" s="4"/>
     </row>
     <row r="455">
       <c r="A455" s="4"/>
-      <c r="F455" s="45"/>
+      <c r="F455" s="46"/>
       <c r="J455" s="4"/>
     </row>
     <row r="456">
       <c r="A456" s="4"/>
-      <c r="F456" s="45"/>
+      <c r="F456" s="46"/>
       <c r="J456" s="4"/>
     </row>
     <row r="457">
       <c r="A457" s="4"/>
-      <c r="F457" s="45"/>
+      <c r="F457" s="46"/>
       <c r="J457" s="4"/>
     </row>
     <row r="458">
       <c r="A458" s="4"/>
-      <c r="F458" s="45"/>
+      <c r="F458" s="46"/>
       <c r="J458" s="4"/>
     </row>
     <row r="459">
       <c r="A459" s="4"/>
-      <c r="F459" s="45"/>
+      <c r="F459" s="46"/>
       <c r="J459" s="4"/>
     </row>
     <row r="460">
       <c r="A460" s="4"/>
-      <c r="F460" s="45"/>
+      <c r="F460" s="46"/>
       <c r="J460" s="4"/>
     </row>
     <row r="461">
       <c r="A461" s="4"/>
-      <c r="F461" s="45"/>
+      <c r="F461" s="46"/>
       <c r="J461" s="4"/>
     </row>
     <row r="462">
       <c r="A462" s="4"/>
-      <c r="F462" s="45"/>
+      <c r="F462" s="46"/>
       <c r="J462" s="4"/>
     </row>
     <row r="463">
       <c r="A463" s="4"/>
-      <c r="F463" s="45"/>
+      <c r="F463" s="46"/>
       <c r="J463" s="4"/>
     </row>
     <row r="464">
       <c r="A464" s="4"/>
-      <c r="F464" s="45"/>
+      <c r="F464" s="46"/>
       <c r="J464" s="4"/>
     </row>
     <row r="465">
       <c r="A465" s="4"/>
-      <c r="F465" s="45"/>
+      <c r="F465" s="46"/>
       <c r="J465" s="4"/>
     </row>
     <row r="466">
       <c r="A466" s="4"/>
-      <c r="F466" s="45"/>
+      <c r="F466" s="46"/>
       <c r="J466" s="4"/>
     </row>
     <row r="467">
       <c r="A467" s="4"/>
-      <c r="F467" s="45"/>
+      <c r="F467" s="46"/>
       <c r="J467" s="4"/>
     </row>
     <row r="468">
       <c r="A468" s="4"/>
-      <c r="F468" s="45"/>
+      <c r="F468" s="46"/>
       <c r="J468" s="4"/>
     </row>
     <row r="469">
       <c r="A469" s="4"/>
-      <c r="F469" s="45"/>
+      <c r="F469" s="46"/>
       <c r="J469" s="4"/>
     </row>
     <row r="470">
       <c r="A470" s="4"/>
-      <c r="F470" s="45"/>
+      <c r="F470" s="46"/>
       <c r="J470" s="4"/>
     </row>
     <row r="471">
       <c r="A471" s="4"/>
-      <c r="F471" s="45"/>
+      <c r="F471" s="46"/>
       <c r="J471" s="4"/>
     </row>
     <row r="472">
       <c r="A472" s="4"/>
-      <c r="F472" s="45"/>
+      <c r="F472" s="46"/>
       <c r="J472" s="4"/>
     </row>
     <row r="473">
       <c r="A473" s="4"/>
-      <c r="F473" s="45"/>
+      <c r="F473" s="46"/>
       <c r="J473" s="4"/>
     </row>
     <row r="474">
       <c r="A474" s="4"/>
-      <c r="F474" s="45"/>
+      <c r="F474" s="46"/>
       <c r="J474" s="4"/>
     </row>
     <row r="475">
       <c r="A475" s="4"/>
-      <c r="F475" s="45"/>
+      <c r="F475" s="46"/>
       <c r="J475" s="4"/>
     </row>
     <row r="476">
       <c r="A476" s="4"/>
-      <c r="F476" s="45"/>
+      <c r="F476" s="46"/>
       <c r="J476" s="4"/>
     </row>
     <row r="477">
       <c r="A477" s="4"/>
-      <c r="F477" s="45"/>
+      <c r="F477" s="46"/>
       <c r="J477" s="4"/>
     </row>
     <row r="478">
       <c r="A478" s="4"/>
-      <c r="F478" s="45"/>
+      <c r="F478" s="46"/>
       <c r="J478" s="4"/>
     </row>
     <row r="479">
       <c r="A479" s="4"/>
-      <c r="F479" s="45"/>
+      <c r="F479" s="46"/>
       <c r="J479" s="4"/>
     </row>
     <row r="480">
       <c r="A480" s="4"/>
-      <c r="F480" s="45"/>
+      <c r="F480" s="46"/>
       <c r="J480" s="4"/>
     </row>
     <row r="481">
       <c r="A481" s="4"/>
-      <c r="F481" s="45"/>
+      <c r="F481" s="46"/>
       <c r="J481" s="4"/>
     </row>
     <row r="482">
       <c r="A482" s="4"/>
-      <c r="F482" s="45"/>
+      <c r="F482" s="46"/>
       <c r="J482" s="4"/>
     </row>
     <row r="483">
       <c r="A483" s="4"/>
-      <c r="F483" s="45"/>
+      <c r="F483" s="46"/>
       <c r="J483" s="4"/>
     </row>
     <row r="484">
       <c r="A484" s="4"/>
-      <c r="F484" s="45"/>
+      <c r="F484" s="46"/>
       <c r="J484" s="4"/>
     </row>
     <row r="485">
       <c r="A485" s="4"/>
-      <c r="F485" s="45"/>
+      <c r="F485" s="46"/>
       <c r="J485" s="4"/>
     </row>
     <row r="486">
       <c r="A486" s="4"/>
-      <c r="F486" s="45"/>
+      <c r="F486" s="46"/>
       <c r="J486" s="4"/>
     </row>
     <row r="487">
       <c r="A487" s="4"/>
-      <c r="F487" s="45"/>
+      <c r="F487" s="46"/>
       <c r="J487" s="4"/>
     </row>
     <row r="488">
       <c r="A488" s="4"/>
-      <c r="F488" s="45"/>
+      <c r="F488" s="46"/>
       <c r="J488" s="4"/>
     </row>
     <row r="489">
       <c r="A489" s="4"/>
-      <c r="F489" s="45"/>
+      <c r="F489" s="46"/>
       <c r="J489" s="4"/>
     </row>
     <row r="490">
       <c r="A490" s="4"/>
-      <c r="F490" s="45"/>
+      <c r="F490" s="46"/>
       <c r="J490" s="4"/>
     </row>
     <row r="491">
       <c r="A491" s="4"/>
-      <c r="F491" s="45"/>
+      <c r="F491" s="46"/>
       <c r="J491" s="4"/>
     </row>
     <row r="492">
       <c r="A492" s="4"/>
-      <c r="F492" s="45"/>
+      <c r="F492" s="46"/>
       <c r="J492" s="4"/>
     </row>
     <row r="493">
       <c r="A493" s="4"/>
-      <c r="F493" s="45"/>
+      <c r="F493" s="46"/>
       <c r="J493" s="4"/>
     </row>
     <row r="494">
       <c r="A494" s="4"/>
-      <c r="F494" s="45"/>
+      <c r="F494" s="46"/>
       <c r="J494" s="4"/>
     </row>
     <row r="495">
       <c r="A495" s="4"/>
-      <c r="F495" s="45"/>
+      <c r="F495" s="46"/>
       <c r="J495" s="4"/>
     </row>
     <row r="496">
       <c r="A496" s="4"/>
-      <c r="F496" s="45"/>
+      <c r="F496" s="46"/>
       <c r="J496" s="4"/>
     </row>
     <row r="497">
       <c r="A497" s="4"/>
-      <c r="F497" s="45"/>
+      <c r="F497" s="46"/>
       <c r="J497" s="4"/>
     </row>
     <row r="498">
       <c r="A498" s="4"/>
-      <c r="F498" s="45"/>
+      <c r="F498" s="46"/>
       <c r="J498" s="4"/>
     </row>
     <row r="499">
       <c r="A499" s="4"/>
-      <c r="F499" s="45"/>
+      <c r="F499" s="46"/>
       <c r="J499" s="4"/>
     </row>
     <row r="500">
       <c r="A500" s="4"/>
-      <c r="F500" s="45"/>
+      <c r="F500" s="46"/>
       <c r="J500" s="4"/>
     </row>
     <row r="501">
       <c r="A501" s="4"/>
-      <c r="F501" s="45"/>
+      <c r="F501" s="46"/>
       <c r="J501" s="4"/>
     </row>
     <row r="502">
       <c r="A502" s="4"/>
-      <c r="F502" s="45"/>
+      <c r="F502" s="46"/>
       <c r="J502" s="4"/>
     </row>
     <row r="503">
       <c r="A503" s="4"/>
-      <c r="F503" s="45"/>
+      <c r="F503" s="46"/>
       <c r="J503" s="4"/>
     </row>
     <row r="504">
       <c r="A504" s="4"/>
-      <c r="F504" s="45"/>
+      <c r="F504" s="46"/>
       <c r="J504" s="4"/>
     </row>
     <row r="505">
       <c r="A505" s="4"/>
-      <c r="F505" s="45"/>
+      <c r="F505" s="46"/>
       <c r="J505" s="4"/>
     </row>
     <row r="506">
       <c r="A506" s="4"/>
-      <c r="F506" s="45"/>
+      <c r="F506" s="46"/>
       <c r="J506" s="4"/>
     </row>
     <row r="507">
       <c r="A507" s="4"/>
-      <c r="F507" s="45"/>
+      <c r="F507" s="46"/>
       <c r="J507" s="4"/>
     </row>
     <row r="508">
       <c r="A508" s="4"/>
-      <c r="F508" s="45"/>
+      <c r="F508" s="46"/>
       <c r="J508" s="4"/>
     </row>
     <row r="509">
       <c r="A509" s="4"/>
-      <c r="F509" s="45"/>
+      <c r="F509" s="46"/>
       <c r="J509" s="4"/>
     </row>
     <row r="510">
       <c r="A510" s="4"/>
-      <c r="F510" s="45"/>
+      <c r="F510" s="46"/>
       <c r="J510" s="4"/>
     </row>
     <row r="511">
       <c r="A511" s="4"/>
-      <c r="F511" s="45"/>
+      <c r="F511" s="46"/>
       <c r="J511" s="4"/>
     </row>
     <row r="512">
       <c r="A512" s="4"/>
-      <c r="F512" s="45"/>
+      <c r="F512" s="46"/>
       <c r="J512" s="4"/>
     </row>
     <row r="513">
       <c r="A513" s="4"/>
-      <c r="F513" s="45"/>
+      <c r="F513" s="46"/>
       <c r="J513" s="4"/>
     </row>
     <row r="514">
       <c r="A514" s="4"/>
-      <c r="F514" s="45"/>
+      <c r="F514" s="46"/>
       <c r="J514" s="4"/>
     </row>
     <row r="515">
       <c r="A515" s="4"/>
-      <c r="F515" s="45"/>
+      <c r="F515" s="46"/>
       <c r="J515" s="4"/>
     </row>
     <row r="516">
       <c r="A516" s="4"/>
-      <c r="F516" s="45"/>
+      <c r="F516" s="46"/>
       <c r="J516" s="4"/>
     </row>
     <row r="517">
       <c r="A517" s="4"/>
-      <c r="F517" s="45"/>
+      <c r="F517" s="46"/>
       <c r="J517" s="4"/>
     </row>
     <row r="518">
       <c r="A518" s="4"/>
-      <c r="F518" s="45"/>
+      <c r="F518" s="46"/>
       <c r="J518" s="4"/>
     </row>
     <row r="519">
       <c r="A519" s="4"/>
-      <c r="F519" s="45"/>
+      <c r="F519" s="46"/>
       <c r="J519" s="4"/>
     </row>
     <row r="520">
       <c r="A520" s="4"/>
-      <c r="F520" s="45"/>
+      <c r="F520" s="46"/>
       <c r="J520" s="4"/>
     </row>
     <row r="521">
       <c r="A521" s="4"/>
-      <c r="F521" s="45"/>
+      <c r="F521" s="46"/>
       <c r="J521" s="4"/>
     </row>
     <row r="522">
       <c r="A522" s="4"/>
-      <c r="F522" s="45"/>
+      <c r="F522" s="46"/>
       <c r="J522" s="4"/>
     </row>
     <row r="523">
       <c r="A523" s="4"/>
-      <c r="F523" s="45"/>
+      <c r="F523" s="46"/>
       <c r="J523" s="4"/>
     </row>
     <row r="524">
       <c r="A524" s="4"/>
-      <c r="F524" s="45"/>
+      <c r="F524" s="46"/>
       <c r="J524" s="4"/>
     </row>
     <row r="525">
       <c r="A525" s="4"/>
-      <c r="F525" s="45"/>
+      <c r="F525" s="46"/>
       <c r="J525" s="4"/>
     </row>
     <row r="526">
       <c r="A526" s="4"/>
-      <c r="F526" s="45"/>
+      <c r="F526" s="46"/>
       <c r="J526" s="4"/>
     </row>
     <row r="527">
       <c r="A527" s="4"/>
-      <c r="F527" s="45"/>
+      <c r="F527" s="46"/>
       <c r="J527" s="4"/>
     </row>
     <row r="528">
       <c r="A528" s="4"/>
-      <c r="F528" s="45"/>
+      <c r="F528" s="46"/>
       <c r="J528" s="4"/>
     </row>
     <row r="529">
       <c r="A529" s="4"/>
-      <c r="F529" s="45"/>
+      <c r="F529" s="46"/>
       <c r="J529" s="4"/>
     </row>
     <row r="530">
       <c r="A530" s="4"/>
-      <c r="F530" s="45"/>
+      <c r="F530" s="46"/>
       <c r="J530" s="4"/>
     </row>
     <row r="531">
       <c r="A531" s="4"/>
-      <c r="F531" s="45"/>
+      <c r="F531" s="46"/>
       <c r="J531" s="4"/>
     </row>
     <row r="532">
       <c r="A532" s="4"/>
-      <c r="F532" s="45"/>
+      <c r="F532" s="46"/>
       <c r="J532" s="4"/>
     </row>
     <row r="533">
       <c r="A533" s="4"/>
-      <c r="F533" s="45"/>
+      <c r="F533" s="46"/>
       <c r="J533" s="4"/>
     </row>
     <row r="534">
       <c r="A534" s="4"/>
-      <c r="F534" s="45"/>
+      <c r="F534" s="46"/>
       <c r="J534" s="4"/>
     </row>
     <row r="535">
       <c r="A535" s="4"/>
-      <c r="F535" s="45"/>
+      <c r="F535" s="46"/>
       <c r="J535" s="4"/>
     </row>
     <row r="536">
       <c r="A536" s="4"/>
-      <c r="F536" s="45"/>
+      <c r="F536" s="46"/>
       <c r="J536" s="4"/>
     </row>
     <row r="537">
       <c r="A537" s="4"/>
-      <c r="F537" s="45"/>
+      <c r="F537" s="46"/>
       <c r="J537" s="4"/>
     </row>
     <row r="538">
       <c r="A538" s="4"/>
-      <c r="F538" s="45"/>
+      <c r="F538" s="46"/>
       <c r="J538" s="4"/>
     </row>
     <row r="539">
       <c r="A539" s="4"/>
-      <c r="F539" s="45"/>
+      <c r="F539" s="46"/>
       <c r="J539" s="4"/>
     </row>
     <row r="540">
       <c r="A540" s="4"/>
-      <c r="F540" s="45"/>
+      <c r="F540" s="46"/>
       <c r="J540" s="4"/>
     </row>
     <row r="541">
       <c r="A541" s="4"/>
-      <c r="F541" s="45"/>
+      <c r="F541" s="46"/>
       <c r="J541" s="4"/>
     </row>
     <row r="542">
       <c r="A542" s="4"/>
-      <c r="F542" s="45"/>
+      <c r="F542" s="46"/>
       <c r="J542" s="4"/>
     </row>
     <row r="543">
       <c r="A543" s="4"/>
-      <c r="F543" s="45"/>
+      <c r="F543" s="46"/>
       <c r="J543" s="4"/>
     </row>
     <row r="544">
       <c r="A544" s="4"/>
-      <c r="F544" s="45"/>
+      <c r="F544" s="46"/>
       <c r="J544" s="4"/>
     </row>
     <row r="545">
       <c r="A545" s="4"/>
-      <c r="F545" s="45"/>
+      <c r="F545" s="46"/>
       <c r="J545" s="4"/>
     </row>
     <row r="546">
       <c r="A546" s="4"/>
-      <c r="F546" s="45"/>
+      <c r="F546" s="46"/>
       <c r="J546" s="4"/>
     </row>
     <row r="547">
       <c r="A547" s="4"/>
-      <c r="F547" s="45"/>
+      <c r="F547" s="46"/>
       <c r="J547" s="4"/>
     </row>
     <row r="548">
       <c r="A548" s="4"/>
-      <c r="F548" s="45"/>
+      <c r="F548" s="46"/>
       <c r="J548" s="4"/>
     </row>
     <row r="549">
       <c r="A549" s="4"/>
-      <c r="F549" s="45"/>
+      <c r="F549" s="46"/>
       <c r="J549" s="4"/>
     </row>
     <row r="550">
       <c r="A550" s="4"/>
-      <c r="F550" s="45"/>
+      <c r="F550" s="46"/>
       <c r="J550" s="4"/>
     </row>
     <row r="551">
       <c r="A551" s="4"/>
-      <c r="F551" s="45"/>
+      <c r="F551" s="46"/>
       <c r="J551" s="4"/>
     </row>
     <row r="552">
       <c r="A552" s="4"/>
-      <c r="F552" s="45"/>
+      <c r="F552" s="46"/>
       <c r="J552" s="4"/>
     </row>
     <row r="553">
       <c r="A553" s="4"/>
-      <c r="F553" s="45"/>
+      <c r="F553" s="46"/>
       <c r="J553" s="4"/>
     </row>
     <row r="554">
       <c r="A554" s="4"/>
-      <c r="F554" s="45"/>
+      <c r="F554" s="46"/>
       <c r="J554" s="4"/>
     </row>
     <row r="555">
       <c r="A555" s="4"/>
-      <c r="F555" s="45"/>
+      <c r="F555" s="46"/>
       <c r="J555" s="4"/>
     </row>
     <row r="556">
       <c r="A556" s="4"/>
-      <c r="F556" s="45"/>
+      <c r="F556" s="46"/>
       <c r="J556" s="4"/>
     </row>
     <row r="557">
       <c r="A557" s="4"/>
-      <c r="F557" s="45"/>
+      <c r="F557" s="46"/>
       <c r="J557" s="4"/>
     </row>
     <row r="558">
       <c r="A558" s="4"/>
-      <c r="F558" s="45"/>
+      <c r="F558" s="46"/>
       <c r="J558" s="4"/>
     </row>
     <row r="559">
       <c r="A559" s="4"/>
-      <c r="F559" s="45"/>
+      <c r="F559" s="46"/>
       <c r="J559" s="4"/>
     </row>
     <row r="560">
       <c r="A560" s="4"/>
-      <c r="F560" s="45"/>
+      <c r="F560" s="46"/>
       <c r="J560" s="4"/>
     </row>
     <row r="561">
       <c r="A561" s="4"/>
-      <c r="F561" s="45"/>
+      <c r="F561" s="46"/>
       <c r="J561" s="4"/>
     </row>
     <row r="562">
       <c r="A562" s="4"/>
-      <c r="F562" s="45"/>
+      <c r="F562" s="46"/>
       <c r="J562" s="4"/>
     </row>
     <row r="563">
       <c r="A563" s="4"/>
-      <c r="F563" s="45"/>
+      <c r="F563" s="46"/>
       <c r="J563" s="4"/>
     </row>
     <row r="564">
       <c r="A564" s="4"/>
-      <c r="F564" s="45"/>
+      <c r="F564" s="46"/>
       <c r="J564" s="4"/>
     </row>
     <row r="565">
       <c r="A565" s="4"/>
-      <c r="F565" s="45"/>
+      <c r="F565" s="46"/>
       <c r="J565" s="4"/>
     </row>
     <row r="566">
       <c r="A566" s="4"/>
-      <c r="F566" s="45"/>
+      <c r="F566" s="46"/>
       <c r="J566" s="4"/>
     </row>
     <row r="567">
       <c r="A567" s="4"/>
-      <c r="F567" s="45"/>
+      <c r="F567" s="46"/>
       <c r="J567" s="4"/>
     </row>
     <row r="568">
       <c r="A568" s="4"/>
-      <c r="F568" s="45"/>
+      <c r="F568" s="46"/>
       <c r="J568" s="4"/>
     </row>
     <row r="569">
       <c r="A569" s="4"/>
-      <c r="F569" s="45"/>
+      <c r="F569" s="46"/>
       <c r="J569" s="4"/>
     </row>
     <row r="570">
       <c r="A570" s="4"/>
-      <c r="F570" s="45"/>
+      <c r="F570" s="46"/>
       <c r="J570" s="4"/>
     </row>
     <row r="571">
       <c r="A571" s="4"/>
-      <c r="F571" s="45"/>
+      <c r="F571" s="46"/>
       <c r="J571" s="4"/>
     </row>
     <row r="572">
       <c r="A572" s="4"/>
-      <c r="F572" s="45"/>
+      <c r="F572" s="46"/>
       <c r="J572" s="4"/>
     </row>
     <row r="573">
       <c r="A573" s="4"/>
-      <c r="F573" s="45"/>
+      <c r="F573" s="46"/>
       <c r="J573" s="4"/>
     </row>
     <row r="574">
       <c r="A574" s="4"/>
-      <c r="F574" s="45"/>
+      <c r="F574" s="46"/>
       <c r="J574" s="4"/>
     </row>
     <row r="575">
       <c r="A575" s="4"/>
-      <c r="F575" s="45"/>
+      <c r="F575" s="46"/>
       <c r="J575" s="4"/>
     </row>
     <row r="576">
       <c r="A576" s="4"/>
-      <c r="F576" s="45"/>
+      <c r="F576" s="46"/>
       <c r="J576" s="4"/>
     </row>
     <row r="577">
       <c r="A577" s="4"/>
-      <c r="F577" s="45"/>
+      <c r="F577" s="46"/>
       <c r="J577" s="4"/>
     </row>
     <row r="578">
       <c r="A578" s="4"/>
-      <c r="F578" s="45"/>
+      <c r="F578" s="46"/>
       <c r="J578" s="4"/>
     </row>
     <row r="579">
       <c r="A579" s="4"/>
-      <c r="F579" s="45"/>
+      <c r="F579" s="46"/>
       <c r="J579" s="4"/>
     </row>
     <row r="580">
       <c r="A580" s="4"/>
-      <c r="F580" s="45"/>
+      <c r="F580" s="46"/>
       <c r="J580" s="4"/>
     </row>
     <row r="581">
       <c r="A581" s="4"/>
-      <c r="F581" s="45"/>
+      <c r="F581" s="46"/>
       <c r="J581" s="4"/>
     </row>
     <row r="582">
       <c r="A582" s="4"/>
-      <c r="F582" s="45"/>
+      <c r="F582" s="46"/>
       <c r="J582" s="4"/>
     </row>
     <row r="583">
       <c r="A583" s="4"/>
-      <c r="F583" s="45"/>
+      <c r="F583" s="46"/>
       <c r="J583" s="4"/>
     </row>
     <row r="584">
       <c r="A584" s="4"/>
-      <c r="F584" s="45"/>
+      <c r="F584" s="46"/>
       <c r="J584" s="4"/>
     </row>
     <row r="585">
       <c r="A585" s="4"/>
-      <c r="F585" s="45"/>
+      <c r="F585" s="46"/>
       <c r="J585" s="4"/>
     </row>
     <row r="586">
       <c r="A586" s="4"/>
-      <c r="F586" s="45"/>
+      <c r="F586" s="46"/>
       <c r="J586" s="4"/>
     </row>
     <row r="587">
       <c r="A587" s="4"/>
-      <c r="F587" s="45"/>
+      <c r="F587" s="46"/>
       <c r="J587" s="4"/>
     </row>
     <row r="588">
       <c r="A588" s="4"/>
-      <c r="F588" s="45"/>
+      <c r="F588" s="46"/>
       <c r="J588" s="4"/>
     </row>
     <row r="589">
       <c r="A589" s="4"/>
-      <c r="F589" s="45"/>
+      <c r="F589" s="46"/>
       <c r="J589" s="4"/>
     </row>
     <row r="590">
       <c r="A590" s="4"/>
-      <c r="F590" s="45"/>
+      <c r="F590" s="46"/>
       <c r="J590" s="4"/>
     </row>
     <row r="591">
       <c r="A591" s="4"/>
-      <c r="F591" s="45"/>
+      <c r="F591" s="46"/>
       <c r="J591" s="4"/>
     </row>
     <row r="592">
       <c r="A592" s="4"/>
-      <c r="F592" s="45"/>
+      <c r="F592" s="46"/>
       <c r="J592" s="4"/>
     </row>
     <row r="593">
       <c r="A593" s="4"/>
-      <c r="F593" s="45"/>
+      <c r="F593" s="46"/>
       <c r="J593" s="4"/>
     </row>
     <row r="594">
       <c r="A594" s="4"/>
-      <c r="F594" s="45"/>
+      <c r="F594" s="46"/>
       <c r="J594" s="4"/>
     </row>
     <row r="595">
       <c r="A595" s="4"/>
-      <c r="F595" s="45"/>
+      <c r="F595" s="46"/>
       <c r="J595" s="4"/>
     </row>
     <row r="596">
       <c r="A596" s="4"/>
-      <c r="F596" s="45"/>
+      <c r="F596" s="46"/>
       <c r="J596" s="4"/>
     </row>
     <row r="597">
       <c r="A597" s="4"/>
-      <c r="F597" s="45"/>
+      <c r="F597" s="46"/>
       <c r="J597" s="4"/>
     </row>
     <row r="598">
       <c r="A598" s="4"/>
-      <c r="F598" s="45"/>
+      <c r="F598" s="46"/>
       <c r="J598" s="4"/>
     </row>
     <row r="599">
       <c r="A599" s="4"/>
-      <c r="F599" s="45"/>
+      <c r="F599" s="46"/>
       <c r="J599" s="4"/>
     </row>
     <row r="600">
       <c r="A600" s="4"/>
-      <c r="F600" s="45"/>
+      <c r="F600" s="46"/>
       <c r="J600" s="4"/>
     </row>
     <row r="601">
       <c r="A601" s="4"/>
-      <c r="F601" s="45"/>
+      <c r="F601" s="46"/>
       <c r="J601" s="4"/>
     </row>
     <row r="602">
       <c r="A602" s="4"/>
-      <c r="F602" s="45"/>
+      <c r="F602" s="46"/>
       <c r="J602" s="4"/>
     </row>
     <row r="603">
       <c r="A603" s="4"/>
-      <c r="F603" s="45"/>
+      <c r="F603" s="46"/>
       <c r="J603" s="4"/>
     </row>
     <row r="604">
       <c r="A604" s="4"/>
-      <c r="F604" s="45"/>
+      <c r="F604" s="46"/>
       <c r="J604" s="4"/>
     </row>
     <row r="605">
       <c r="A605" s="4"/>
-      <c r="F605" s="45"/>
+      <c r="F605" s="46"/>
       <c r="J605" s="4"/>
     </row>
     <row r="606">
       <c r="A606" s="4"/>
-      <c r="F606" s="45"/>
+      <c r="F606" s="46"/>
       <c r="J606" s="4"/>
     </row>
     <row r="607">
       <c r="A607" s="4"/>
-      <c r="F607" s="45"/>
+      <c r="F607" s="46"/>
       <c r="J607" s="4"/>
     </row>
     <row r="608">
       <c r="A608" s="4"/>
-      <c r="F608" s="45"/>
+      <c r="F608" s="46"/>
       <c r="J608" s="4"/>
     </row>
     <row r="609">
       <c r="A609" s="4"/>
-      <c r="F609" s="45"/>
+      <c r="F609" s="46"/>
       <c r="J609" s="4"/>
     </row>
     <row r="610">
       <c r="A610" s="4"/>
-      <c r="F610" s="45"/>
+      <c r="F610" s="46"/>
       <c r="J610" s="4"/>
     </row>
     <row r="611">
       <c r="A611" s="4"/>
-      <c r="F611" s="45"/>
+      <c r="F611" s="46"/>
       <c r="J611" s="4"/>
     </row>
     <row r="612">
       <c r="A612" s="4"/>
-      <c r="F612" s="45"/>
+      <c r="F612" s="46"/>
       <c r="J612" s="4"/>
     </row>
     <row r="613">
       <c r="A613" s="4"/>
-      <c r="F613" s="45"/>
+      <c r="F613" s="46"/>
       <c r="J613" s="4"/>
     </row>
     <row r="614">
       <c r="A614" s="4"/>
-      <c r="F614" s="45"/>
+      <c r="F614" s="46"/>
       <c r="J614" s="4"/>
     </row>
     <row r="615">
       <c r="A615" s="4"/>
-      <c r="F615" s="45"/>
+      <c r="F615" s="46"/>
       <c r="J615" s="4"/>
     </row>
     <row r="616">
       <c r="A616" s="4"/>
-      <c r="F616" s="45"/>
+      <c r="F616" s="46"/>
       <c r="J616" s="4"/>
     </row>
     <row r="617">
       <c r="A617" s="4"/>
-      <c r="F617" s="45"/>
+      <c r="F617" s="46"/>
       <c r="J617" s="4"/>
     </row>
     <row r="618">
       <c r="A618" s="4"/>
-      <c r="F618" s="45"/>
+      <c r="F618" s="46"/>
       <c r="J618" s="4"/>
     </row>
     <row r="619">
       <c r="A619" s="4"/>
-      <c r="F619" s="45"/>
+      <c r="F619" s="46"/>
       <c r="J619" s="4"/>
     </row>
     <row r="620">
       <c r="A620" s="4"/>
-      <c r="F620" s="45"/>
+      <c r="F620" s="46"/>
       <c r="J620" s="4"/>
     </row>
     <row r="621">
       <c r="A621" s="4"/>
-      <c r="F621" s="45"/>
+      <c r="F621" s="46"/>
       <c r="J621" s="4"/>
     </row>
     <row r="622">
       <c r="A622" s="4"/>
-      <c r="F622" s="45"/>
+      <c r="F622" s="46"/>
       <c r="J622" s="4"/>
     </row>
     <row r="623">
       <c r="A623" s="4"/>
-      <c r="F623" s="45"/>
+      <c r="F623" s="46"/>
       <c r="J623" s="4"/>
     </row>
     <row r="624">
       <c r="A624" s="4"/>
-      <c r="F624" s="45"/>
+      <c r="F624" s="46"/>
       <c r="J624" s="4"/>
     </row>
     <row r="625">
       <c r="A625" s="4"/>
-      <c r="F625" s="45"/>
+      <c r="F625" s="46"/>
       <c r="J625" s="4"/>
     </row>
     <row r="626">
       <c r="A626" s="4"/>
-      <c r="F626" s="45"/>
+      <c r="F626" s="46"/>
       <c r="J626" s="4"/>
     </row>
     <row r="627">
       <c r="A627" s="4"/>
-      <c r="F627" s="45"/>
+      <c r="F627" s="46"/>
       <c r="J627" s="4"/>
     </row>
     <row r="628">
       <c r="A628" s="4"/>
-      <c r="F628" s="45"/>
+      <c r="F628" s="46"/>
       <c r="J628" s="4"/>
     </row>
     <row r="629">
       <c r="A629" s="4"/>
-      <c r="F629" s="45"/>
+      <c r="F629" s="46"/>
       <c r="J629" s="4"/>
     </row>
     <row r="630">
       <c r="A630" s="4"/>
-      <c r="F630" s="45"/>
+      <c r="F630" s="46"/>
       <c r="J630" s="4"/>
     </row>
     <row r="631">
       <c r="A631" s="4"/>
-      <c r="F631" s="45"/>
+      <c r="F631" s="46"/>
       <c r="J631" s="4"/>
     </row>
     <row r="632">
       <c r="A632" s="4"/>
-      <c r="F632" s="45"/>
+      <c r="F632" s="46"/>
       <c r="J632" s="4"/>
     </row>
     <row r="633">
       <c r="A633" s="4"/>
-      <c r="F633" s="45"/>
+      <c r="F633" s="46"/>
       <c r="J633" s="4"/>
     </row>
     <row r="634">
       <c r="A634" s="4"/>
-      <c r="F634" s="45"/>
+      <c r="F634" s="46"/>
       <c r="J634" s="4"/>
     </row>
     <row r="635">
       <c r="A635" s="4"/>
-      <c r="F635" s="45"/>
+      <c r="F635" s="46"/>
       <c r="J635" s="4"/>
     </row>
     <row r="636">
       <c r="A636" s="4"/>
-      <c r="F636" s="45"/>
+      <c r="F636" s="46"/>
       <c r="J636" s="4"/>
     </row>
     <row r="637">
       <c r="A637" s="4"/>
-      <c r="F637" s="45"/>
+      <c r="F637" s="46"/>
       <c r="J637" s="4"/>
     </row>
     <row r="638">
       <c r="A638" s="4"/>
-      <c r="F638" s="45"/>
+      <c r="F638" s="46"/>
       <c r="J638" s="4"/>
     </row>
     <row r="639">
       <c r="A639" s="4"/>
-      <c r="F639" s="45"/>
+      <c r="F639" s="46"/>
       <c r="J639" s="4"/>
     </row>
     <row r="640">
       <c r="A640" s="4"/>
-      <c r="F640" s="45"/>
+      <c r="F640" s="46"/>
       <c r="J640" s="4"/>
     </row>
     <row r="641">
       <c r="A641" s="4"/>
-      <c r="F641" s="45"/>
+      <c r="F641" s="46"/>
       <c r="J641" s="4"/>
     </row>
     <row r="642">
       <c r="A642" s="4"/>
-      <c r="F642" s="45"/>
+      <c r="F642" s="46"/>
       <c r="J642" s="4"/>
     </row>
     <row r="643">
       <c r="A643" s="4"/>
-      <c r="F643" s="45"/>
+      <c r="F643" s="46"/>
       <c r="J643" s="4"/>
     </row>
     <row r="644">
       <c r="A644" s="4"/>
-      <c r="F644" s="45"/>
+      <c r="F644" s="46"/>
       <c r="J644" s="4"/>
     </row>
     <row r="645">
       <c r="A645" s="4"/>
-      <c r="F645" s="45"/>
+      <c r="F645" s="46"/>
       <c r="J645" s="4"/>
     </row>
     <row r="646">
       <c r="A646" s="4"/>
-      <c r="F646" s="45"/>
+      <c r="F646" s="46"/>
       <c r="J646" s="4"/>
     </row>
     <row r="647">
       <c r="A647" s="4"/>
-      <c r="F647" s="45"/>
+      <c r="F647" s="46"/>
       <c r="J647" s="4"/>
     </row>
     <row r="648">
       <c r="A648" s="4"/>
-      <c r="F648" s="45"/>
+      <c r="F648" s="46"/>
       <c r="J648" s="4"/>
     </row>
     <row r="649">
       <c r="A649" s="4"/>
-      <c r="F649" s="45"/>
+      <c r="F649" s="46"/>
       <c r="J649" s="4"/>
     </row>
     <row r="650">
       <c r="A650" s="4"/>
-      <c r="F650" s="45"/>
+      <c r="F650" s="46"/>
       <c r="J650" s="4"/>
     </row>
     <row r="651">
       <c r="A651" s="4"/>
-      <c r="F651" s="45"/>
+      <c r="F651" s="46"/>
       <c r="J651" s="4"/>
     </row>
     <row r="652">
       <c r="A652" s="4"/>
-      <c r="F652" s="45"/>
+      <c r="F652" s="46"/>
       <c r="J652" s="4"/>
     </row>
     <row r="653">
       <c r="A653" s="4"/>
-      <c r="F653" s="45"/>
+      <c r="F653" s="46"/>
       <c r="J653" s="4"/>
     </row>
     <row r="654">
       <c r="A654" s="4"/>
-      <c r="F654" s="45"/>
+      <c r="F654" s="46"/>
       <c r="J654" s="4"/>
     </row>
     <row r="655">
       <c r="A655" s="4"/>
-      <c r="F655" s="45"/>
+      <c r="F655" s="46"/>
       <c r="J655" s="4"/>
     </row>
     <row r="656">
       <c r="A656" s="4"/>
-      <c r="F656" s="45"/>
+      <c r="F656" s="46"/>
       <c r="J656" s="4"/>
     </row>
     <row r="657">
       <c r="A657" s="4"/>
-      <c r="F657" s="45"/>
+      <c r="F657" s="46"/>
       <c r="J657" s="4"/>
     </row>
     <row r="658">
       <c r="A658" s="4"/>
-      <c r="F658" s="45"/>
+      <c r="F658" s="46"/>
       <c r="J658" s="4"/>
     </row>
     <row r="659">
       <c r="A659" s="4"/>
-      <c r="F659" s="45"/>
+      <c r="F659" s="46"/>
       <c r="J659" s="4"/>
     </row>
     <row r="660">
       <c r="A660" s="4"/>
-      <c r="F660" s="45"/>
+      <c r="F660" s="46"/>
       <c r="J660" s="4"/>
     </row>
     <row r="661">
       <c r="A661" s="4"/>
-      <c r="F661" s="45"/>
+      <c r="F661" s="46"/>
       <c r="J661" s="4"/>
     </row>
     <row r="662">
       <c r="A662" s="4"/>
-      <c r="F662" s="45"/>
+      <c r="F662" s="46"/>
       <c r="J662" s="4"/>
     </row>
     <row r="663">
       <c r="A663" s="4"/>
-      <c r="F663" s="45"/>
+      <c r="F663" s="46"/>
       <c r="J663" s="4"/>
     </row>
     <row r="664">
       <c r="A664" s="4"/>
-      <c r="F664" s="45"/>
+      <c r="F664" s="46"/>
       <c r="J664" s="4"/>
     </row>
     <row r="665">
       <c r="A665" s="4"/>
-      <c r="F665" s="45"/>
+      <c r="F665" s="46"/>
       <c r="J665" s="4"/>
     </row>
     <row r="666">
       <c r="A666" s="4"/>
-      <c r="F666" s="45"/>
+      <c r="F666" s="46"/>
       <c r="J666" s="4"/>
     </row>
     <row r="667">
       <c r="A667" s="4"/>
-      <c r="F667" s="45"/>
+      <c r="F667" s="46"/>
       <c r="J667" s="4"/>
     </row>
     <row r="668">
       <c r="A668" s="4"/>
-      <c r="F668" s="45"/>
+      <c r="F668" s="46"/>
       <c r="J668" s="4"/>
     </row>
     <row r="669">
       <c r="A669" s="4"/>
-      <c r="F669" s="45"/>
+      <c r="F669" s="46"/>
       <c r="J669" s="4"/>
     </row>
     <row r="670">
       <c r="A670" s="4"/>
-      <c r="F670" s="45"/>
+      <c r="F670" s="46"/>
       <c r="J670" s="4"/>
     </row>
     <row r="671">
       <c r="A671" s="4"/>
-      <c r="F671" s="45"/>
+      <c r="F671" s="46"/>
       <c r="J671" s="4"/>
     </row>
     <row r="672">
       <c r="A672" s="4"/>
-      <c r="F672" s="45"/>
+      <c r="F672" s="46"/>
       <c r="J672" s="4"/>
     </row>
     <row r="673">
       <c r="A673" s="4"/>
-      <c r="F673" s="45"/>
+      <c r="F673" s="46"/>
       <c r="J673" s="4"/>
     </row>
     <row r="674">
       <c r="A674" s="4"/>
-      <c r="F674" s="45"/>
+      <c r="F674" s="46"/>
       <c r="J674" s="4"/>
     </row>
     <row r="675">
       <c r="A675" s="4"/>
-      <c r="F675" s="45"/>
+      <c r="F675" s="46"/>
       <c r="J675" s="4"/>
     </row>
     <row r="676">
       <c r="A676" s="4"/>
-      <c r="F676" s="45"/>
+      <c r="F676" s="46"/>
       <c r="J676" s="4"/>
     </row>
     <row r="677">
       <c r="A677" s="4"/>
-      <c r="F677" s="45"/>
+      <c r="F677" s="46"/>
       <c r="J677" s="4"/>
     </row>
     <row r="678">
       <c r="A678" s="4"/>
-      <c r="F678" s="45"/>
+      <c r="F678" s="46"/>
       <c r="J678" s="4"/>
     </row>
     <row r="679">
       <c r="A679" s="4"/>
-      <c r="F679" s="45"/>
+      <c r="F679" s="46"/>
       <c r="J679" s="4"/>
     </row>
     <row r="680">
       <c r="A680" s="4"/>
-      <c r="F680" s="45"/>
+      <c r="F680" s="46"/>
       <c r="J680" s="4"/>
     </row>
     <row r="681">
       <c r="A681" s="4"/>
-      <c r="F681" s="45"/>
+      <c r="F681" s="46"/>
       <c r="J681" s="4"/>
     </row>
     <row r="682">
       <c r="A682" s="4"/>
-      <c r="F682" s="45"/>
+      <c r="F682" s="46"/>
       <c r="J682" s="4"/>
     </row>
     <row r="683">
       <c r="A683" s="4"/>
-      <c r="F683" s="45"/>
+      <c r="F683" s="46"/>
       <c r="J683" s="4"/>
     </row>
     <row r="684">
       <c r="A684" s="4"/>
-      <c r="F684" s="45"/>
+      <c r="F684" s="46"/>
       <c r="J684" s="4"/>
     </row>
     <row r="685">
       <c r="A685" s="4"/>
-      <c r="F685" s="45"/>
+      <c r="F685" s="46"/>
       <c r="J685" s="4"/>
     </row>
     <row r="686">
       <c r="A686" s="4"/>
-      <c r="F686" s="45"/>
+      <c r="F686" s="46"/>
       <c r="J686" s="4"/>
     </row>
     <row r="687">
       <c r="A687" s="4"/>
-      <c r="F687" s="45"/>
+      <c r="F687" s="46"/>
       <c r="J687" s="4"/>
     </row>
     <row r="688">
       <c r="A688" s="4"/>
-      <c r="F688" s="45"/>
+      <c r="F688" s="46"/>
       <c r="J688" s="4"/>
     </row>
     <row r="689">
       <c r="A689" s="4"/>
-      <c r="F689" s="45"/>
+      <c r="F689" s="46"/>
       <c r="J689" s="4"/>
     </row>
     <row r="690">
       <c r="A690" s="4"/>
-      <c r="F690" s="45"/>
+      <c r="F690" s="46"/>
       <c r="J690" s="4"/>
     </row>
     <row r="691">
       <c r="A691" s="4"/>
-      <c r="F691" s="45"/>
+      <c r="F691" s="46"/>
       <c r="J691" s="4"/>
     </row>
     <row r="692">
       <c r="A692" s="4"/>
-      <c r="F692" s="45"/>
+      <c r="F692" s="46"/>
       <c r="J692" s="4"/>
     </row>
     <row r="693">
       <c r="A693" s="4"/>
-      <c r="F693" s="45"/>
+      <c r="F693" s="46"/>
       <c r="J693" s="4"/>
     </row>
     <row r="694">
       <c r="A694" s="4"/>
-      <c r="F694" s="45"/>
+      <c r="F694" s="46"/>
       <c r="J694" s="4"/>
     </row>
     <row r="695">
       <c r="A695" s="4"/>
-      <c r="F695" s="45"/>
+      <c r="F695" s="46"/>
       <c r="J695" s="4"/>
     </row>
     <row r="696">
       <c r="A696" s="4"/>
-      <c r="F696" s="45"/>
+      <c r="F696" s="46"/>
       <c r="J696" s="4"/>
     </row>
     <row r="697">
       <c r="A697" s="4"/>
-      <c r="F697" s="45"/>
+      <c r="F697" s="46"/>
       <c r="J697" s="4"/>
     </row>
     <row r="698">
       <c r="A698" s="4"/>
-      <c r="F698" s="45"/>
+      <c r="F698" s="46"/>
       <c r="J698" s="4"/>
     </row>
     <row r="699">
       <c r="A699" s="4"/>
-      <c r="F699" s="45"/>
+      <c r="F699" s="46"/>
       <c r="J699" s="4"/>
     </row>
     <row r="700">
       <c r="A700" s="4"/>
-      <c r="F700" s="45"/>
+      <c r="F700" s="46"/>
       <c r="J700" s="4"/>
     </row>
     <row r="701">
       <c r="A701" s="4"/>
-      <c r="F701" s="45"/>
+      <c r="F701" s="46"/>
       <c r="J701" s="4"/>
     </row>
     <row r="702">
       <c r="A702" s="4"/>
-      <c r="F702" s="45"/>
+      <c r="F702" s="46"/>
       <c r="J702" s="4"/>
     </row>
     <row r="703">
       <c r="A703" s="4"/>
-      <c r="F703" s="45"/>
+      <c r="F703" s="46"/>
       <c r="J703" s="4"/>
     </row>
     <row r="704">
       <c r="A704" s="4"/>
-      <c r="F704" s="45"/>
+      <c r="F704" s="46"/>
       <c r="J704" s="4"/>
     </row>
     <row r="705">
       <c r="A705" s="4"/>
-      <c r="F705" s="45"/>
+      <c r="F705" s="46"/>
       <c r="J705" s="4"/>
     </row>
     <row r="706">
       <c r="A706" s="4"/>
-      <c r="F706" s="45"/>
+      <c r="F706" s="46"/>
       <c r="J706" s="4"/>
     </row>
     <row r="707">
       <c r="A707" s="4"/>
-      <c r="F707" s="45"/>
+      <c r="F707" s="46"/>
       <c r="J707" s="4"/>
     </row>
     <row r="708">
       <c r="A708" s="4"/>
-      <c r="F708" s="45"/>
+      <c r="F708" s="46"/>
       <c r="J708" s="4"/>
     </row>
     <row r="709">
       <c r="A709" s="4"/>
-      <c r="F709" s="45"/>
+      <c r="F709" s="46"/>
       <c r="J709" s="4"/>
     </row>
     <row r="710">
       <c r="A710" s="4"/>
-      <c r="F710" s="45"/>
+      <c r="F710" s="46"/>
       <c r="J710" s="4"/>
     </row>
     <row r="711">
       <c r="A711" s="4"/>
-      <c r="F711" s="45"/>
+      <c r="F711" s="46"/>
       <c r="J711" s="4"/>
     </row>
     <row r="712">
       <c r="A712" s="4"/>
-      <c r="F712" s="45"/>
+      <c r="F712" s="46"/>
       <c r="J712" s="4"/>
     </row>
     <row r="713">
       <c r="A713" s="4"/>
-      <c r="F713" s="45"/>
+      <c r="F713" s="46"/>
       <c r="J713" s="4"/>
     </row>
     <row r="714">
       <c r="A714" s="4"/>
-      <c r="F714" s="45"/>
+      <c r="F714" s="46"/>
       <c r="J714" s="4"/>
     </row>
     <row r="715">
       <c r="A715" s="4"/>
-      <c r="F715" s="45"/>
+      <c r="F715" s="46"/>
       <c r="J715" s="4"/>
     </row>
     <row r="716">
       <c r="A716" s="4"/>
-      <c r="F716" s="45"/>
+      <c r="F716" s="46"/>
       <c r="J716" s="4"/>
     </row>
     <row r="717">
       <c r="A717" s="4"/>
-      <c r="F717" s="45"/>
+      <c r="F717" s="46"/>
       <c r="J717" s="4"/>
     </row>
     <row r="718">
       <c r="A718" s="4"/>
-      <c r="F718" s="45"/>
+      <c r="F718" s="46"/>
       <c r="J718" s="4"/>
     </row>
     <row r="719">
       <c r="A719" s="4"/>
-      <c r="F719" s="45"/>
+      <c r="F719" s="46"/>
       <c r="J719" s="4"/>
     </row>
     <row r="720">
       <c r="A720" s="4"/>
-      <c r="F720" s="45"/>
+      <c r="F720" s="46"/>
       <c r="J720" s="4"/>
     </row>
     <row r="721">
       <c r="A721" s="4"/>
-      <c r="F721" s="45"/>
+      <c r="F721" s="46"/>
       <c r="J721" s="4"/>
     </row>
     <row r="722">
       <c r="A722" s="4"/>
-      <c r="F722" s="45"/>
+      <c r="F722" s="46"/>
       <c r="J722" s="4"/>
     </row>
     <row r="723">
       <c r="A723" s="4"/>
-      <c r="F723" s="45"/>
+      <c r="F723" s="46"/>
       <c r="J723" s="4"/>
     </row>
     <row r="724">
       <c r="A724" s="4"/>
-      <c r="F724" s="45"/>
+      <c r="F724" s="46"/>
       <c r="J724" s="4"/>
     </row>
     <row r="725">
       <c r="A725" s="4"/>
-      <c r="F725" s="45"/>
+      <c r="F725" s="46"/>
       <c r="J725" s="4"/>
     </row>
     <row r="726">
       <c r="A726" s="4"/>
-      <c r="F726" s="45"/>
+      <c r="F726" s="46"/>
       <c r="J726" s="4"/>
     </row>
     <row r="727">
       <c r="A727" s="4"/>
-      <c r="F727" s="45"/>
+      <c r="F727" s="46"/>
       <c r="J727" s="4"/>
     </row>
     <row r="728">
       <c r="A728" s="4"/>
-      <c r="F728" s="45"/>
+      <c r="F728" s="46"/>
       <c r="J728" s="4"/>
     </row>
     <row r="729">
       <c r="A729" s="4"/>
-      <c r="F729" s="45"/>
+      <c r="F729" s="46"/>
       <c r="J729" s="4"/>
     </row>
     <row r="730">
       <c r="A730" s="4"/>
-      <c r="F730" s="45"/>
+      <c r="F730" s="46"/>
       <c r="J730" s="4"/>
     </row>
     <row r="731">
       <c r="A731" s="4"/>
-      <c r="F731" s="45"/>
+      <c r="F731" s="46"/>
       <c r="J731" s="4"/>
     </row>
     <row r="732">
       <c r="A732" s="4"/>
-      <c r="F732" s="45"/>
+      <c r="F732" s="46"/>
       <c r="J732" s="4"/>
     </row>
     <row r="733">
       <c r="A733" s="4"/>
-      <c r="F733" s="45"/>
+      <c r="F733" s="46"/>
       <c r="J733" s="4"/>
     </row>
     <row r="734">
       <c r="A734" s="4"/>
-      <c r="F734" s="45"/>
+      <c r="F734" s="46"/>
       <c r="J734" s="4"/>
     </row>
     <row r="735">
       <c r="A735" s="4"/>
-      <c r="F735" s="45"/>
+      <c r="F735" s="46"/>
       <c r="J735" s="4"/>
     </row>
     <row r="736">
       <c r="A736" s="4"/>
-      <c r="F736" s="45"/>
+      <c r="F736" s="46"/>
       <c r="J736" s="4"/>
     </row>
     <row r="737">
       <c r="A737" s="4"/>
-      <c r="F737" s="45"/>
+      <c r="F737" s="46"/>
       <c r="J737" s="4"/>
     </row>
     <row r="738">
       <c r="A738" s="4"/>
-      <c r="F738" s="45"/>
+      <c r="F738" s="46"/>
       <c r="J738" s="4"/>
     </row>
     <row r="739">
       <c r="A739" s="4"/>
-      <c r="F739" s="45"/>
+      <c r="F739" s="46"/>
       <c r="J739" s="4"/>
     </row>
     <row r="740">
       <c r="A740" s="4"/>
-      <c r="F740" s="45"/>
+      <c r="F740" s="46"/>
       <c r="J740" s="4"/>
     </row>
     <row r="741">
       <c r="A741" s="4"/>
-      <c r="F741" s="45"/>
+      <c r="F741" s="46"/>
       <c r="J741" s="4"/>
     </row>
     <row r="742">
       <c r="A742" s="4"/>
-      <c r="F742" s="45"/>
+      <c r="F742" s="46"/>
       <c r="J742" s="4"/>
     </row>
     <row r="743">
       <c r="A743" s="4"/>
-      <c r="F743" s="45"/>
+      <c r="F743" s="46"/>
       <c r="J743" s="4"/>
     </row>
     <row r="744">
       <c r="A744" s="4"/>
-      <c r="F744" s="45"/>
+      <c r="F744" s="46"/>
       <c r="J744" s="4"/>
     </row>
     <row r="745">
       <c r="A745" s="4"/>
-      <c r="F745" s="45"/>
+      <c r="F745" s="46"/>
       <c r="J745" s="4"/>
     </row>
     <row r="746">
       <c r="A746" s="4"/>
-      <c r="F746" s="45"/>
+      <c r="F746" s="46"/>
       <c r="J746" s="4"/>
     </row>
     <row r="747">
       <c r="A747" s="4"/>
-      <c r="F747" s="45"/>
+      <c r="F747" s="46"/>
       <c r="J747" s="4"/>
     </row>
     <row r="748">
       <c r="A748" s="4"/>
-      <c r="F748" s="45"/>
+      <c r="F748" s="46"/>
       <c r="J748" s="4"/>
     </row>
     <row r="749">
       <c r="A749" s="4"/>
-      <c r="F749" s="45"/>
+      <c r="F749" s="46"/>
       <c r="J749" s="4"/>
     </row>
     <row r="750">
       <c r="A750" s="4"/>
-      <c r="F750" s="45"/>
+      <c r="F750" s="46"/>
       <c r="J750" s="4"/>
     </row>
     <row r="751">
       <c r="A751" s="4"/>
-      <c r="F751" s="45"/>
+      <c r="F751" s="46"/>
       <c r="J751" s="4"/>
     </row>
     <row r="752">
       <c r="A752" s="4"/>
-      <c r="F752" s="45"/>
+      <c r="F752" s="46"/>
       <c r="J752" s="4"/>
     </row>
     <row r="753">
       <c r="A753" s="4"/>
-      <c r="F753" s="45"/>
+      <c r="F753" s="46"/>
       <c r="J753" s="4"/>
     </row>
     <row r="754">
       <c r="A754" s="4"/>
-      <c r="F754" s="45"/>
+      <c r="F754" s="46"/>
       <c r="J754" s="4"/>
     </row>
     <row r="755">
       <c r="A755" s="4"/>
-      <c r="F755" s="45"/>
+      <c r="F755" s="46"/>
       <c r="J755" s="4"/>
     </row>
     <row r="756">
       <c r="A756" s="4"/>
-      <c r="F756" s="45"/>
+      <c r="F756" s="46"/>
       <c r="J756" s="4"/>
     </row>
     <row r="757">
       <c r="A757" s="4"/>
-      <c r="F757" s="45"/>
+      <c r="F757" s="46"/>
       <c r="J757" s="4"/>
     </row>
     <row r="758">
       <c r="A758" s="4"/>
-      <c r="F758" s="45"/>
+      <c r="F758" s="46"/>
       <c r="J758" s="4"/>
     </row>
     <row r="759">
       <c r="A759" s="4"/>
-      <c r="F759" s="45"/>
+      <c r="F759" s="46"/>
       <c r="J759" s="4"/>
     </row>
     <row r="760">
       <c r="A760" s="4"/>
-      <c r="F760" s="45"/>
+      <c r="F760" s="46"/>
       <c r="J760" s="4"/>
     </row>
     <row r="761">
       <c r="A761" s="4"/>
-      <c r="F761" s="45"/>
+      <c r="F761" s="46"/>
       <c r="J761" s="4"/>
     </row>
     <row r="762">
       <c r="A762" s="4"/>
-      <c r="F762" s="45"/>
+      <c r="F762" s="46"/>
       <c r="J762" s="4"/>
     </row>
     <row r="763">
       <c r="A763" s="4"/>
-      <c r="F763" s="45"/>
+      <c r="F763" s="46"/>
       <c r="J763" s="4"/>
     </row>
     <row r="764">
       <c r="A764" s="4"/>
-      <c r="F764" s="45"/>
+      <c r="F764" s="46"/>
       <c r="J764" s="4"/>
     </row>
     <row r="765">
       <c r="A765" s="4"/>
-      <c r="F765" s="45"/>
+      <c r="F765" s="46"/>
       <c r="J765" s="4"/>
     </row>
     <row r="766">
       <c r="A766" s="4"/>
-      <c r="F766" s="45"/>
+      <c r="F766" s="46"/>
       <c r="J766" s="4"/>
     </row>
     <row r="767">
       <c r="A767" s="4"/>
-      <c r="F767" s="45"/>
+      <c r="F767" s="46"/>
       <c r="J767" s="4"/>
     </row>
     <row r="768">
       <c r="A768" s="4"/>
-      <c r="F768" s="45"/>
+      <c r="F768" s="46"/>
       <c r="J768" s="4"/>
     </row>
     <row r="769">
       <c r="A769" s="4"/>
-      <c r="F769" s="45"/>
+      <c r="F769" s="46"/>
       <c r="J769" s="4"/>
     </row>
     <row r="770">
       <c r="A770" s="4"/>
-      <c r="F770" s="45"/>
+      <c r="F770" s="46"/>
       <c r="J770" s="4"/>
     </row>
     <row r="771">
       <c r="A771" s="4"/>
-      <c r="F771" s="45"/>
+      <c r="F771" s="46"/>
       <c r="J771" s="4"/>
     </row>
     <row r="772">
       <c r="A772" s="4"/>
-      <c r="F772" s="45"/>
+      <c r="F772" s="46"/>
       <c r="J772" s="4"/>
     </row>
     <row r="773">
       <c r="A773" s="4"/>
-      <c r="F773" s="45"/>
+      <c r="F773" s="46"/>
       <c r="J773" s="4"/>
     </row>
     <row r="774">
       <c r="A774" s="4"/>
-      <c r="F774" s="45"/>
+      <c r="F774" s="46"/>
       <c r="J774" s="4"/>
     </row>
     <row r="775">
       <c r="A775" s="4"/>
-      <c r="F775" s="45"/>
+      <c r="F775" s="46"/>
       <c r="J775" s="4"/>
     </row>
     <row r="776">
       <c r="A776" s="4"/>
-      <c r="F776" s="45"/>
+      <c r="F776" s="46"/>
       <c r="J776" s="4"/>
     </row>
     <row r="777">
       <c r="A777" s="4"/>
-      <c r="F777" s="45"/>
+      <c r="F777" s="46"/>
       <c r="J777" s="4"/>
     </row>
     <row r="778">
       <c r="A778" s="4"/>
-      <c r="F778" s="45"/>
+      <c r="F778" s="46"/>
       <c r="J778" s="4"/>
     </row>
     <row r="779">
       <c r="A779" s="4"/>
-      <c r="F779" s="45"/>
+      <c r="F779" s="46"/>
       <c r="J779" s="4"/>
     </row>
     <row r="780">
       <c r="A780" s="4"/>
-      <c r="F780" s="45"/>
+      <c r="F780" s="46"/>
       <c r="J780" s="4"/>
     </row>
     <row r="781">
       <c r="A781" s="4"/>
-      <c r="F781" s="45"/>
+      <c r="F781" s="46"/>
       <c r="J781" s="4"/>
     </row>
     <row r="782">
       <c r="A782" s="4"/>
-      <c r="F782" s="45"/>
+      <c r="F782" s="46"/>
       <c r="J782" s="4"/>
     </row>
     <row r="783">
       <c r="A783" s="4"/>
-      <c r="F783" s="45"/>
+      <c r="F783" s="46"/>
       <c r="J783" s="4"/>
     </row>
     <row r="784">
       <c r="A784" s="4"/>
-      <c r="F784" s="45"/>
+      <c r="F784" s="46"/>
       <c r="J784" s="4"/>
     </row>
     <row r="785">
       <c r="A785" s="4"/>
-      <c r="F785" s="45"/>
+      <c r="F785" s="46"/>
       <c r="J785" s="4"/>
     </row>
     <row r="786">
       <c r="A786" s="4"/>
-      <c r="F786" s="45"/>
+      <c r="F786" s="46"/>
       <c r="J786" s="4"/>
     </row>
     <row r="787">
       <c r="A787" s="4"/>
-      <c r="F787" s="45"/>
+      <c r="F787" s="46"/>
       <c r="J787" s="4"/>
     </row>
     <row r="788">
       <c r="A788" s="4"/>
-      <c r="F788" s="45"/>
+      <c r="F788" s="46"/>
       <c r="J788" s="4"/>
     </row>
     <row r="789">
       <c r="A789" s="4"/>
-      <c r="F789" s="45"/>
+      <c r="F789" s="46"/>
       <c r="J789" s="4"/>
     </row>
     <row r="790">
       <c r="A790" s="4"/>
-      <c r="F790" s="45"/>
+      <c r="F790" s="46"/>
       <c r="J790" s="4"/>
     </row>
     <row r="791">
       <c r="A791" s="4"/>
-      <c r="F791" s="45"/>
+      <c r="F791" s="46"/>
       <c r="J791" s="4"/>
     </row>
     <row r="792">
       <c r="A792" s="4"/>
-      <c r="F792" s="45"/>
+      <c r="F792" s="46"/>
       <c r="J792" s="4"/>
     </row>
     <row r="793">
       <c r="A793" s="4"/>
-      <c r="F793" s="45"/>
+      <c r="F793" s="46"/>
       <c r="J793" s="4"/>
     </row>
     <row r="794">
       <c r="A794" s="4"/>
-      <c r="F794" s="45"/>
+      <c r="F794" s="46"/>
       <c r="J794" s="4"/>
     </row>
     <row r="795">
       <c r="A795" s="4"/>
-      <c r="F795" s="45"/>
+      <c r="F795" s="46"/>
       <c r="J795" s="4"/>
     </row>
     <row r="796">
       <c r="A796" s="4"/>
-      <c r="F796" s="45"/>
+      <c r="F796" s="46"/>
       <c r="J796" s="4"/>
     </row>
     <row r="797">
       <c r="A797" s="4"/>
-      <c r="F797" s="45"/>
+      <c r="F797" s="46"/>
       <c r="J797" s="4"/>
     </row>
     <row r="798">
       <c r="A798" s="4"/>
-      <c r="F798" s="45"/>
+      <c r="F798" s="46"/>
       <c r="J798" s="4"/>
     </row>
     <row r="799">
       <c r="A799" s="4"/>
-      <c r="F799" s="45"/>
+      <c r="F799" s="46"/>
       <c r="J799" s="4"/>
     </row>
     <row r="800">
       <c r="A800" s="4"/>
-      <c r="F800" s="45"/>
+      <c r="F800" s="46"/>
       <c r="J800" s="4"/>
     </row>
     <row r="801">
       <c r="A801" s="4"/>
-      <c r="F801" s="45"/>
+      <c r="F801" s="46"/>
       <c r="J801" s="4"/>
     </row>
     <row r="802">
       <c r="A802" s="4"/>
-      <c r="F802" s="45"/>
+      <c r="F802" s="46"/>
       <c r="J802" s="4"/>
     </row>
     <row r="803">
       <c r="A803" s="4"/>
-      <c r="F803" s="45"/>
+      <c r="F803" s="46"/>
       <c r="J803" s="4"/>
     </row>
     <row r="804">
       <c r="A804" s="4"/>
-      <c r="F804" s="45"/>
+      <c r="F804" s="46"/>
       <c r="J804" s="4"/>
     </row>
     <row r="805">
       <c r="A805" s="4"/>
-      <c r="F805" s="45"/>
+      <c r="F805" s="46"/>
       <c r="J805" s="4"/>
     </row>
     <row r="806">
       <c r="A806" s="4"/>
-      <c r="F806" s="45"/>
+      <c r="F806" s="46"/>
       <c r="J806" s="4"/>
     </row>
     <row r="807">
       <c r="A807" s="4"/>
-      <c r="F807" s="45"/>
+      <c r="F807" s="46"/>
       <c r="J807" s="4"/>
     </row>
     <row r="808">
       <c r="A808" s="4"/>
-      <c r="F808" s="45"/>
+      <c r="F808" s="46"/>
       <c r="J808" s="4"/>
     </row>
     <row r="809">
       <c r="A809" s="4"/>
-      <c r="F809" s="45"/>
+      <c r="F809" s="46"/>
       <c r="J809" s="4"/>
     </row>
     <row r="810">
       <c r="A810" s="4"/>
-      <c r="F810" s="45"/>
+      <c r="F810" s="46"/>
       <c r="J810" s="4"/>
     </row>
     <row r="811">
       <c r="A811" s="4"/>
-      <c r="F811" s="45"/>
+      <c r="F811" s="46"/>
       <c r="J811" s="4"/>
     </row>
     <row r="812">
       <c r="A812" s="4"/>
-      <c r="F812" s="45"/>
+      <c r="F812" s="46"/>
       <c r="J812" s="4"/>
     </row>
     <row r="813">
       <c r="A813" s="4"/>
-      <c r="F813" s="45"/>
+      <c r="F813" s="46"/>
       <c r="J813" s="4"/>
     </row>
     <row r="814">
       <c r="A814" s="4"/>
-      <c r="F814" s="45"/>
+      <c r="F814" s="46"/>
       <c r="J814" s="4"/>
     </row>
     <row r="815">
       <c r="A815" s="4"/>
-      <c r="F815" s="45"/>
+      <c r="F815" s="46"/>
       <c r="J815" s="4"/>
     </row>
     <row r="816">
       <c r="A816" s="4"/>
-      <c r="F816" s="45"/>
+      <c r="F816" s="46"/>
       <c r="J816" s="4"/>
     </row>
     <row r="817">
       <c r="A817" s="4"/>
-      <c r="F817" s="45"/>
+      <c r="F817" s="46"/>
       <c r="J817" s="4"/>
     </row>
     <row r="818">
       <c r="A818" s="4"/>
-      <c r="F818" s="45"/>
+      <c r="F818" s="46"/>
       <c r="J818" s="4"/>
     </row>
     <row r="819">
       <c r="A819" s="4"/>
-      <c r="F819" s="45"/>
+      <c r="F819" s="46"/>
       <c r="J819" s="4"/>
     </row>
     <row r="820">
       <c r="A820" s="4"/>
-      <c r="F820" s="45"/>
+      <c r="F820" s="46"/>
       <c r="J820" s="4"/>
     </row>
     <row r="821">
       <c r="A821" s="4"/>
-      <c r="F821" s="45"/>
+      <c r="F821" s="46"/>
       <c r="J821" s="4"/>
     </row>
     <row r="822">
       <c r="A822" s="4"/>
-      <c r="F822" s="45"/>
+      <c r="F822" s="46"/>
       <c r="J822" s="4"/>
     </row>
     <row r="823">
       <c r="A823" s="4"/>
-      <c r="F823" s="45"/>
+      <c r="F823" s="46"/>
       <c r="J823" s="4"/>
     </row>
     <row r="824">
       <c r="A824" s="4"/>
-      <c r="F824" s="45"/>
+      <c r="F824" s="46"/>
       <c r="J824" s="4"/>
     </row>
     <row r="825">
       <c r="A825" s="4"/>
-      <c r="F825" s="45"/>
+      <c r="F825" s="46"/>
       <c r="J825" s="4"/>
     </row>
     <row r="826">
       <c r="A826" s="4"/>
-      <c r="F826" s="45"/>
+      <c r="F826" s="46"/>
       <c r="J826" s="4"/>
     </row>
     <row r="827">
       <c r="A827" s="4"/>
-      <c r="F827" s="45"/>
+      <c r="F827" s="46"/>
       <c r="J827" s="4"/>
     </row>
     <row r="828">
       <c r="A828" s="4"/>
-      <c r="F828" s="45"/>
+      <c r="F828" s="46"/>
       <c r="J828" s="4"/>
     </row>
     <row r="829">
       <c r="A829" s="4"/>
-      <c r="F829" s="45"/>
+      <c r="F829" s="46"/>
       <c r="J829" s="4"/>
     </row>
     <row r="830">
       <c r="A830" s="4"/>
-      <c r="F830" s="45"/>
+      <c r="F830" s="46"/>
       <c r="J830" s="4"/>
     </row>
     <row r="831">
       <c r="A831" s="4"/>
-      <c r="F831" s="45"/>
+      <c r="F831" s="46"/>
       <c r="J831" s="4"/>
     </row>
     <row r="832">
       <c r="A832" s="4"/>
-      <c r="F832" s="45"/>
+      <c r="F832" s="46"/>
       <c r="J832" s="4"/>
     </row>
     <row r="833">
       <c r="A833" s="4"/>
-      <c r="F833" s="45"/>
+      <c r="F833" s="46"/>
       <c r="J833" s="4"/>
     </row>
     <row r="834">
       <c r="A834" s="4"/>
-      <c r="F834" s="45"/>
+      <c r="F834" s="46"/>
       <c r="J834" s="4"/>
     </row>
     <row r="835">
       <c r="A835" s="4"/>
-      <c r="F835" s="45"/>
+      <c r="F835" s="46"/>
       <c r="J835" s="4"/>
     </row>
     <row r="836">
       <c r="A836" s="4"/>
-      <c r="F836" s="45"/>
+      <c r="F836" s="46"/>
       <c r="J836" s="4"/>
     </row>
     <row r="837">
       <c r="A837" s="4"/>
-      <c r="F837" s="45"/>
+      <c r="F837" s="46"/>
       <c r="J837" s="4"/>
     </row>
     <row r="838">
       <c r="A838" s="4"/>
-      <c r="F838" s="45"/>
+      <c r="F838" s="46"/>
       <c r="J838" s="4"/>
     </row>
     <row r="839">
       <c r="A839" s="4"/>
-      <c r="F839" s="45"/>
+      <c r="F839" s="46"/>
       <c r="J839" s="4"/>
     </row>
     <row r="840">
       <c r="A840" s="4"/>
-      <c r="F840" s="45"/>
+      <c r="F840" s="46"/>
       <c r="J840" s="4"/>
     </row>
     <row r="841">
       <c r="A841" s="4"/>
-      <c r="F841" s="45"/>
+      <c r="F841" s="46"/>
       <c r="J841" s="4"/>
     </row>
     <row r="842">
       <c r="A842" s="4"/>
-      <c r="F842" s="45"/>
+      <c r="F842" s="46"/>
       <c r="J842" s="4"/>
     </row>
     <row r="843">
       <c r="A843" s="4"/>
-      <c r="F843" s="45"/>
+      <c r="F843" s="46"/>
       <c r="J843" s="4"/>
     </row>
     <row r="844">
       <c r="A844" s="4"/>
-      <c r="F844" s="45"/>
+      <c r="F844" s="46"/>
       <c r="J844" s="4"/>
     </row>
     <row r="845">
       <c r="A845" s="4"/>
-      <c r="F845" s="45"/>
+      <c r="F845" s="46"/>
       <c r="J845" s="4"/>
     </row>
     <row r="846">
       <c r="A846" s="4"/>
-      <c r="F846" s="45"/>
+      <c r="F846" s="46"/>
       <c r="J846" s="4"/>
     </row>
     <row r="847">
       <c r="A847" s="4"/>
-      <c r="F847" s="45"/>
+      <c r="F847" s="46"/>
       <c r="J847" s="4"/>
     </row>
     <row r="848">
       <c r="A848" s="4"/>
-      <c r="F848" s="45"/>
+      <c r="F848" s="46"/>
       <c r="J848" s="4"/>
     </row>
     <row r="849">
       <c r="A849" s="4"/>
-      <c r="F849" s="45"/>
+      <c r="F849" s="46"/>
       <c r="J849" s="4"/>
     </row>
     <row r="850">
       <c r="A850" s="4"/>
-      <c r="F850" s="45"/>
+      <c r="F850" s="46"/>
       <c r="J850" s="4"/>
     </row>
     <row r="851">
       <c r="A851" s="4"/>
-      <c r="F851" s="45"/>
+      <c r="F851" s="46"/>
       <c r="J851" s="4"/>
     </row>
     <row r="852">
       <c r="A852" s="4"/>
-      <c r="F852" s="45"/>
+      <c r="F852" s="46"/>
       <c r="J852" s="4"/>
     </row>
     <row r="853">
       <c r="A853" s="4"/>
-      <c r="F853" s="45"/>
+      <c r="F853" s="46"/>
       <c r="J853" s="4"/>
     </row>
     <row r="854">
       <c r="A854" s="4"/>
-      <c r="F854" s="45"/>
+      <c r="F854" s="46"/>
       <c r="J854" s="4"/>
     </row>
     <row r="855">
       <c r="A855" s="4"/>
-      <c r="F855" s="45"/>
+      <c r="F855" s="46"/>
       <c r="J855" s="4"/>
     </row>
     <row r="856">
       <c r="A856" s="4"/>
-      <c r="F856" s="45"/>
+      <c r="F856" s="46"/>
       <c r="J856" s="4"/>
     </row>
     <row r="857">
       <c r="A857" s="4"/>
-      <c r="F857" s="45"/>
+      <c r="F857" s="46"/>
       <c r="J857" s="4"/>
     </row>
     <row r="858">
       <c r="A858" s="4"/>
-      <c r="F858" s="45"/>
+      <c r="F858" s="46"/>
       <c r="J858" s="4"/>
     </row>
     <row r="859">
       <c r="A859" s="4"/>
-      <c r="F859" s="45"/>
+      <c r="F859" s="46"/>
       <c r="J859" s="4"/>
     </row>
     <row r="860">
       <c r="A860" s="4"/>
-      <c r="F860" s="45"/>
+      <c r="F860" s="46"/>
       <c r="J860" s="4"/>
     </row>
     <row r="861">
       <c r="A861" s="4"/>
-      <c r="F861" s="45"/>
+      <c r="F861" s="46"/>
       <c r="J861" s="4"/>
     </row>
     <row r="862">
       <c r="A862" s="4"/>
-      <c r="F862" s="45"/>
+      <c r="F862" s="46"/>
       <c r="J862" s="4"/>
     </row>
     <row r="863">
       <c r="A863" s="4"/>
-      <c r="F863" s="45"/>
+      <c r="F863" s="46"/>
       <c r="J863" s="4"/>
     </row>
     <row r="864">
       <c r="A864" s="4"/>
-      <c r="F864" s="45"/>
+      <c r="F864" s="46"/>
       <c r="J864" s="4"/>
     </row>
     <row r="865">
       <c r="A865" s="4"/>
-      <c r="F865" s="45"/>
+      <c r="F865" s="46"/>
       <c r="J865" s="4"/>
     </row>
     <row r="866">
       <c r="A866" s="4"/>
-      <c r="F866" s="45"/>
+      <c r="F866" s="46"/>
       <c r="J866" s="4"/>
     </row>
     <row r="867">
       <c r="A867" s="4"/>
-      <c r="F867" s="45"/>
+      <c r="F867" s="46"/>
       <c r="J867" s="4"/>
     </row>
     <row r="868">
       <c r="A868" s="4"/>
-      <c r="F868" s="45"/>
+      <c r="F868" s="46"/>
       <c r="J868" s="4"/>
     </row>
     <row r="869">
       <c r="A869" s="4"/>
-      <c r="F869" s="45"/>
+      <c r="F869" s="46"/>
       <c r="J869" s="4"/>
     </row>
     <row r="870">
       <c r="A870" s="4"/>
-      <c r="F870" s="45"/>
+      <c r="F870" s="46"/>
       <c r="J870" s="4"/>
     </row>
     <row r="871">
       <c r="A871" s="4"/>
-      <c r="F871" s="45"/>
+      <c r="F871" s="46"/>
       <c r="J871" s="4"/>
     </row>
     <row r="872">
       <c r="A872" s="4"/>
-      <c r="F872" s="45"/>
+      <c r="F872" s="46"/>
       <c r="J872" s="4"/>
     </row>
     <row r="873">
       <c r="A873" s="4"/>
-      <c r="F873" s="45"/>
+      <c r="F873" s="46"/>
       <c r="J873" s="4"/>
     </row>
     <row r="874">
       <c r="A874" s="4"/>
-      <c r="F874" s="45"/>
+      <c r="F874" s="46"/>
       <c r="J874" s="4"/>
     </row>
     <row r="875">
       <c r="A875" s="4"/>
-      <c r="F875" s="45"/>
+      <c r="F875" s="46"/>
       <c r="J875" s="4"/>
     </row>
     <row r="876">
       <c r="A876" s="4"/>
-      <c r="F876" s="45"/>
+      <c r="F876" s="46"/>
       <c r="J876" s="4"/>
     </row>
     <row r="877">
       <c r="A877" s="4"/>
-      <c r="F877" s="45"/>
+      <c r="F877" s="46"/>
       <c r="J877" s="4"/>
     </row>
     <row r="878">
       <c r="A878" s="4"/>
-      <c r="F878" s="45"/>
+      <c r="F878" s="46"/>
       <c r="J878" s="4"/>
     </row>
     <row r="879">
       <c r="A879" s="4"/>
-      <c r="F879" s="45"/>
+      <c r="F879" s="46"/>
       <c r="J879" s="4"/>
     </row>
     <row r="880">
       <c r="A880" s="4"/>
-      <c r="F880" s="45"/>
+      <c r="F880" s="46"/>
       <c r="J880" s="4"/>
     </row>
     <row r="881">
       <c r="A881" s="4"/>
-      <c r="F881" s="45"/>
+      <c r="F881" s="46"/>
       <c r="J881" s="4"/>
     </row>
     <row r="882">
       <c r="A882" s="4"/>
-      <c r="F882" s="45"/>
+      <c r="F882" s="46"/>
       <c r="J882" s="4"/>
     </row>
     <row r="883">
       <c r="A883" s="4"/>
-      <c r="F883" s="45"/>
+      <c r="F883" s="46"/>
       <c r="J883" s="4"/>
     </row>
     <row r="884">
       <c r="A884" s="4"/>
-      <c r="F884" s="45"/>
+      <c r="F884" s="46"/>
       <c r="J884" s="4"/>
     </row>
     <row r="885">
       <c r="A885" s="4"/>
-      <c r="F885" s="45"/>
+      <c r="F885" s="46"/>
       <c r="J885" s="4"/>
     </row>
     <row r="886">
       <c r="A886" s="4"/>
-      <c r="F886" s="45"/>
+      <c r="F886" s="46"/>
       <c r="J886" s="4"/>
     </row>
     <row r="887">
       <c r="A887" s="4"/>
-      <c r="F887" s="45"/>
+      <c r="F887" s="46"/>
       <c r="J887" s="4"/>
     </row>
     <row r="888">
       <c r="A888" s="4"/>
-      <c r="F888" s="45"/>
+      <c r="F888" s="46"/>
       <c r="J888" s="4"/>
     </row>
     <row r="889">
       <c r="A889" s="4"/>
-      <c r="F889" s="45"/>
+      <c r="F889" s="46"/>
       <c r="J889" s="4"/>
     </row>
     <row r="890">
       <c r="A890" s="4"/>
-      <c r="F890" s="45"/>
+      <c r="F890" s="46"/>
       <c r="J890" s="4"/>
     </row>
     <row r="891">
       <c r="A891" s="4"/>
-      <c r="F891" s="45"/>
+      <c r="F891" s="46"/>
       <c r="J891" s="4"/>
     </row>
     <row r="892">
       <c r="A892" s="4"/>
-      <c r="F892" s="45"/>
+      <c r="F892" s="46"/>
       <c r="J892" s="4"/>
     </row>
     <row r="893">
       <c r="A893" s="4"/>
-      <c r="F893" s="45"/>
+      <c r="F893" s="46"/>
       <c r="J893" s="4"/>
     </row>
     <row r="894">
       <c r="A894" s="4"/>
-      <c r="F894" s="45"/>
+      <c r="F894" s="46"/>
       <c r="J894" s="4"/>
     </row>
     <row r="895">
       <c r="A895" s="4"/>
-      <c r="F895" s="45"/>
+      <c r="F895" s="46"/>
       <c r="J895" s="4"/>
     </row>
     <row r="896">
       <c r="A896" s="4"/>
-      <c r="F896" s="45"/>
+      <c r="F896" s="46"/>
       <c r="J896" s="4"/>
     </row>
     <row r="897">
       <c r="A897" s="4"/>
-      <c r="F897" s="45"/>
+      <c r="F897" s="46"/>
       <c r="J897" s="4"/>
     </row>
     <row r="898">
       <c r="A898" s="4"/>
-      <c r="F898" s="45"/>
+      <c r="F898" s="46"/>
       <c r="J898" s="4"/>
     </row>
     <row r="899">
       <c r="A899" s="4"/>
-      <c r="F899" s="45"/>
+      <c r="F899" s="46"/>
       <c r="J899" s="4"/>
     </row>
     <row r="900">
       <c r="A900" s="4"/>
-      <c r="F900" s="45"/>
+      <c r="F900" s="46"/>
       <c r="J900" s="4"/>
     </row>
     <row r="901">
       <c r="A901" s="4"/>
-      <c r="F901" s="45"/>
+      <c r="F901" s="46"/>
       <c r="J901" s="4"/>
     </row>
     <row r="902">
       <c r="A902" s="4"/>
-      <c r="F902" s="45"/>
+      <c r="F902" s="46"/>
       <c r="J902" s="4"/>
     </row>
     <row r="903">
       <c r="A903" s="4"/>
-      <c r="F903" s="45"/>
+      <c r="F903" s="46"/>
       <c r="J903" s="4"/>
     </row>
     <row r="904">
       <c r="A904" s="4"/>
-      <c r="F904" s="45"/>
+      <c r="F904" s="46"/>
       <c r="J904" s="4"/>
     </row>
     <row r="905">
       <c r="A905" s="4"/>
-      <c r="F905" s="45"/>
+      <c r="F905" s="46"/>
       <c r="J905" s="4"/>
     </row>
     <row r="906">
       <c r="A906" s="4"/>
-      <c r="F906" s="45"/>
+      <c r="F906" s="46"/>
       <c r="J906" s="4"/>
     </row>
     <row r="907">
       <c r="A907" s="4"/>
-      <c r="F907" s="45"/>
+      <c r="F907" s="46"/>
       <c r="J907" s="4"/>
     </row>
     <row r="908">
       <c r="A908" s="4"/>
-      <c r="F908" s="45"/>
+      <c r="F908" s="46"/>
       <c r="J908" s="4"/>
     </row>
     <row r="909">
       <c r="A909" s="4"/>
-      <c r="F909" s="45"/>
+      <c r="F909" s="46"/>
       <c r="J909" s="4"/>
     </row>
     <row r="910">
       <c r="A910" s="4"/>
-      <c r="F910" s="45"/>
+      <c r="F910" s="46"/>
       <c r="J910" s="4"/>
     </row>
     <row r="911">
       <c r="A911" s="4"/>
-      <c r="F911" s="45"/>
+      <c r="F911" s="46"/>
       <c r="J911" s="4"/>
     </row>
     <row r="912">
       <c r="A912" s="4"/>
-      <c r="F912" s="45"/>
+      <c r="F912" s="46"/>
       <c r="J912" s="4"/>
     </row>
     <row r="913">
       <c r="A913" s="4"/>
-      <c r="F913" s="45"/>
+      <c r="F913" s="46"/>
       <c r="J913" s="4"/>
     </row>
     <row r="914">
       <c r="A914" s="4"/>
-      <c r="F914" s="45"/>
+      <c r="F914" s="46"/>
       <c r="J914" s="4"/>
     </row>
     <row r="915">
       <c r="A915" s="4"/>
-      <c r="F915" s="45"/>
+      <c r="F915" s="46"/>
       <c r="J915" s="4"/>
     </row>
     <row r="916">
       <c r="A916" s="4"/>
-      <c r="F916" s="45"/>
+      <c r="F916" s="46"/>
       <c r="J916" s="4"/>
     </row>
     <row r="917">
       <c r="A917" s="4"/>
-      <c r="F917" s="45"/>
+      <c r="F917" s="46"/>
       <c r="J917" s="4"/>
     </row>
     <row r="918">
       <c r="A918" s="4"/>
-      <c r="F918" s="45"/>
+      <c r="F918" s="46"/>
       <c r="J918" s="4"/>
     </row>
     <row r="919">
       <c r="A919" s="4"/>
-      <c r="F919" s="45"/>
+      <c r="F919" s="46"/>
       <c r="J919" s="4"/>
     </row>
     <row r="920">
       <c r="A920" s="4"/>
-      <c r="F920" s="45"/>
+      <c r="F920" s="46"/>
       <c r="J920" s="4"/>
     </row>
     <row r="921">
       <c r="A921" s="4"/>
-      <c r="F921" s="45"/>
+      <c r="F921" s="46"/>
       <c r="J921" s="4"/>
     </row>
     <row r="922">
       <c r="A922" s="4"/>
-      <c r="F922" s="45"/>
+      <c r="F922" s="46"/>
       <c r="J922" s="4"/>
     </row>
     <row r="923">
       <c r="A923" s="4"/>
-      <c r="F923" s="45"/>
+      <c r="F923" s="46"/>
       <c r="J923" s="4"/>
     </row>
     <row r="924">
       <c r="A924" s="4"/>
-      <c r="F924" s="45"/>
+      <c r="F924" s="46"/>
       <c r="J924" s="4"/>
     </row>
     <row r="925">
       <c r="A925" s="4"/>
-      <c r="F925" s="45"/>
+      <c r="F925" s="46"/>
       <c r="J925" s="4"/>
     </row>
     <row r="926">
       <c r="A926" s="4"/>
-      <c r="F926" s="45"/>
+      <c r="F926" s="46"/>
       <c r="J926" s="4"/>
     </row>
     <row r="927">
       <c r="A927" s="4"/>
-      <c r="F927" s="45"/>
+      <c r="F927" s="46"/>
       <c r="J927" s="4"/>
     </row>
     <row r="928">
       <c r="A928" s="4"/>
-      <c r="F928" s="45"/>
+      <c r="F928" s="46"/>
       <c r="J928" s="4"/>
     </row>
     <row r="929">
       <c r="A929" s="4"/>
-      <c r="F929" s="45"/>
+      <c r="F929" s="46"/>
       <c r="J929" s="4"/>
     </row>
     <row r="930">
       <c r="A930" s="4"/>
-      <c r="F930" s="45"/>
+      <c r="F930" s="46"/>
       <c r="J930" s="4"/>
     </row>
     <row r="931">
       <c r="A931" s="4"/>
-      <c r="F931" s="45"/>
+      <c r="F931" s="46"/>
       <c r="J931" s="4"/>
     </row>
     <row r="932">
       <c r="A932" s="4"/>
-      <c r="F932" s="45"/>
+      <c r="F932" s="46"/>
       <c r="J932" s="4"/>
     </row>
     <row r="933">
       <c r="A933" s="4"/>
-      <c r="F933" s="45"/>
+      <c r="F933" s="46"/>
       <c r="J933" s="4"/>
     </row>
     <row r="934">
       <c r="A934" s="4"/>
-      <c r="F934" s="45"/>
+      <c r="F934" s="46"/>
       <c r="J934" s="4"/>
     </row>
     <row r="935">
       <c r="A935" s="4"/>
-      <c r="F935" s="45"/>
+      <c r="F935" s="46"/>
       <c r="J935" s="4"/>
     </row>
     <row r="936">
       <c r="A936" s="4"/>
-      <c r="F936" s="45"/>
+      <c r="F936" s="46"/>
       <c r="J936" s="4"/>
     </row>
     <row r="937">
       <c r="A937" s="4"/>
-      <c r="F937" s="45"/>
+      <c r="F937" s="46"/>
       <c r="J937" s="4"/>
     </row>
     <row r="938">
       <c r="A938" s="4"/>
-      <c r="F938" s="45"/>
+      <c r="F938" s="46"/>
       <c r="J938" s="4"/>
     </row>
     <row r="939">
       <c r="A939" s="4"/>
-      <c r="F939" s="45"/>
+      <c r="F939" s="46"/>
       <c r="J939" s="4"/>
     </row>
     <row r="940">
       <c r="A940" s="4"/>
-      <c r="F940" s="45"/>
+      <c r="F940" s="46"/>
       <c r="J940" s="4"/>
     </row>
     <row r="941">
       <c r="A941" s="4"/>
-      <c r="F941" s="45"/>
+      <c r="F941" s="46"/>
       <c r="J941" s="4"/>
     </row>
     <row r="942">
       <c r="A942" s="4"/>
-      <c r="F942" s="45"/>
+      <c r="F942" s="46"/>
       <c r="J942" s="4"/>
     </row>
     <row r="943">
       <c r="A943" s="4"/>
-      <c r="F943" s="45"/>
+      <c r="F943" s="46"/>
       <c r="J943" s="4"/>
     </row>
     <row r="944">
       <c r="A944" s="4"/>
-      <c r="F944" s="45"/>
+      <c r="F944" s="46"/>
       <c r="J944" s="4"/>
     </row>
     <row r="945">
       <c r="A945" s="4"/>
-      <c r="F945" s="45"/>
+      <c r="F945" s="46"/>
       <c r="J945" s="4"/>
     </row>
     <row r="946">
       <c r="A946" s="4"/>
-      <c r="F946" s="45"/>
+      <c r="F946" s="46"/>
       <c r="J946" s="4"/>
     </row>
     <row r="947">
       <c r="A947" s="4"/>
-      <c r="F947" s="45"/>
+      <c r="F947" s="46"/>
       <c r="J947" s="4"/>
     </row>
     <row r="948">
       <c r="A948" s="4"/>
-      <c r="F948" s="45"/>
+      <c r="F948" s="46"/>
       <c r="J948" s="4"/>
     </row>
     <row r="949">
       <c r="A949" s="4"/>
-      <c r="F949" s="45"/>
+      <c r="F949" s="46"/>
       <c r="J949" s="4"/>
     </row>
     <row r="950">
       <c r="A950" s="4"/>
-      <c r="F950" s="45"/>
+      <c r="F950" s="46"/>
       <c r="J950" s="4"/>
     </row>
     <row r="951">
       <c r="A951" s="4"/>
-      <c r="F951" s="45"/>
+      <c r="F951" s="46"/>
       <c r="J951" s="4"/>
     </row>
     <row r="952">
       <c r="A952" s="4"/>
-      <c r="F952" s="45"/>
+      <c r="F952" s="46"/>
       <c r="J952" s="4"/>
     </row>
     <row r="953">
       <c r="A953" s="4"/>
-      <c r="F953" s="45"/>
+      <c r="F953" s="46"/>
       <c r="J953" s="4"/>
     </row>
     <row r="954">
       <c r="A954" s="4"/>
-      <c r="F954" s="45"/>
+      <c r="F954" s="46"/>
       <c r="J954" s="4"/>
     </row>
     <row r="955">
       <c r="A955" s="4"/>
-      <c r="F955" s="45"/>
+      <c r="F955" s="46"/>
       <c r="J955" s="4"/>
     </row>
     <row r="956">
       <c r="A956" s="4"/>
-      <c r="F956" s="45"/>
+      <c r="F956" s="46"/>
       <c r="J956" s="4"/>
     </row>
     <row r="957">
       <c r="A957" s="4"/>
-      <c r="F957" s="45"/>
+      <c r="F957" s="46"/>
       <c r="J957" s="4"/>
     </row>
     <row r="958">
       <c r="A958" s="4"/>
-      <c r="F958" s="45"/>
+      <c r="F958" s="46"/>
       <c r="J958" s="4"/>
     </row>
     <row r="959">
       <c r="A959" s="4"/>
-      <c r="F959" s="45"/>
+      <c r="F959" s="46"/>
       <c r="J959" s="4"/>
     </row>
     <row r="960">
       <c r="A960" s="4"/>
-      <c r="F960" s="45"/>
+      <c r="F960" s="46"/>
       <c r="J960" s="4"/>
     </row>
     <row r="961">
       <c r="A961" s="4"/>
-      <c r="F961" s="45"/>
+      <c r="F961" s="46"/>
       <c r="J961" s="4"/>
     </row>
     <row r="962">
       <c r="A962" s="4"/>
-      <c r="F962" s="45"/>
+      <c r="F962" s="46"/>
       <c r="J962" s="4"/>
     </row>
     <row r="963">
       <c r="A963" s="4"/>
-      <c r="F963" s="45"/>
+      <c r="F963" s="46"/>
       <c r="J963" s="4"/>
     </row>
     <row r="964">
       <c r="A964" s="4"/>
-      <c r="F964" s="45"/>
+      <c r="F964" s="46"/>
       <c r="J964" s="4"/>
     </row>
     <row r="965">
       <c r="A965" s="4"/>
-      <c r="F965" s="45"/>
+      <c r="F965" s="46"/>
       <c r="J965" s="4"/>
     </row>
     <row r="966">
       <c r="A966" s="4"/>
-      <c r="F966" s="45"/>
+      <c r="F966" s="46"/>
       <c r="J966" s="4"/>
     </row>
     <row r="967">
       <c r="A967" s="4"/>
-      <c r="F967" s="45"/>
+      <c r="F967" s="46"/>
       <c r="J967" s="4"/>
     </row>
     <row r="968">
       <c r="A968" s="4"/>
-      <c r="F968" s="45"/>
+      <c r="F968" s="46"/>
       <c r="J968" s="4"/>
     </row>
     <row r="969">
       <c r="A969" s="4"/>
-      <c r="F969" s="45"/>
+      <c r="F969" s="46"/>
       <c r="J969" s="4"/>
     </row>
     <row r="970">
       <c r="A970" s="4"/>
-      <c r="F970" s="45"/>
+      <c r="F970" s="46"/>
       <c r="J970" s="4"/>
     </row>
     <row r="971">
       <c r="A971" s="4"/>
-      <c r="F971" s="45"/>
+      <c r="F971" s="46"/>
       <c r="J971" s="4"/>
     </row>
     <row r="972">
       <c r="A972" s="4"/>
-      <c r="F972" s="45"/>
+      <c r="F972" s="46"/>
       <c r="J972" s="4"/>
     </row>
     <row r="973">
       <c r="A973" s="4"/>
-      <c r="F973" s="45"/>
+      <c r="F973" s="46"/>
       <c r="J973" s="4"/>
     </row>
     <row r="974">
       <c r="A974" s="4"/>
-      <c r="F974" s="45"/>
+      <c r="F974" s="46"/>
       <c r="J974" s="4"/>
     </row>
     <row r="975">
       <c r="A975" s="4"/>
-      <c r="F975" s="45"/>
+      <c r="F975" s="46"/>
       <c r="J975" s="4"/>
     </row>
     <row r="976">
       <c r="A976" s="4"/>
-      <c r="F976" s="45"/>
+      <c r="F976" s="46"/>
       <c r="J976" s="4"/>
     </row>
     <row r="977">
       <c r="A977" s="4"/>
-      <c r="F977" s="45"/>
+      <c r="F977" s="46"/>
       <c r="J977" s="4"/>
     </row>
     <row r="978">
       <c r="A978" s="4"/>
-      <c r="F978" s="45"/>
+      <c r="F978" s="46"/>
       <c r="J978" s="4"/>
     </row>
     <row r="979">
       <c r="A979" s="4"/>
-      <c r="F979" s="45"/>
+      <c r="F979" s="46"/>
       <c r="J979" s="4"/>
     </row>
     <row r="980">
       <c r="A980" s="4"/>
-      <c r="F980" s="45"/>
+      <c r="F980" s="46"/>
       <c r="J980" s="4"/>
     </row>
     <row r="981">
       <c r="A981" s="4"/>
-      <c r="F981" s="45"/>
+      <c r="F981" s="46"/>
       <c r="J981" s="4"/>
     </row>
     <row r="982">
       <c r="A982" s="4"/>
-      <c r="F982" s="45"/>
+      <c r="F982" s="46"/>
       <c r="J982" s="4"/>
     </row>
     <row r="983">
       <c r="A983" s="4"/>
-      <c r="F983" s="45"/>
+      <c r="F983" s="46"/>
       <c r="J983" s="4"/>
     </row>
     <row r="984">
       <c r="A984" s="4"/>
-      <c r="F984" s="45"/>
+      <c r="F984" s="46"/>
       <c r="J984" s="4"/>
     </row>
     <row r="985">
       <c r="A985" s="4"/>
-      <c r="F985" s="45"/>
+      <c r="F985" s="46"/>
       <c r="J985" s="4"/>
     </row>
     <row r="986">
       <c r="A986" s="4"/>
-      <c r="F986" s="45"/>
+      <c r="F986" s="46"/>
       <c r="J986" s="4"/>
     </row>
     <row r="987">
       <c r="A987" s="4"/>
-      <c r="F987" s="45"/>
+      <c r="F987" s="46"/>
       <c r="J987" s="4"/>
     </row>
     <row r="988">
       <c r="A988" s="4"/>
-      <c r="F988" s="45"/>
+      <c r="F988" s="46"/>
       <c r="J988" s="4"/>
     </row>
     <row r="989">
       <c r="A989" s="4"/>
-      <c r="F989" s="45"/>
+      <c r="F989" s="46"/>
       <c r="J989" s="4"/>
     </row>
     <row r="990">
       <c r="A990" s="4"/>
-      <c r="F990" s="45"/>
+      <c r="F990" s="46"/>
       <c r="J990" s="4"/>
     </row>
     <row r="991">
       <c r="A991" s="4"/>
-      <c r="F991" s="45"/>
+      <c r="F991" s="46"/>
       <c r="J991" s="4"/>
     </row>
     <row r="992">
       <c r="A992" s="4"/>
-      <c r="F992" s="45"/>
+      <c r="F992" s="46"/>
       <c r="J992" s="4"/>
     </row>
     <row r="993">
       <c r="A993" s="4"/>
-      <c r="F993" s="45"/>
+      <c r="F993" s="46"/>
       <c r="J993" s="4"/>
     </row>
     <row r="994">
       <c r="A994" s="4"/>
-      <c r="F994" s="45"/>
+      <c r="F994" s="46"/>
       <c r="J994" s="4"/>
     </row>
     <row r="995">
       <c r="A995" s="4"/>
-      <c r="F995" s="45"/>
+      <c r="F995" s="46"/>
       <c r="J995" s="4"/>
     </row>
     <row r="996">
       <c r="A996" s="4"/>
-      <c r="F996" s="45"/>
+      <c r="F996" s="46"/>
       <c r="J996" s="4"/>
     </row>
     <row r="997">
       <c r="A997" s="4"/>
-      <c r="F997" s="45"/>
+      <c r="F997" s="46"/>
       <c r="J997" s="4"/>
     </row>
     <row r="998">
       <c r="A998" s="4"/>
-      <c r="F998" s="45"/>
+      <c r="F998" s="46"/>
       <c r="J998" s="4"/>
     </row>
     <row r="999">
       <c r="A999" s="4"/>
-      <c r="F999" s="45"/>
+      <c r="F999" s="46"/>
       <c r="J999" s="4"/>
     </row>
   </sheetData>
